--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -601,7 +601,7 @@
         <v>46057</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>46070</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44722</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46205</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46033</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>46184</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45092</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>46181</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>46033</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45016</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>44637</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45812</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>46140</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>46178</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>45785</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>46205</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>46157</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45775</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45917</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>46069</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>46191</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45897</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>46055</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45469</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45016</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45533</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>46196</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>46178</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>46178</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         <v>46089</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>46033</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>46196</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>46104</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>45932</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>45510</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>45695</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>46055</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>45016</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>44610</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>45938</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>46055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>44090</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>44722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45099</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>45583</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>45775</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>46055</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>46178</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>46190</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>46029</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>45839</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44722</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>45971</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>46055</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>46092</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45799</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>44464</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>45754</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>45903</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>45181</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>44796</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>46093</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>45713</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>46258</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>45443</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>45315</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>44589</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>45903</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>44704</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>44741</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>45895</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>45925</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>44936</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>45995</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>44501</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>45714</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>44641</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>46164</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>45233</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>45831</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45831</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>44722</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>44721</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>44867</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>44910</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>45705</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>45461</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>45623</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>45119</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>45824</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>44523</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>45246</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45971</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>45188</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>45053</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>46029</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>45187</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>45631</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>45538</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>44944</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>45247</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>45713</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>45461</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>46266</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>45053</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>46274</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>45411</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>44637</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>44512</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>44489</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>44508</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44537</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>44511</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44712</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>44852</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>44733</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>44811</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>44756</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44887</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>44696</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>44616</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>44503</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>44588</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>44809</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44602</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>44533</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>44529</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>44462</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>44501</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>44613</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>44540</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>44701</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>44469</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>44721</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>44557</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44547</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>44802</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>44512</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>44886</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>44739</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>44721</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>44743</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>44743</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>44616</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>44811</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>44839</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>44544</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>44749</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44858</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>44501</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>44600</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>44603</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>44743</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>44811</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44811</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>45632</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>45645</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44978</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>45674</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>45244</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>45519</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>45007</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>45713</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>44900</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44515</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45252</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>45191</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>45769</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>44894</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>44599</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>45093</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>45636</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>45225</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>45237</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45162</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>45677</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>44832</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>45245</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>45559</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>45747</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>45453</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>45644</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>45629</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>45089</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>45727</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>45592</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>45659</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19697,7 +19697,7 @@
         <v>45761</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44928</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44896</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45202</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45071</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>44903</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44739</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>44741</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>45191</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>45152</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>45231</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>44903</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>44946</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>44931</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45204</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>44804</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>45461</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>44938</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>45072</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>45037</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45238</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>45428</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44462</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>45541</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45477</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>44677</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>44897</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>45219</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>45121</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45677</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>44886</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>44881</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>45530</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>45229</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>45672</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45036</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45541</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>44860</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>45204</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45204</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>45642</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>45714</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>45692</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45203</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>45541</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>45534</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>45763</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>45198</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>45608</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>45257</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>45525</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>45257</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>45575</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>44911</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>45243</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>45237</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>45237</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23948,7 +23948,7 @@
         <v>45622</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>45712</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>45007</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>45488</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>45547</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>45883</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45728</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>45757</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45714</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45609</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>46136</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>44637</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>45448</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>45642</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>45211</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>45875</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>45831</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>45902</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44994</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>45252</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>45153</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>45891</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>45891</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>45891</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45890</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>45890</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>45891</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>45892</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>45895</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45894</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45491</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>45749</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>44697</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45090</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45898</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>45079</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>45898</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>45775</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45597</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45769</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>45540</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>44881</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>45901</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>45511</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>45757</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>45902</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>45902</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>45902</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>45902</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44511</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>46133</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>46031</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45904</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>45904</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45713</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>45875</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>45908</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>45162</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>45470</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>45566</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>45481</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>45910</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>45721</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45910</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>45824</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>46140</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>45911</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>45654</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>45915</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>45841</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>45336</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45912</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>45665</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>45912</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>45485</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>45600</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>45916</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>45916</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>45916</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>45919</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>45919</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>45713</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>45919</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>45636</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>45510</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>45749</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         <v>45925</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30444,7 +30444,7 @@
         <v>45761</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>45926</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>45926</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>45929</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30746,7 +30746,7 @@
         <v>45929</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>45406</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
         <v>45294</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>46142</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>45930</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>45624</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31194,7 +31194,7 @@
         <v>45624</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>45931</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>45931</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>45931</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>45792</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         <v>45266</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>44903</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31710,7 +31710,7 @@
         <v>45062</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>45933</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>45933</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>45236</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>44740</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>45434</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>45936</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>45936</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45936</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>45322</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>45817</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>45937</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>45937</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>45937</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>45939</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32845,7 +32845,7 @@
         <v>44501</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>45937</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>46146</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>44938</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>45460</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>45937</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>45940</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>45339</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>45541</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>45930</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>45940</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45643</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>45301</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>46149</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>46148</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>45947</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>46149</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>45041</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>45931</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>45951</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34360,7 +34360,7 @@
         <v>46153</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>45225</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>45952</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>45952</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>45574</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>44950</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>45957</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>45957</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45957</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>45957</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>45957</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>45957</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>45672</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>45567</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>45957</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35490,7 +35490,7 @@
         <v>45548</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>45673</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>45960</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35714,7 +35714,7 @@
         <v>45960</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>45538</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>45960</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>45959</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>45965</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>45964</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36167,7 +36167,7 @@
         <v>45964</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36245,7 +36245,7 @@
         <v>45964</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36318,7 +36318,7 @@
         <v>45964</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>45965</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45106</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>44881</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45580</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>45967</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>45967</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36829,7 +36829,7 @@
         <v>45965</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36907,7 +36907,7 @@
         <v>45965</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>45971</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45197</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>45925</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45973</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>45971</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>45972</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>45972</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37506,7 +37506,7 @@
         <v>45973</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37584,7 +37584,7 @@
         <v>44897</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>45629</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37730,7 +37730,7 @@
         <v>45974</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>45450</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>45974</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37959,7 +37959,7 @@
         <v>45560</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>45978</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>45978</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>45874</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45979</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>45223</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>45980</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>45981</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38553,7 +38553,7 @@
         <v>45980</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38626,7 +38626,7 @@
         <v>45439</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>44979</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>45769</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45566</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>45439</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>45163</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>45720</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>45727</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45355</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39308,7 +39308,7 @@
         <v>45525</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>45987</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>45987</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39532,7 +39532,7 @@
         <v>46160</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39610,7 +39610,7 @@
         <v>45989</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>45989</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>45646</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>46160</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>45993</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39995,7 +39995,7 @@
         <v>44508</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40068,7 +40068,7 @@
         <v>45992</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>45992</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>45539</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40292,7 +40292,7 @@
         <v>45187</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40365,7 +40365,7 @@
         <v>46160</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40443,7 +40443,7 @@
         <v>45407</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>45679</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>45993</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>45993</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40740,7 +40740,7 @@
         <v>45429</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>45709</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>45999</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>46001</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>46001</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>46003</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>46003</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>45449</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>46002</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>46002</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>45483</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45560</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
         <v>46007</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>46006</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>46006</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41855,7 +41855,7 @@
         <v>45608</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45177</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>46008</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>46009</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>46008</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>46010</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>46010</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>46010</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42454,7 +42454,7 @@
         <v>44789</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42527,7 +42527,7 @@
         <v>45294</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45462</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42673,7 +42673,7 @@
         <v>45236</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>45271</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42824,7 +42824,7 @@
         <v>46024</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42897,7 +42897,7 @@
         <v>46029</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>46030</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43048,7 +43048,7 @@
         <v>46031</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>46034</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>46034</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>46035</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43345,7 +43345,7 @@
         <v>46034</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>46034</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>44978</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>44981</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43642,7 +43642,7 @@
         <v>46036</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43715,7 +43715,7 @@
         <v>46036</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43788,7 +43788,7 @@
         <v>46036</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43861,7 +43861,7 @@
         <v>46036</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>46036</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44007,7 +44007,7 @@
         <v>46036</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44080,7 +44080,7 @@
         <v>44495</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44153,7 +44153,7 @@
         <v>46036</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44226,7 +44226,7 @@
         <v>46036</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45982</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44377,7 +44377,7 @@
         <v>45215</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>44725</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>44546</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>45757</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>44908</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>46174</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44830,7 +44830,7 @@
         <v>44907</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44903,7 +44903,7 @@
         <v>44963</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44976,7 +44976,7 @@
         <v>45149</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45054,7 +45054,7 @@
         <v>45168</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45127,7 +45127,7 @@
         <v>45624</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>45335</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>45621</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>46034</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45419,7 +45419,7 @@
         <v>46044</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>46044</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45565,7 +45565,7 @@
         <v>45509</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45638,7 +45638,7 @@
         <v>44862</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45711,7 +45711,7 @@
         <v>45097</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>45614</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>44795</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>45957</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         <v>45491</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>46055</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>44923</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>44923</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46300,7 +46300,7 @@
         <v>44923</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46373,7 +46373,7 @@
         <v>45177</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>44938</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46519,7 +46519,7 @@
         <v>44782</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>45188</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>45188</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46743,7 +46743,7 @@
         <v>46059</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46816,7 +46816,7 @@
         <v>46059</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>46059</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46962,7 +46962,7 @@
         <v>46059</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>46177</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
         <v>46064</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>44928</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>46064</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>45252</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47405,7 +47405,7 @@
         <v>46066</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>46070</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>45321</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47629,7 +47629,7 @@
         <v>45670</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47702,7 +47702,7 @@
         <v>45267</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47775,7 +47775,7 @@
         <v>45574</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47853,7 +47853,7 @@
         <v>46073</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47931,7 +47931,7 @@
         <v>46073</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48004,7 +48004,7 @@
         <v>45621</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>46073</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48150,7 +48150,7 @@
         <v>45642</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48223,7 +48223,7 @@
         <v>45226</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48301,7 +48301,7 @@
         <v>45483</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>45642</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48447,7 +48447,7 @@
         <v>45503</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>46073</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>45072</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48681,7 +48681,7 @@
         <v>45195</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>44523</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>45204</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48910,7 +48910,7 @@
         <v>45106</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>46085</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45583</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>45244</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45597</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49285,7 +49285,7 @@
         <v>45246</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45645</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49431,7 +49431,7 @@
         <v>46189</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>45775</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49582,7 +49582,7 @@
         <v>46029</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>46189</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49738,7 +49738,7 @@
         <v>46092</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49811,7 +49811,7 @@
         <v>46092</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49884,7 +49884,7 @@
         <v>45874</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49957,7 +49957,7 @@
         <v>46093</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>46093</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>45720</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50176,7 +50176,7 @@
         <v>46093</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50249,7 +50249,7 @@
         <v>45483</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50322,7 +50322,7 @@
         <v>45756</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50400,7 +50400,7 @@
         <v>46098</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>46100</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50546,7 +50546,7 @@
         <v>46104</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50619,7 +50619,7 @@
         <v>45665</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50692,7 +50692,7 @@
         <v>45672</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50765,7 +50765,7 @@
         <v>45077</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45391</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50911,7 +50911,7 @@
         <v>45231</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50984,7 +50984,7 @@
         <v>44837</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51062,7 +51062,7 @@
         <v>45225</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         <v>44888</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51213,7 +51213,7 @@
         <v>44643</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51291,7 +51291,7 @@
         <v>46107</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51364,7 +51364,7 @@
         <v>45531</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51442,7 +51442,7 @@
         <v>45769</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51515,7 +51515,7 @@
         <v>45355</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>45072</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>45118</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51739,7 +51739,7 @@
         <v>44540</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51817,7 +51817,7 @@
         <v>46121</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>46126</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>45078</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52051,7 +52051,7 @@
         <v>45225</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52124,7 +52124,7 @@
         <v>46244</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>46126</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>46245</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52343,7 +52343,7 @@
         <v>46128</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52416,7 +52416,7 @@
         <v>46202</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>46245</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52567,7 +52567,7 @@
         <v>45215</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>45034</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52713,7 +52713,7 @@
         <v>46128</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52786,7 +52786,7 @@
         <v>46127</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52859,7 +52859,7 @@
         <v>45579</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52937,7 +52937,7 @@
         <v>46127</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53010,7 +53010,7 @@
         <v>46133</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>46132</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53166,7 +53166,7 @@
         <v>44923</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>46132</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53317,7 +53317,7 @@
         <v>45639</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53390,7 +53390,7 @@
         <v>45456</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
         <v>46135</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53546,7 +53546,7 @@
         <v>44623</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53624,7 +53624,7 @@
         <v>45446</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53702,7 +53702,7 @@
         <v>45272</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>46134</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53853,7 +53853,7 @@
         <v>44914</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>46247</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53999,7 +53999,7 @@
         <v>45201</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54072,7 +54072,7 @@
         <v>45430</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54145,7 +54145,7 @@
         <v>46204</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54218,7 +54218,7 @@
         <v>45034</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54291,7 +54291,7 @@
         <v>45257</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54364,7 +54364,7 @@
         <v>44916</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
         <v>46246</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54510,7 +54510,7 @@
         <v>44589</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45646</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54661,7 +54661,7 @@
         <v>46205</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54734,7 +54734,7 @@
         <v>45128</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54812,7 +54812,7 @@
         <v>45245</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54885,7 +54885,7 @@
         <v>45684</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54958,7 +54958,7 @@
         <v>45072</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55031,7 +55031,7 @@
         <v>45238</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55104,7 +55104,7 @@
         <v>45476</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55177,7 +55177,7 @@
         <v>45187</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55250,7 +55250,7 @@
         <v>45561</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55323,7 +55323,7 @@
         <v>45355</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55396,7 +55396,7 @@
         <v>45355</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55469,7 +55469,7 @@
         <v>45301</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55542,7 +55542,7 @@
         <v>45623</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55615,7 +55615,7 @@
         <v>45636</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55688,7 +55688,7 @@
         <v>45303</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55761,7 +55761,7 @@
         <v>45271</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55834,7 +55834,7 @@
         <v>46211</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55912,7 +55912,7 @@
         <v>44623</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55985,7 +55985,7 @@
         <v>45420</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56058,7 +56058,7 @@
         <v>46211</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56136,7 +56136,7 @@
         <v>45194</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56209,7 +56209,7 @@
         <v>45204</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56287,7 +56287,7 @@
         <v>45089</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56365,7 +56365,7 @@
         <v>44791</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56443,7 +56443,7 @@
         <v>45027</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56516,7 +56516,7 @@
         <v>45054</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56589,7 +56589,7 @@
         <v>46259</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56667,7 +56667,7 @@
         <v>45720</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56740,7 +56740,7 @@
         <v>45749</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>44950</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56886,7 +56886,7 @@
         <v>44725</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56964,7 +56964,7 @@
         <v>45491</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57042,7 +57042,7 @@
         <v>45293</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45432</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57188,7 +57188,7 @@
         <v>45638</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57261,7 +57261,7 @@
         <v>45175</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57334,7 +57334,7 @@
         <v>44928</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>45517</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57480,7 +57480,7 @@
         <v>45226</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57553,7 +57553,7 @@
         <v>45053</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>45175</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57699,7 +57699,7 @@
         <v>45726</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57772,7 +57772,7 @@
         <v>45442</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57845,7 +57845,7 @@
         <v>46267</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57918,7 +57918,7 @@
         <v>45041</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57991,7 +57991,7 @@
         <v>45547</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58064,7 +58064,7 @@
         <v>45301</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58137,7 +58137,7 @@
         <v>44512</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58215,7 +58215,7 @@
         <v>45119</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58288,7 +58288,7 @@
         <v>44957</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58361,7 +58361,7 @@
         <v>46226</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58434,7 +58434,7 @@
         <v>45482</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58512,7 +58512,7 @@
         <v>45525</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58585,7 +58585,7 @@
         <v>46272</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58663,7 +58663,7 @@
         <v>46272</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58741,7 +58741,7 @@
         <v>45455</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58819,7 +58819,7 @@
         <v>44911</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58892,7 +58892,7 @@
         <v>46272</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58970,7 +58970,7 @@
         <v>46272</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59048,7 +59048,7 @@
         <v>46274</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59121,7 +59121,7 @@
         <v>46274</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59194,7 +59194,7 @@
         <v>46275</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59272,7 +59272,7 @@
         <v>46274</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59350,7 +59350,7 @@
         <v>46275</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59428,7 +59428,7 @@
         <v>46231</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59506,7 +59506,7 @@
         <v>44641</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59584,7 +59584,7 @@
         <v>45399</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59657,7 +59657,7 @@
         <v>45054</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59735,7 +59735,7 @@
         <v>45789</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59813,7 +59813,7 @@
         <v>46275</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59891,7 +59891,7 @@
         <v>46280</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59969,7 +59969,7 @@
         <v>45195</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60042,7 +60042,7 @@
         <v>45712</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60115,7 +60115,7 @@
         <v>45488</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60193,7 +60193,7 @@
         <v>45036</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60266,7 +60266,7 @@
         <v>45229</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60344,7 +60344,7 @@
         <v>45020</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60417,7 +60417,7 @@
         <v>45797</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60495,7 +60495,7 @@
         <v>44923</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60568,7 +60568,7 @@
         <v>45540</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60641,7 +60641,7 @@
         <v>45797</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60719,7 +60719,7 @@
         <v>45797</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60792,7 +60792,7 @@
         <v>45797</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60870,7 +60870,7 @@
         <v>46239</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60943,7 +60943,7 @@
         <v>45188</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61016,7 +61016,7 @@
         <v>46239</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61089,7 +61089,7 @@
         <v>46283</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61167,7 +61167,7 @@
         <v>46282</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61245,7 +61245,7 @@
         <v>45799</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61318,7 +61318,7 @@
         <v>45800</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61396,7 +61396,7 @@
         <v>45800</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61474,7 +61474,7 @@
         <v>45747</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61552,7 +61552,7 @@
         <v>45805</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>45804</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61708,7 +61708,7 @@
         <v>45804</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61781,7 +61781,7 @@
         <v>45805</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61859,7 +61859,7 @@
         <v>45804</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61932,7 +61932,7 @@
         <v>45747</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62005,7 +62005,7 @@
         <v>45807</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62078,7 +62078,7 @@
         <v>45807</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62151,7 +62151,7 @@
         <v>45810</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62224,7 +62224,7 @@
         <v>45322</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62297,7 +62297,7 @@
         <v>45817</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62375,7 +62375,7 @@
         <v>45740</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62448,7 +62448,7 @@
         <v>45818</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62521,7 +62521,7 @@
         <v>45762</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62594,7 +62594,7 @@
         <v>45818</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62667,7 +62667,7 @@
         <v>45818</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62740,7 +62740,7 @@
         <v>45749</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62813,7 +62813,7 @@
         <v>45820</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62886,7 +62886,7 @@
         <v>45821</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62964,7 +62964,7 @@
         <v>45821</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63042,7 +63042,7 @@
         <v>45821</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63120,7 +63120,7 @@
         <v>45824</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63193,7 +63193,7 @@
         <v>45824</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63266,7 +63266,7 @@
         <v>45827</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63339,7 +63339,7 @@
         <v>45831</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63417,7 +63417,7 @@
         <v>45831</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63495,7 +63495,7 @@
         <v>45833</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63573,7 +63573,7 @@
         <v>45832</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63651,7 +63651,7 @@
         <v>45833</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63729,7 +63729,7 @@
         <v>45832</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63807,7 +63807,7 @@
         <v>45835</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63880,7 +63880,7 @@
         <v>45838</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63953,7 +63953,7 @@
         <v>45839</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64026,7 +64026,7 @@
         <v>45838</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64104,7 +64104,7 @@
         <v>45839</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64177,7 +64177,7 @@
         <v>45840</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64250,7 +64250,7 @@
         <v>45841</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64323,7 +64323,7 @@
         <v>45840</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64401,7 +64401,7 @@
         <v>45841</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64474,7 +64474,7 @@
         <v>45841</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64552,7 +64552,7 @@
         <v>45841</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64630,7 +64630,7 @@
         <v>45841</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64708,7 +64708,7 @@
         <v>45842</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64781,7 +64781,7 @@
         <v>45357</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64854,7 +64854,7 @@
         <v>45846</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64927,7 +64927,7 @@
         <v>45849</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65005,7 +65005,7 @@
         <v>45849</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65078,7 +65078,7 @@
         <v>45849</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65151,7 +65151,7 @@
         <v>45849</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65224,7 +65224,7 @@
         <v>45853</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65302,7 +65302,7 @@
         <v>45855</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65380,7 +65380,7 @@
         <v>45855</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65453,7 +65453,7 @@
         <v>45867</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65526,7 +65526,7 @@
         <v>45694</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65599,7 +65599,7 @@
         <v>45880</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65672,7 +65672,7 @@
         <v>45880</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65745,7 +65745,7 @@
         <v>45880</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65818,7 +65818,7 @@
         <v>45762</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65891,7 +65891,7 @@
         <v>45883</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65964,7 +65964,7 @@
         <v>44722</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66042,7 +66042,7 @@
         <v>45371</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66115,7 +66115,7 @@
         <v>44684</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66193,7 +66193,7 @@
         <v>45699</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66271,7 +66271,7 @@
         <v>45756</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66349,7 +66349,7 @@
         <v>45778</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66422,7 +66422,7 @@
         <v>45342</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66495,7 +66495,7 @@
         <v>46089</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66573,7 +66573,7 @@
         <v>46072</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66651,7 +66651,7 @@
         <v>46171</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>

--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -601,7 +601,7 @@
         <v>46057</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>46070</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44722</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46205</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46033</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>46184</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45092</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>46181</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>46033</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45016</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>44637</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45812</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>46140</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>46178</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>45785</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>46205</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>46157</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>44796</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45775</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45917</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>46069</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>46191</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45897</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>46055</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45469</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45016</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>45533</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>46196</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>46178</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>46178</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         <v>46089</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>46104</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>46033</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>46196</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>45932</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>46055</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>45695</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>45510</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>45016</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>44610</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>45938</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>46055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>44090</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>44722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45099</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>46055</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>45775</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45839</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>46178</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>46029</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>46190</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>45583</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44722</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>45799</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>46055</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>46092</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>45971</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>45903</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>46093</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44796</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>45443</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>45181</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>46258</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>45754</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>45713</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>44589</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>45315</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>45903</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>44704</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>45895</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>45925</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>44936</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>45995</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>45831</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>45831</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>44501</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>45714</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>46164</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>44641</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>44741</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>45233</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44722</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>44721</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>45119</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>44523</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>46029</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>45538</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>44910</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>45971</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>45461</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>45824</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>45705</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>44944</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>45631</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45247</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>45187</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>46266</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>45188</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>46274</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>45246</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45053</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>46287</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>46290</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>45623</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>45713</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>45461</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>44867</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>45053</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>44637</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>45411</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44512</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>44489</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>44508</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>44537</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>44511</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>44712</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44852</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>44733</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>44811</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>44756</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>44887</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>44696</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>44616</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>44503</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>44588</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>44809</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44602</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>44533</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>44529</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>44501</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>44613</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>44540</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>44701</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>44469</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>44721</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>44557</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>44547</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>44802</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>44512</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44886</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>44721</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44739</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>44743</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>44743</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>44616</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>44811</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44839</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>44544</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44749</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44858</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44501</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>44600</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>44603</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>44743</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>44811</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>44811</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>45089</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45709</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>44725</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45187</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>44862</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45531</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45215</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>44795</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45541</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>45252</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45335</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45720</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45391</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>45321</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>44928</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45267</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>44903</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45446</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>44914</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44897</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44546</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>45271</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>45883</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>46024</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45712</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>45188</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45229</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45020</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>45294</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>46030</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>45540</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45488</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>45503</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>45483</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>45036</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>44923</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45797</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>45797</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>45797</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>45797</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
         <v>46029</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>46031</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>46034</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20580,7 +20580,7 @@
         <v>46034</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>46034</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>46034</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         <v>45434</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>44928</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>46035</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21028,7 +21028,7 @@
         <v>46036</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>46036</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>46036</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>45799</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>46036</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>45483</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>46036</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>46036</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>46036</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>45890</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>45890</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>46036</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>45511</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45891</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
         <v>45800</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>45891</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45892</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45195</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45583</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>45891</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>45891</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>45894</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>45982</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>44896</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45895</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>46044</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>45775</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>44907</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45898</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>46044</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>45898</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>45488</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>45540</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>46034</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>45902</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>45902</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45902</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>45902</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45901</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>45456</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>45904</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>45491</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>45491</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>45904</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>45875</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45908</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>45481</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>45800</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>45476</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
         <v>45910</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>45910</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>46055</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>45912</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>45911</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>45912</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>45525</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25246,7 +25246,7 @@
         <v>45804</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>45747</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45916</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>45915</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45916</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>45916</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>45608</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>46059</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>46059</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>46059</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>46059</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45525</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>45713</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>45547</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
         <v>44928</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>46064</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>46064</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>45919</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>45804</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>45919</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26721,7 +26721,7 @@
         <v>45919</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26794,7 +26794,7 @@
         <v>45561</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>46066</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>45225</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>46070</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45636</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45804</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>45747</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>45805</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         <v>45041</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>45925</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>45926</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>45805</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>46073</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>46073</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>46073</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>45926</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45534</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45930</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45931</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>46085</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>45807</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>45632</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>45322</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45807</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45449</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>45810</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45931</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45442</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>45931</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>46073</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45575</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44916</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45933</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45933</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>45936</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45429</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>45936</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45936</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>45937</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45937</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29774,7 +29774,7 @@
         <v>45937</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>46093</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29925,7 +29925,7 @@
         <v>45937</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>44512</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45679</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30154,7 +30154,7 @@
         <v>46092</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>46093</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>45937</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30373,7 +30373,7 @@
         <v>45244</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>45940</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>46093</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30592,7 +30592,7 @@
         <v>44923</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>44923</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>45874</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>45757</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>46092</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30957,7 +30957,7 @@
         <v>45939</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>45930</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31108,7 +31108,7 @@
         <v>45646</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>45646</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>46098</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44903</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45007</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>45931</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>46100</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         <v>46104</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>45191</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>44725</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45226</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>45947</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>45187</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>45952</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>46107</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>44994</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>45951</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>45952</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>45559</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>45957</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32588,7 +32588,7 @@
         <v>45957</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>45957</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>45957</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>44923</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>45957</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32968,7 +32968,7 @@
         <v>45957</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>45957</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33124,7 +33124,7 @@
         <v>45960</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33202,7 +33202,7 @@
         <v>45579</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>45960</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33358,7 +33358,7 @@
         <v>45959</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>45960</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>45964</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33582,7 +33582,7 @@
         <v>45964</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>46121</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>45964</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>45580</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33884,7 +33884,7 @@
         <v>45225</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>45964</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>45636</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>45574</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>46127</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>45965</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34337,7 +34337,7 @@
         <v>45965</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>45965</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>45965</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>45967</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>45967</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45925</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>45971</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>45971</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45972</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45972</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>45225</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>45461</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>45974</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45973</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>46126</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>46126</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>45973</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>46127</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>45974</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>46128</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>45519</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>45817</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>46132</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45818</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45762</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>45740</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>45204</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>45978</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44981</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45673</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>46132</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>45978</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>46128</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45980</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45980</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>46133</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>46134</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>45979</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37191,7 +37191,7 @@
         <v>45728</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>45636</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>45769</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37410,7 +37410,7 @@
         <v>45659</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37483,7 +37483,7 @@
         <v>45981</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37556,7 +37556,7 @@
         <v>45712</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>45642</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37702,7 +37702,7 @@
         <v>45566</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37775,7 +37775,7 @@
         <v>45638</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37848,7 +37848,7 @@
         <v>45987</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37921,7 +37921,7 @@
         <v>45034</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37994,7 +37994,7 @@
         <v>45034</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38067,7 +38067,7 @@
         <v>45629</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38140,7 +38140,7 @@
         <v>46135</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>45987</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38291,7 +38291,7 @@
         <v>46136</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>45992</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>45639</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38510,7 +38510,7 @@
         <v>45992</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45989</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45727</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38734,7 +38734,7 @@
         <v>45818</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>45989</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>45993</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>45993</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39036,7 +39036,7 @@
         <v>45883</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>45721</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>45993</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39260,7 +39260,7 @@
         <v>45875</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>45831</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
         <v>45999</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>44508</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39552,7 +39552,7 @@
         <v>45749</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39625,7 +39625,7 @@
         <v>45747</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39698,7 +39698,7 @@
         <v>45243</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>46001</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>45665</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>46002</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>46001</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40068,7 +40068,7 @@
         <v>45153</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>45818</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>46002</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>46140</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45089</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>45448</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>45219</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>46006</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45162</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>46006</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40803,7 +40803,7 @@
         <v>46003</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>45820</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>46003</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
         <v>44978</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41100,7 +41100,7 @@
         <v>46008</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>45600</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45824</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
         <v>45237</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
         <v>44697</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>45763</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>46007</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
         <v>46008</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>45749</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>46010</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>46031</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>46010</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>45168</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45566</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>46009</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>45684</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42298,7 +42298,7 @@
         <v>46010</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42371,7 +42371,7 @@
         <v>45824</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42444,7 +42444,7 @@
         <v>45821</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42522,7 +42522,7 @@
         <v>45336</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>46133</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42668,7 +42668,7 @@
         <v>45821</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>45406</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45902</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42897,7 +42897,7 @@
         <v>45821</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45757</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43048,7 +43048,7 @@
         <v>45672</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>45824</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45119</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>45509</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45609</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>45792</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>45223</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43569,7 +43569,7 @@
         <v>45078</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43647,7 +43647,7 @@
         <v>44789</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45027</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43793,7 +43793,7 @@
         <v>45749</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43871,7 +43871,7 @@
         <v>45244</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         <v>45654</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44017,7 +44017,7 @@
         <v>46142</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>45485</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44173,7 +44173,7 @@
         <v>45470</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44251,7 +44251,7 @@
         <v>45510</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44329,7 +44329,7 @@
         <v>45266</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44402,7 +44402,7 @@
         <v>45071</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44480,7 +44480,7 @@
         <v>45827</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44553,7 +44553,7 @@
         <v>45761</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44631,7 +44631,7 @@
         <v>45841</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>45769</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
         <v>45439</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44860,7 +44860,7 @@
         <v>46146</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>44881</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>45832</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>46148</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45167,7 +45167,7 @@
         <v>45817</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45245,7 +45245,7 @@
         <v>45832</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>46149</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>45831</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45479,7 +45479,7 @@
         <v>45831</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>46149</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45635,7 +45635,7 @@
         <v>45833</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45713,7 +45713,7 @@
         <v>45769</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>46153</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45859,7 +45859,7 @@
         <v>45077</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45037</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46005,7 +46005,7 @@
         <v>45614</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46078,7 +46078,7 @@
         <v>45833</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>45874</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46229,7 +46229,7 @@
         <v>45835</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46302,7 +46302,7 @@
         <v>45838</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
         <v>45838</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46453,7 +46453,7 @@
         <v>44791</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>45301</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>45714</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>45757</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>46160</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46828,7 +46828,7 @@
         <v>44837</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46906,7 +46906,7 @@
         <v>46160</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46984,7 +46984,7 @@
         <v>45106</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47062,7 +47062,7 @@
         <v>46160</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45840</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>45840</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47291,7 +47291,7 @@
         <v>45839</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47364,7 +47364,7 @@
         <v>45839</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47437,7 +47437,7 @@
         <v>45749</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45128</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47588,7 +47588,7 @@
         <v>45491</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47661,7 +47661,7 @@
         <v>45841</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47739,7 +47739,7 @@
         <v>45841</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47812,7 +47812,7 @@
         <v>45842</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47885,7 +47885,7 @@
         <v>45841</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>44540</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>45841</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>44903</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48187,7 +48187,7 @@
         <v>45841</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45357</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>45846</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48411,7 +48411,7 @@
         <v>45118</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>45756</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48562,7 +48562,7 @@
         <v>45194</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48635,7 +48635,7 @@
         <v>45672</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>45849</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>45849</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45849</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45853</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49005,7 +49005,7 @@
         <v>45855</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49083,7 +49083,7 @@
         <v>45855</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45271</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49229,7 +49229,7 @@
         <v>45462</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49302,7 +49302,7 @@
         <v>45530</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49375,7 +49375,7 @@
         <v>46174</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49448,7 +49448,7 @@
         <v>45694</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49521,7 +49521,7 @@
         <v>45608</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49594,7 +49594,7 @@
         <v>45539</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>46177</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49750,7 +49750,7 @@
         <v>44938</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49823,7 +49823,7 @@
         <v>45149</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49901,7 +49901,7 @@
         <v>45867</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49974,7 +49974,7 @@
         <v>45236</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>44523</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50125,7 +50125,7 @@
         <v>45229</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50203,7 +50203,7 @@
         <v>45428</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50276,7 +50276,7 @@
         <v>45079</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>46189</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>46189</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50505,7 +50505,7 @@
         <v>46029</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>44599</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>45355</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45355</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>45548</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50875,7 +50875,7 @@
         <v>45621</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50948,7 +50948,7 @@
         <v>45517</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45560</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51099,7 +51099,7 @@
         <v>45204</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51177,7 +51177,7 @@
         <v>45483</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51250,7 +51250,7 @@
         <v>45036</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51323,7 +51323,7 @@
         <v>45880</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51396,7 +51396,7 @@
         <v>45880</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51469,7 +51469,7 @@
         <v>45541</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45880</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45054</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>46202</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51771,7 +51771,7 @@
         <v>45713</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51844,7 +51844,7 @@
         <v>45645</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51917,7 +51917,7 @@
         <v>45097</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45642</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52063,7 +52063,7 @@
         <v>45597</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52136,7 +52136,7 @@
         <v>46205</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45072</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>45762</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52360,7 +52360,7 @@
         <v>46204</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52433,7 +52433,7 @@
         <v>45203</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52506,7 +52506,7 @@
         <v>45121</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>45677</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52657,7 +52657,7 @@
         <v>45072</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52730,7 +52730,7 @@
         <v>45197</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52803,7 +52803,7 @@
         <v>45201</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52876,7 +52876,7 @@
         <v>45624</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45714</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         <v>45236</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53100,7 +53100,7 @@
         <v>45093</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>44804</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53246,7 +53246,7 @@
         <v>45204</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53324,7 +53324,7 @@
         <v>46211</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53402,7 +53402,7 @@
         <v>45231</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53475,7 +53475,7 @@
         <v>46211</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53553,7 +53553,7 @@
         <v>45629</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53626,7 +53626,7 @@
         <v>45775</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53699,7 +53699,7 @@
         <v>45198</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>45211</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53850,7 +53850,7 @@
         <v>44677</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53928,7 +53928,7 @@
         <v>45621</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54001,7 +54001,7 @@
         <v>45622</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54079,7 +54079,7 @@
         <v>45642</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45642</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54225,7 +54225,7 @@
         <v>45191</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54298,7 +54298,7 @@
         <v>45177</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54371,7 +54371,7 @@
         <v>46259</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54449,7 +54449,7 @@
         <v>45246</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54522,7 +54522,7 @@
         <v>45245</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54595,7 +54595,7 @@
         <v>45175</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54668,7 +54668,7 @@
         <v>45245</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54741,7 +54741,7 @@
         <v>45188</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54814,7 +54814,7 @@
         <v>45188</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45175</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54960,7 +54960,7 @@
         <v>45225</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55033,7 +55033,7 @@
         <v>45252</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55106,7 +55106,7 @@
         <v>44739</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55179,7 +55179,7 @@
         <v>45645</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55252,7 +55252,7 @@
         <v>45257</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55325,7 +55325,7 @@
         <v>44782</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55403,7 +55403,7 @@
         <v>45727</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55476,7 +55476,7 @@
         <v>45252</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55549,7 +55549,7 @@
         <v>45713</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55622,7 +55622,7 @@
         <v>45322</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>44886</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>46267</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         <v>44881</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55914,7 +55914,7 @@
         <v>45237</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55987,7 +55987,7 @@
         <v>45237</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>45257</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56133,7 +56133,7 @@
         <v>46272</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56211,7 +56211,7 @@
         <v>46272</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56289,7 +56289,7 @@
         <v>46272</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56367,7 +56367,7 @@
         <v>46226</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56440,7 +56440,7 @@
         <v>45769</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56518,7 +56518,7 @@
         <v>46272</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56596,7 +56596,7 @@
         <v>45355</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56669,7 +56669,7 @@
         <v>44908</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>46231</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         <v>46274</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>44950</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56976,7 +56976,7 @@
         <v>44950</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57049,7 +57049,7 @@
         <v>45272</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57122,7 +57122,7 @@
         <v>46274</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57195,7 +57195,7 @@
         <v>45355</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57273,7 +57273,7 @@
         <v>46274</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57346,7 +57346,7 @@
         <v>46275</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57424,7 +57424,7 @@
         <v>46275</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57502,7 +57502,7 @@
         <v>45541</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57580,7 +57580,7 @@
         <v>46280</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>44495</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57731,7 +57731,7 @@
         <v>45301</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45303</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57877,7 +57877,7 @@
         <v>46275</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57955,7 +57955,7 @@
         <v>44938</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>46239</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58101,7 +58101,7 @@
         <v>45567</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58174,7 +58174,7 @@
         <v>46282</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58252,7 +58252,7 @@
         <v>45547</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58325,7 +58325,7 @@
         <v>45053</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58398,7 +58398,7 @@
         <v>46239</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58471,7 +58471,7 @@
         <v>46283</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58549,7 +58549,7 @@
         <v>44860</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58622,7 +58622,7 @@
         <v>44900</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>45623</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58773,7 +58773,7 @@
         <v>45453</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58846,7 +58846,7 @@
         <v>44897</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58919,7 +58919,7 @@
         <v>44740</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>44589</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59075,7 +59075,7 @@
         <v>46287</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59148,7 +59148,7 @@
         <v>44957</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59221,7 +59221,7 @@
         <v>44832</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59294,7 +59294,7 @@
         <v>46287</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59372,7 +59372,7 @@
         <v>46245</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59445,7 +59445,7 @@
         <v>46288</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59523,7 +59523,7 @@
         <v>44741</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59601,7 +59601,7 @@
         <v>45420</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59674,7 +59674,7 @@
         <v>44979</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59747,7 +59747,7 @@
         <v>46244</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59820,7 +59820,7 @@
         <v>46287</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59898,7 +59898,7 @@
         <v>46245</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>46247</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60044,7 +60044,7 @@
         <v>44637</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60122,7 +60122,7 @@
         <v>45929</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60195,7 +60195,7 @@
         <v>44623</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60273,7 +60273,7 @@
         <v>45162</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60351,7 +60351,7 @@
         <v>44946</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60424,7 +60424,7 @@
         <v>46290</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60502,7 +60502,7 @@
         <v>45720</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60575,7 +60575,7 @@
         <v>45674</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60648,7 +60648,7 @@
         <v>46246</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60721,7 +60721,7 @@
         <v>45450</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60794,7 +60794,7 @@
         <v>45204</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60872,7 +60872,7 @@
         <v>46289</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60950,7 +60950,7 @@
         <v>44623</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61023,7 +61023,7 @@
         <v>45226</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61096,7 +61096,7 @@
         <v>45041</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61174,7 +61174,7 @@
         <v>45477</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61247,7 +61247,7 @@
         <v>45106</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61320,7 +61320,7 @@
         <v>44511</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61393,7 +61393,7 @@
         <v>44923</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61466,7 +61466,7 @@
         <v>44963</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61539,7 +61539,7 @@
         <v>45007</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61612,7 +61612,7 @@
         <v>45592</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61685,7 +61685,7 @@
         <v>44643</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61763,7 +61763,7 @@
         <v>44978</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61836,7 +61836,7 @@
         <v>44911</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61909,7 +61909,7 @@
         <v>45231</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61982,7 +61982,7 @@
         <v>45538</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62055,7 +62055,7 @@
         <v>45597</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62128,7 +62128,7 @@
         <v>44938</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62201,7 +62201,7 @@
         <v>44501</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62279,7 +62279,7 @@
         <v>45072</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62357,7 +62357,7 @@
         <v>45293</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62430,7 +62430,7 @@
         <v>44894</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62508,7 +62508,7 @@
         <v>45761</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62586,7 +62586,7 @@
         <v>45202</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62659,7 +62659,7 @@
         <v>45301</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62732,7 +62732,7 @@
         <v>45574</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62810,7 +62810,7 @@
         <v>45644</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62883,7 +62883,7 @@
         <v>45670</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62956,7 +62956,7 @@
         <v>45541</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         <v>45460</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63112,7 +63112,7 @@
         <v>45677</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63185,7 +63185,7 @@
         <v>44881</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63258,7 +63258,7 @@
         <v>45257</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63336,7 +63336,7 @@
         <v>45665</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63409,7 +63409,7 @@
         <v>45238</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63482,7 +63482,7 @@
         <v>45560</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63555,7 +63555,7 @@
         <v>45152</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63633,7 +63633,7 @@
         <v>45090</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63706,7 +63706,7 @@
         <v>45072</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63784,7 +63784,7 @@
         <v>44515</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63862,7 +63862,7 @@
         <v>45062</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63935,7 +63935,7 @@
         <v>44931</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64008,7 +64008,7 @@
         <v>45339</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64081,7 +64081,7 @@
         <v>45407</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64154,7 +64154,7 @@
         <v>44888</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64227,7 +64227,7 @@
         <v>45163</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64305,7 +64305,7 @@
         <v>45643</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64378,7 +64378,7 @@
         <v>45238</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64451,7 +64451,7 @@
         <v>45430</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64524,7 +64524,7 @@
         <v>45177</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64597,7 +64597,7 @@
         <v>45439</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64675,7 +64675,7 @@
         <v>45692</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64748,7 +64748,7 @@
         <v>45204</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64826,7 +64826,7 @@
         <v>45624</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64899,7 +64899,7 @@
         <v>45624</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64972,7 +64972,7 @@
         <v>45294</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65045,7 +65045,7 @@
         <v>45672</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65118,7 +65118,7 @@
         <v>45432</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65191,7 +65191,7 @@
         <v>45726</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65264,7 +65264,7 @@
         <v>45215</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65337,7 +65337,7 @@
         <v>45525</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65410,7 +65410,7 @@
         <v>45482</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65488,7 +65488,7 @@
         <v>45455</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65566,7 +65566,7 @@
         <v>44641</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65644,7 +65644,7 @@
         <v>44911</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65717,7 +65717,7 @@
         <v>45399</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65790,7 +65790,7 @@
         <v>45054</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65868,7 +65868,7 @@
         <v>45789</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65946,7 +65946,7 @@
         <v>45195</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66019,7 +66019,7 @@
         <v>44722</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66097,7 +66097,7 @@
         <v>44684</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66175,7 +66175,7 @@
         <v>45371</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66248,7 +66248,7 @@
         <v>45699</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66326,7 +66326,7 @@
         <v>45756</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66404,7 +66404,7 @@
         <v>45778</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66477,7 +66477,7 @@
         <v>45342</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66550,7 +66550,7 @@
         <v>46089</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66628,7 +66628,7 @@
         <v>46072</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66706,7 +66706,7 @@
         <v>46171</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>

--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -601,7 +601,7 @@
         <v>46057</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>46070</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44722</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46205</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46033</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>46184</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45092</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>46181</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>46033</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45016</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>44637</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45812</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>46140</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>46178</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>45785</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>46205</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>46157</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>44796</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45775</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45917</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>46069</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>46191</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45897</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>46055</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45469</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45016</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>45533</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>46196</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>46178</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>46178</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         <v>46089</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>46104</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>46033</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>46196</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>45932</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>46055</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>45695</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>45510</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>45016</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>44610</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>45938</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>46055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>44090</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>44722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45099</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>46055</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>45775</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45839</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>46178</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>46029</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>46190</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>45583</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44722</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>45799</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>46055</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>46092</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>45971</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>45903</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>46093</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44796</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>45443</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>45181</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>46258</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>45754</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>45713</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>44589</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>45315</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>45903</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>44704</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>45895</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>45925</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>44936</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>45995</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>45831</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>45831</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>44501</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>45714</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>46164</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>44641</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>44741</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>45233</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44722</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>44721</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>45119</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>44523</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>46029</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>45538</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>44910</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>45971</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>45461</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>45824</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>45705</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>44944</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>45631</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45247</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>45187</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>46266</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>45188</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>46274</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>45246</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45053</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>46287</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>46290</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>45623</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>45713</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>45461</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>44867</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>45053</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>44637</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>45411</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44512</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>44489</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>44508</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>44537</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>44511</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>44712</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44852</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>44733</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>44811</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>44756</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>44887</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>44696</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>44616</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>44503</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>44588</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>44809</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44602</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>44533</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>44529</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>44501</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>44613</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>44540</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>44701</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>44469</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>44721</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>44557</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>44547</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>44802</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>44512</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44886</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>44721</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44739</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>44743</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>44743</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>44616</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>44811</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44839</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>44544</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44749</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44858</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44501</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>44600</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>44603</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>44743</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>44811</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>44811</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>45089</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45709</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>44725</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45187</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>44862</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45531</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45215</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>44795</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45541</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>45252</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45335</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45720</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45391</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>45321</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>44928</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45267</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>44903</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45446</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>44914</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44897</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44546</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>45271</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>45883</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>46024</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45712</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>45188</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45229</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45020</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>45294</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>46030</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>45540</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45488</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>45503</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>45483</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>45036</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>44923</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45797</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>45797</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>45797</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>45797</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
         <v>46029</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>46031</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>46034</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20580,7 +20580,7 @@
         <v>46034</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>46034</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>46034</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         <v>45434</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>44928</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>46035</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21028,7 +21028,7 @@
         <v>46036</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>46036</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>46036</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>45799</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>46036</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>45483</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>46036</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>46036</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>46036</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>45890</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>45890</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>46036</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>45511</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45891</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
         <v>45800</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>45891</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45892</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45195</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45583</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>45891</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>45891</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>45894</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>45982</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>44896</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45895</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>46044</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>45775</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>44907</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45898</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>46044</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>45898</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>45488</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>45540</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>46034</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>45902</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>45902</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45902</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>45902</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45901</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>45456</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>45904</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>45491</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>45491</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>45904</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>45875</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45908</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>45481</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>45800</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>45476</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
         <v>45910</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>45910</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>46055</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>45912</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>45911</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>45912</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>45525</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25246,7 +25246,7 @@
         <v>45804</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>45747</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45916</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>45915</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45916</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>45916</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>45608</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>46059</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>46059</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>46059</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>46059</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45525</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>45713</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>45547</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
         <v>44928</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>46064</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>46064</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>45919</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>45804</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>45919</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26721,7 +26721,7 @@
         <v>45919</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26794,7 +26794,7 @@
         <v>45561</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>46066</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>45225</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>46070</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45636</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45804</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>45747</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>45805</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         <v>45041</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>45925</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>45926</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>45805</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>46073</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>46073</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>46073</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>45926</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45534</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45930</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45931</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>46085</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>45807</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>45632</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>45322</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45807</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45449</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>45810</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45931</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45442</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>45931</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>46073</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45575</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44916</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45933</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45933</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>45936</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45429</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>45936</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45936</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>45937</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45937</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29774,7 +29774,7 @@
         <v>45937</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>46093</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29925,7 +29925,7 @@
         <v>45937</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>44512</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45679</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30154,7 +30154,7 @@
         <v>46092</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>46093</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>45937</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30373,7 +30373,7 @@
         <v>45244</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>45940</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>46093</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30592,7 +30592,7 @@
         <v>44923</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>44923</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>45874</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>45757</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>46092</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30957,7 +30957,7 @@
         <v>45939</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>45930</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31108,7 +31108,7 @@
         <v>45646</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>45646</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>46098</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44903</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45007</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>45931</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>46100</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         <v>46104</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>45191</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>44725</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45226</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>45947</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>45187</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>45952</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>46107</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>44994</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>45951</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>45952</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>45559</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>45957</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32588,7 +32588,7 @@
         <v>45957</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>45957</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>45957</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>44923</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>45957</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32968,7 +32968,7 @@
         <v>45957</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>45957</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33124,7 +33124,7 @@
         <v>45960</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33202,7 +33202,7 @@
         <v>45579</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>45960</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33358,7 +33358,7 @@
         <v>45959</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>45960</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>45964</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33582,7 +33582,7 @@
         <v>45964</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>46121</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>45964</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>45580</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33884,7 +33884,7 @@
         <v>45225</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>45964</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>45636</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>45574</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>46127</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>45965</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34337,7 +34337,7 @@
         <v>45965</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>45965</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>45965</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>45967</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>45967</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45925</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>45971</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>45971</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45972</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45972</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>45225</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>45461</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>45974</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45973</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>46126</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>46126</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>45973</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>46127</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>45974</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>46128</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>45519</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>45817</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>46132</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45818</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45762</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>45740</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>45204</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>45978</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44981</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45673</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>46132</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>45978</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>46128</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45980</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45980</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>46133</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>46134</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>45979</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37191,7 +37191,7 @@
         <v>45728</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>45636</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>45769</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37410,7 +37410,7 @@
         <v>45659</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37483,7 +37483,7 @@
         <v>45981</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37556,7 +37556,7 @@
         <v>45712</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>45642</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37702,7 +37702,7 @@
         <v>45566</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37775,7 +37775,7 @@
         <v>45638</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37848,7 +37848,7 @@
         <v>45987</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37921,7 +37921,7 @@
         <v>45034</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37994,7 +37994,7 @@
         <v>45034</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38067,7 +38067,7 @@
         <v>45629</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38140,7 +38140,7 @@
         <v>46135</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>45987</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38291,7 +38291,7 @@
         <v>46136</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>45992</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>45639</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38510,7 +38510,7 @@
         <v>45992</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45989</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45727</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38734,7 +38734,7 @@
         <v>45818</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>45989</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>45993</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>45993</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39036,7 +39036,7 @@
         <v>45883</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>45721</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>45993</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39260,7 +39260,7 @@
         <v>45875</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>45831</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
         <v>45999</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>44508</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39552,7 +39552,7 @@
         <v>45749</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39625,7 +39625,7 @@
         <v>45747</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39698,7 +39698,7 @@
         <v>45243</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>46001</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>45665</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>46002</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>46001</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40068,7 +40068,7 @@
         <v>45153</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>45818</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>46002</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>46140</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45089</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>45448</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>45219</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>46006</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45162</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>46006</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40803,7 +40803,7 @@
         <v>46003</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>45820</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>46003</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
         <v>44978</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41100,7 +41100,7 @@
         <v>46008</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>45600</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45824</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
         <v>45237</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
         <v>44697</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>45763</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>46007</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
         <v>46008</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>45749</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>46010</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>46031</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>46010</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>45168</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45566</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>46009</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>45684</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42298,7 +42298,7 @@
         <v>46010</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42371,7 +42371,7 @@
         <v>45824</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42444,7 +42444,7 @@
         <v>45821</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42522,7 +42522,7 @@
         <v>45336</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>46133</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42668,7 +42668,7 @@
         <v>45821</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>45406</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45902</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42897,7 +42897,7 @@
         <v>45821</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45757</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43048,7 +43048,7 @@
         <v>45672</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>45824</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45119</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>45509</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45609</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>45792</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>45223</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43569,7 +43569,7 @@
         <v>45078</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43647,7 +43647,7 @@
         <v>44789</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45027</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43793,7 +43793,7 @@
         <v>45749</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43871,7 +43871,7 @@
         <v>45244</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         <v>45654</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44017,7 +44017,7 @@
         <v>46142</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>45485</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44173,7 +44173,7 @@
         <v>45470</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44251,7 +44251,7 @@
         <v>45510</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44329,7 +44329,7 @@
         <v>45266</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44402,7 +44402,7 @@
         <v>45071</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44480,7 +44480,7 @@
         <v>45827</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44553,7 +44553,7 @@
         <v>45761</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44631,7 +44631,7 @@
         <v>45841</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>45769</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
         <v>45439</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44860,7 +44860,7 @@
         <v>46146</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>44881</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>45832</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>46148</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45167,7 +45167,7 @@
         <v>45817</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45245,7 +45245,7 @@
         <v>45832</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>46149</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>45831</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45479,7 +45479,7 @@
         <v>45831</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>46149</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45635,7 +45635,7 @@
         <v>45833</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45713,7 +45713,7 @@
         <v>45769</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>46153</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45859,7 +45859,7 @@
         <v>45077</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45037</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46005,7 +46005,7 @@
         <v>45614</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46078,7 +46078,7 @@
         <v>45833</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>45874</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46229,7 +46229,7 @@
         <v>45835</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46302,7 +46302,7 @@
         <v>45838</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
         <v>45838</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46453,7 +46453,7 @@
         <v>44791</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>45301</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>45714</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>45757</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>46160</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46828,7 +46828,7 @@
         <v>44837</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46906,7 +46906,7 @@
         <v>46160</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46984,7 +46984,7 @@
         <v>45106</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47062,7 +47062,7 @@
         <v>46160</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45840</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>45840</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47291,7 +47291,7 @@
         <v>45839</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47364,7 +47364,7 @@
         <v>45839</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47437,7 +47437,7 @@
         <v>45749</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45128</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47588,7 +47588,7 @@
         <v>45491</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47661,7 +47661,7 @@
         <v>45841</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47739,7 +47739,7 @@
         <v>45841</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47812,7 +47812,7 @@
         <v>45842</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47885,7 +47885,7 @@
         <v>45841</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>44540</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>45841</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>44903</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48187,7 +48187,7 @@
         <v>45841</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45357</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>45846</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48411,7 +48411,7 @@
         <v>45118</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>45756</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48562,7 +48562,7 @@
         <v>45194</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48635,7 +48635,7 @@
         <v>45672</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>45849</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>45849</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45849</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45853</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49005,7 +49005,7 @@
         <v>45855</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49083,7 +49083,7 @@
         <v>45855</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45271</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49229,7 +49229,7 @@
         <v>45462</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49302,7 +49302,7 @@
         <v>45530</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49375,7 +49375,7 @@
         <v>46174</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49448,7 +49448,7 @@
         <v>45694</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49521,7 +49521,7 @@
         <v>45608</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49594,7 +49594,7 @@
         <v>45539</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>46177</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49750,7 +49750,7 @@
         <v>44938</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49823,7 +49823,7 @@
         <v>45149</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49901,7 +49901,7 @@
         <v>45867</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49974,7 +49974,7 @@
         <v>45236</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>44523</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50125,7 +50125,7 @@
         <v>45229</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50203,7 +50203,7 @@
         <v>45428</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50276,7 +50276,7 @@
         <v>45079</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>46189</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>46189</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50505,7 +50505,7 @@
         <v>46029</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>44599</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>45355</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45355</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>45548</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50875,7 +50875,7 @@
         <v>45621</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50948,7 +50948,7 @@
         <v>45517</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45560</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51099,7 +51099,7 @@
         <v>45204</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51177,7 +51177,7 @@
         <v>45483</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51250,7 +51250,7 @@
         <v>45036</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51323,7 +51323,7 @@
         <v>45880</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51396,7 +51396,7 @@
         <v>45880</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51469,7 +51469,7 @@
         <v>45541</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45880</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45054</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>46202</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51771,7 +51771,7 @@
         <v>45713</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51844,7 +51844,7 @@
         <v>45645</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51917,7 +51917,7 @@
         <v>45097</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45642</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52063,7 +52063,7 @@
         <v>45597</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52136,7 +52136,7 @@
         <v>46205</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45072</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>45762</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52360,7 +52360,7 @@
         <v>46204</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52433,7 +52433,7 @@
         <v>45203</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52506,7 +52506,7 @@
         <v>45121</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>45677</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52657,7 +52657,7 @@
         <v>45072</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52730,7 +52730,7 @@
         <v>45197</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52803,7 +52803,7 @@
         <v>45201</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52876,7 +52876,7 @@
         <v>45624</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45714</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         <v>45236</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53100,7 +53100,7 @@
         <v>45093</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>44804</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53246,7 +53246,7 @@
         <v>45204</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53324,7 +53324,7 @@
         <v>46211</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53402,7 +53402,7 @@
         <v>45231</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53475,7 +53475,7 @@
         <v>46211</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53553,7 +53553,7 @@
         <v>45629</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53626,7 +53626,7 @@
         <v>45775</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53699,7 +53699,7 @@
         <v>45198</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>45211</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53850,7 +53850,7 @@
         <v>44677</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53928,7 +53928,7 @@
         <v>45621</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54001,7 +54001,7 @@
         <v>45622</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54079,7 +54079,7 @@
         <v>45642</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45642</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54225,7 +54225,7 @@
         <v>45191</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54298,7 +54298,7 @@
         <v>45177</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54371,7 +54371,7 @@
         <v>46259</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54449,7 +54449,7 @@
         <v>45246</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54522,7 +54522,7 @@
         <v>45245</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54595,7 +54595,7 @@
         <v>45175</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54668,7 +54668,7 @@
         <v>45245</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54741,7 +54741,7 @@
         <v>45188</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54814,7 +54814,7 @@
         <v>45188</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45175</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54960,7 +54960,7 @@
         <v>45225</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55033,7 +55033,7 @@
         <v>45252</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55106,7 +55106,7 @@
         <v>44739</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55179,7 +55179,7 @@
         <v>45645</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55252,7 +55252,7 @@
         <v>45257</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55325,7 +55325,7 @@
         <v>44782</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55403,7 +55403,7 @@
         <v>45727</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55476,7 +55476,7 @@
         <v>45252</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55549,7 +55549,7 @@
         <v>45713</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55622,7 +55622,7 @@
         <v>45322</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>44886</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>46267</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         <v>44881</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55914,7 +55914,7 @@
         <v>45237</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55987,7 +55987,7 @@
         <v>45237</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>45257</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56133,7 +56133,7 @@
         <v>46272</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56211,7 +56211,7 @@
         <v>46272</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56289,7 +56289,7 @@
         <v>46272</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56367,7 +56367,7 @@
         <v>46226</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56440,7 +56440,7 @@
         <v>45769</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56518,7 +56518,7 @@
         <v>46272</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56596,7 +56596,7 @@
         <v>45355</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56669,7 +56669,7 @@
         <v>44908</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>46231</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         <v>46274</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>44950</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56976,7 +56976,7 @@
         <v>44950</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57049,7 +57049,7 @@
         <v>45272</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57122,7 +57122,7 @@
         <v>46274</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57195,7 +57195,7 @@
         <v>45355</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57273,7 +57273,7 @@
         <v>46274</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57346,7 +57346,7 @@
         <v>46275</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57424,7 +57424,7 @@
         <v>46275</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57502,7 +57502,7 @@
         <v>45541</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57580,7 +57580,7 @@
         <v>46280</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>44495</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57731,7 +57731,7 @@
         <v>45301</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45303</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57877,7 +57877,7 @@
         <v>46275</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57955,7 +57955,7 @@
         <v>44938</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>46239</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58101,7 +58101,7 @@
         <v>45567</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58174,7 +58174,7 @@
         <v>46282</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58252,7 +58252,7 @@
         <v>45547</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58325,7 +58325,7 @@
         <v>45053</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58398,7 +58398,7 @@
         <v>46239</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58471,7 +58471,7 @@
         <v>46283</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58549,7 +58549,7 @@
         <v>44860</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58622,7 +58622,7 @@
         <v>44900</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>45623</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58773,7 +58773,7 @@
         <v>45453</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58846,7 +58846,7 @@
         <v>44897</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58919,7 +58919,7 @@
         <v>44740</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>44589</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59075,7 +59075,7 @@
         <v>46287</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59148,7 +59148,7 @@
         <v>44957</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59221,7 +59221,7 @@
         <v>44832</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59294,7 +59294,7 @@
         <v>46287</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59372,7 +59372,7 @@
         <v>46245</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59445,7 +59445,7 @@
         <v>46288</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59523,7 +59523,7 @@
         <v>44741</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59601,7 +59601,7 @@
         <v>45420</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59674,7 +59674,7 @@
         <v>44979</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59747,7 +59747,7 @@
         <v>46244</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59820,7 +59820,7 @@
         <v>46287</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59898,7 +59898,7 @@
         <v>46245</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>46247</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60044,7 +60044,7 @@
         <v>44637</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60122,7 +60122,7 @@
         <v>45929</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60195,7 +60195,7 @@
         <v>44623</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60273,7 +60273,7 @@
         <v>45162</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60351,7 +60351,7 @@
         <v>44946</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60424,7 +60424,7 @@
         <v>46290</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60502,7 +60502,7 @@
         <v>45720</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60575,7 +60575,7 @@
         <v>45674</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60648,7 +60648,7 @@
         <v>46246</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60721,7 +60721,7 @@
         <v>45450</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60794,7 +60794,7 @@
         <v>45204</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60872,7 +60872,7 @@
         <v>46289</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60950,7 +60950,7 @@
         <v>44623</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61023,7 +61023,7 @@
         <v>45226</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61096,7 +61096,7 @@
         <v>45041</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61174,7 +61174,7 @@
         <v>45477</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61247,7 +61247,7 @@
         <v>45106</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61320,7 +61320,7 @@
         <v>44511</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61393,7 +61393,7 @@
         <v>44923</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61466,7 +61466,7 @@
         <v>44963</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61539,7 +61539,7 @@
         <v>45007</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61612,7 +61612,7 @@
         <v>45592</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61685,7 +61685,7 @@
         <v>44643</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61763,7 +61763,7 @@
         <v>44978</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61836,7 +61836,7 @@
         <v>44911</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61909,7 +61909,7 @@
         <v>45231</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61982,7 +61982,7 @@
         <v>45538</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62055,7 +62055,7 @@
         <v>45597</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62128,7 +62128,7 @@
         <v>44938</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62201,7 +62201,7 @@
         <v>44501</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62279,7 +62279,7 @@
         <v>45072</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62357,7 +62357,7 @@
         <v>45293</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62430,7 +62430,7 @@
         <v>44894</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62508,7 +62508,7 @@
         <v>45761</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62586,7 +62586,7 @@
         <v>45202</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62659,7 +62659,7 @@
         <v>45301</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62732,7 +62732,7 @@
         <v>45574</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62810,7 +62810,7 @@
         <v>45644</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62883,7 +62883,7 @@
         <v>45670</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62956,7 +62956,7 @@
         <v>45541</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         <v>45460</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63112,7 +63112,7 @@
         <v>45677</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63185,7 +63185,7 @@
         <v>44881</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63258,7 +63258,7 @@
         <v>45257</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63336,7 +63336,7 @@
         <v>45665</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63409,7 +63409,7 @@
         <v>45238</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63482,7 +63482,7 @@
         <v>45560</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63555,7 +63555,7 @@
         <v>45152</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63633,7 +63633,7 @@
         <v>45090</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63706,7 +63706,7 @@
         <v>45072</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63784,7 +63784,7 @@
         <v>44515</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63862,7 +63862,7 @@
         <v>45062</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63935,7 +63935,7 @@
         <v>44931</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64008,7 +64008,7 @@
         <v>45339</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64081,7 +64081,7 @@
         <v>45407</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64154,7 +64154,7 @@
         <v>44888</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64227,7 +64227,7 @@
         <v>45163</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64305,7 +64305,7 @@
         <v>45643</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64378,7 +64378,7 @@
         <v>45238</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64451,7 +64451,7 @@
         <v>45430</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64524,7 +64524,7 @@
         <v>45177</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64597,7 +64597,7 @@
         <v>45439</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64675,7 +64675,7 @@
         <v>45692</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64748,7 +64748,7 @@
         <v>45204</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64826,7 +64826,7 @@
         <v>45624</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64899,7 +64899,7 @@
         <v>45624</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64972,7 +64972,7 @@
         <v>45294</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65045,7 +65045,7 @@
         <v>45672</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65118,7 +65118,7 @@
         <v>45432</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65191,7 +65191,7 @@
         <v>45726</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65264,7 +65264,7 @@
         <v>45215</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65337,7 +65337,7 @@
         <v>45525</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65410,7 +65410,7 @@
         <v>45482</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65488,7 +65488,7 @@
         <v>45455</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65566,7 +65566,7 @@
         <v>44641</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65644,7 +65644,7 @@
         <v>44911</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65717,7 +65717,7 @@
         <v>45399</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65790,7 +65790,7 @@
         <v>45054</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65868,7 +65868,7 @@
         <v>45789</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65946,7 +65946,7 @@
         <v>45195</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66019,7 +66019,7 @@
         <v>44722</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66097,7 +66097,7 @@
         <v>44684</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66175,7 +66175,7 @@
         <v>45371</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66248,7 +66248,7 @@
         <v>45699</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66326,7 +66326,7 @@
         <v>45756</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66404,7 +66404,7 @@
         <v>45778</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66477,7 +66477,7 @@
         <v>45342</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66550,7 +66550,7 @@
         <v>46089</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66628,7 +66628,7 @@
         <v>46072</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66706,7 +66706,7 @@
         <v>46171</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>

--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -601,7 +601,7 @@
         <v>46057</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>46070</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44722</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46205</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46033</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>46184</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45092</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>46181</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>46033</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45016</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>44637</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45812</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>46140</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>46178</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>45785</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>46205</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>46157</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45775</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45917</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>46069</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>46191</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45897</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>46055</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45469</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45016</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>46089</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>45533</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>46196</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>46178</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>46178</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>46104</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>46033</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>46196</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>45932</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>45510</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>46055</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45695</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>45016</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>44610</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>45938</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>46055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>44090</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>44722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>45775</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>45099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>46055</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>45839</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45583</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>46178</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>46190</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>46029</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44722</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>45799</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         <v>46055</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>46092</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>45971</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>45754</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>45903</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>45443</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>46093</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45181</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44796</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>46258</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>45713</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45315</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         <v>44589</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45903</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>44704</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>45895</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>45925</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>44741</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>45995</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>45831</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>45831</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>44936</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>44501</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>46164</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>45714</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>44641</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>45233</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>44722</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>44721</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>44867</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>44910</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>46029</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>45705</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>45623</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>45461</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>45957</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>45971</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>45119</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>45824</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>44523</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>45246</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>45188</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>45053</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>45187</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>45631</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>46266</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>46274</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>45538</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>46287</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>46290</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>44944</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>45247</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>45713</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>45461</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>45053</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>45411</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>44637</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>44512</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>44489</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>44508</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>44537</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>44511</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44712</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>44852</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>44733</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>44811</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>44756</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>44887</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44696</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>44616</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>44503</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44588</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>44809</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44602</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>44533</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>44529</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>44501</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         <v>44613</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>44540</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>44701</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44721</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44557</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>44547</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         <v>44802</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>44512</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>44886</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>44721</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>44739</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>44743</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>44743</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>44616</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44811</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>44839</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>44544</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>44749</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>44858</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>44501</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>44600</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44603</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44743</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>44811</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>44811</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45632</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>45645</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>45674</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>44978</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45007</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>45713</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>45244</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>45519</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>44515</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>44900</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>45769</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>44599</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>44894</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45252</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>45191</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>46001</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>45644</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>46003</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>46003</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45093</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>45636</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45162</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>46002</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>45225</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>45789</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>46002</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45237</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>46007</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>46006</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>46006</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>44832</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45245</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>46008</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>45747</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>46009</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>46008</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45195</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45677</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45559</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>46010</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>45453</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>46010</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45629</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>46010</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45089</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45891</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>45891</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>45891</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45890</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>45890</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45891</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>46024</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>45892</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45895</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>45727</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45894</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>45761</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>46029</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>45592</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>46030</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44896</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>45202</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>45898</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
         <v>46031</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>45898</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22249,7 +22249,7 @@
         <v>45659</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>46034</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>46034</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>45775</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>45540</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>44928</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>46035</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>45901</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>45071</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>45712</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>46034</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>46034</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23140,7 +23140,7 @@
         <v>44903</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>44739</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>44741</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>45902</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>45902</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>45902</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>45902</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>46036</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>46036</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>45191</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45152</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>46036</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>46036</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>46036</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>46036</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44946</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>46036</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>46036</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>45982</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24552,7 +24552,7 @@
         <v>45904</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>45904</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>45875</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>45231</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>44903</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>45908</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         <v>45488</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>45481</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>45910</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45036</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45229</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>45020</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>45797</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>45910</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>44923</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>45540</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>45911</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45204</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>45797</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>45797</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>45797</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>45915</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>46034</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>46044</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>46044</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>45912</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26505,7 +26505,7 @@
         <v>45912</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>44931</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>45188</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45916</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>45916</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>45916</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>45799</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>44938</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>45530</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>45919</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>45800</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45800</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>45747</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>45805</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>45804</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>45919</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27698,7 +27698,7 @@
         <v>45713</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
         <v>45919</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45804</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>45805</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>45804</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>45747</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>45807</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>45807</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>44804</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>46055</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>45925</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45461</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>45926</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>45926</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>46059</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>46059</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>46059</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>46059</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>45072</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>45930</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45931</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>45931</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>45931</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>46064</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>45933</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45933</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>45238</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>46064</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>45936</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>45936</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>44897</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>45936</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>46066</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>45810</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>45037</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>45428</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>45937</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30444,7 +30444,7 @@
         <v>45541</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>45937</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>44677</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30678,7 +30678,7 @@
         <v>46070</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30751,7 +30751,7 @@
         <v>45937</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>45939</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>45219</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>45937</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>45477</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45937</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>46073</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>46073</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>45930</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>45940</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>46073</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>45121</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>44886</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>44881</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>45677</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>45947</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>45931</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>45322</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>45672</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>45951</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>45229</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>45036</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>45952</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>45952</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>46073</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>45957</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>45957</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45541</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>45957</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45204</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45204</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45642</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45957</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>45957</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>46085</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>45957</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44860</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>45960</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>45960</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>45960</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33771,7 +33771,7 @@
         <v>45959</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         <v>45965</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33917,7 +33917,7 @@
         <v>45714</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33990,7 +33990,7 @@
         <v>46092</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>45964</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>46092</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>45874</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>45964</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>45964</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>46093</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34511,7 +34511,7 @@
         <v>45964</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>45965</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>45203</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>45692</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>46093</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>45541</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45534</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>45967</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45967</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45965</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>46093</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>45965</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>45971</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>46098</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45763</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>45925</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45198</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>45608</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>46100</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35928,7 +35928,7 @@
         <v>45973</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>45971</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>45972</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>45972</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>45973</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>46104</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45974</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>45974</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>45817</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45525</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>45740</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>45978</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>45978</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36907,7 +36907,7 @@
         <v>45257</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36980,7 +36980,7 @@
         <v>45257</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45575</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>45979</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45818</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>44911</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>45980</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>45981</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>45762</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>45818</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>46107</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>45980</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45622</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>45818</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>45749</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>45007</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>45566</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45820</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>45243</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45821</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38387,7 +38387,7 @@
         <v>45821</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>45821</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>45488</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>45547</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>45987</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>45237</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>45237</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45712</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>45987</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45824</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39132,7 +39132,7 @@
         <v>45989</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45989</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39288,7 +39288,7 @@
         <v>45824</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39361,7 +39361,7 @@
         <v>45993</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>45992</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>45992</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>45728</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>46121</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45993</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>45993</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>46126</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>45714</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45225</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>45827</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>46126</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>45999</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>46128</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>46128</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>46127</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>44637</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>46001</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>46127</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         <v>46133</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>46132</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45831</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>45642</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45831</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45211</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>46132</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41314,7 +41314,7 @@
         <v>45833</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>45832</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>45833</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>46135</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
         <v>44994</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41699,7 +41699,7 @@
         <v>45252</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>45832</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41850,7 +41850,7 @@
         <v>45835</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>46134</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>45838</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>45839</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42147,7 +42147,7 @@
         <v>45491</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>45838</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45839</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>44697</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>45840</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42522,7 +42522,7 @@
         <v>45090</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>45841</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42668,7 +42668,7 @@
         <v>45840</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>45841</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45079</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42892,7 +42892,7 @@
         <v>45597</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>45769</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43038,7 +43038,7 @@
         <v>45841</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43116,7 +43116,7 @@
         <v>45841</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>44881</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>45841</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43345,7 +43345,7 @@
         <v>45842</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>45511</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>45757</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>45883</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43637,7 +43637,7 @@
         <v>44511</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45357</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>45757</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45713</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>45609</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44007,7 +44007,7 @@
         <v>46136</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44080,7 +44080,7 @@
         <v>45846</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44153,7 +44153,7 @@
         <v>45849</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44226,7 +44226,7 @@
         <v>45849</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45849</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>45448</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45875</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45831</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>45853</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>45902</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44747,7 +44747,7 @@
         <v>45855</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>45153</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44898,7 +44898,7 @@
         <v>45636</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>45749</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         <v>45855</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45761</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45195,7 +45195,7 @@
         <v>46133</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>46031</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>45294</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>45624</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>45624</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>44903</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45633,7 +45633,7 @@
         <v>45062</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45706,7 +45706,7 @@
         <v>45162</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45470</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>45566</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>45236</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         <v>44740</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>45434</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45721</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>45867</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>45322</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46378,7 +46378,7 @@
         <v>45824</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>46140</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>45654</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46602,7 +46602,7 @@
         <v>44501</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>44938</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45460</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46831,7 +46831,7 @@
         <v>45841</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>45336</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>45339</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>45541</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47133,7 +47133,7 @@
         <v>45665</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45485</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>45600</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47362,7 +47362,7 @@
         <v>45694</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47435,7 +47435,7 @@
         <v>45643</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>45301</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47581,7 +47581,7 @@
         <v>45510</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>45749</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47737,7 +47737,7 @@
         <v>45406</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47810,7 +47810,7 @@
         <v>45041</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47888,7 +47888,7 @@
         <v>46142</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>45792</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48039,7 +48039,7 @@
         <v>45266</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48112,7 +48112,7 @@
         <v>45225</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48185,7 +48185,7 @@
         <v>45817</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45574</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48341,7 +48341,7 @@
         <v>44950</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48414,7 +48414,7 @@
         <v>46146</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48492,7 +48492,7 @@
         <v>45672</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48565,7 +48565,7 @@
         <v>45567</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48638,7 +48638,7 @@
         <v>46149</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48716,7 +48716,7 @@
         <v>46148</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>46149</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48872,7 +48872,7 @@
         <v>46153</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48945,7 +48945,7 @@
         <v>45548</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49018,7 +49018,7 @@
         <v>45673</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49091,7 +49091,7 @@
         <v>45538</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49164,7 +49164,7 @@
         <v>45106</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>44881</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49310,7 +49310,7 @@
         <v>45874</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45580</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49456,7 +49456,7 @@
         <v>46160</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>46160</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45197</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49685,7 +49685,7 @@
         <v>46160</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49763,7 +49763,7 @@
         <v>44897</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49836,7 +49836,7 @@
         <v>45629</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49909,7 +49909,7 @@
         <v>45450</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49982,7 +49982,7 @@
         <v>45560</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50055,7 +50055,7 @@
         <v>45223</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
         <v>45439</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>44979</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50284,7 +50284,7 @@
         <v>45880</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
         <v>45769</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>45439</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>45163</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50591,7 +50591,7 @@
         <v>45727</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50664,7 +50664,7 @@
         <v>45355</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50742,7 +50742,7 @@
         <v>45525</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>45880</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50893,7 +50893,7 @@
         <v>45880</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50966,7 +50966,7 @@
         <v>45646</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45762</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51112,7 +51112,7 @@
         <v>44508</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51185,7 +51185,7 @@
         <v>46174</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51258,7 +51258,7 @@
         <v>45883</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>45539</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51409,7 +51409,7 @@
         <v>45187</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51482,7 +51482,7 @@
         <v>45407</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51555,7 +51555,7 @@
         <v>46177</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45679</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51706,7 +51706,7 @@
         <v>45429</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51784,7 +51784,7 @@
         <v>45709</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51857,7 +51857,7 @@
         <v>46189</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>45449</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52008,7 +52008,7 @@
         <v>46029</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52086,7 +52086,7 @@
         <v>46189</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52164,7 +52164,7 @@
         <v>45483</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52237,7 +52237,7 @@
         <v>45560</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52315,7 +52315,7 @@
         <v>45608</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52388,7 +52388,7 @@
         <v>45177</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>44789</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52534,7 +52534,7 @@
         <v>45294</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45462</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52680,7 +52680,7 @@
         <v>45236</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52758,7 +52758,7 @@
         <v>45271</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52831,7 +52831,7 @@
         <v>46202</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52909,7 +52909,7 @@
         <v>46204</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52982,7 +52982,7 @@
         <v>46205</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53055,7 +53055,7 @@
         <v>44978</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53128,7 +53128,7 @@
         <v>44981</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53206,7 +53206,7 @@
         <v>44495</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53279,7 +53279,7 @@
         <v>45215</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>44725</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53435,7 +53435,7 @@
         <v>44546</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53508,7 +53508,7 @@
         <v>45757</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53581,7 +53581,7 @@
         <v>46211</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53659,7 +53659,7 @@
         <v>44908</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53737,7 +53737,7 @@
         <v>46211</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53815,7 +53815,7 @@
         <v>44907</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53888,7 +53888,7 @@
         <v>44963</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53961,7 +53961,7 @@
         <v>45149</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54039,7 +54039,7 @@
         <v>45168</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54112,7 +54112,7 @@
         <v>45624</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54185,7 +54185,7 @@
         <v>45335</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54258,7 +54258,7 @@
         <v>46259</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54336,7 +54336,7 @@
         <v>45621</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54409,7 +54409,7 @@
         <v>45509</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>44862</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45097</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         <v>45614</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54701,7 +54701,7 @@
         <v>44795</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54774,7 +54774,7 @@
         <v>45491</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54847,7 +54847,7 @@
         <v>44923</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54920,7 +54920,7 @@
         <v>44923</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>44923</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55066,7 +55066,7 @@
         <v>45177</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55139,7 +55139,7 @@
         <v>44938</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55212,7 +55212,7 @@
         <v>44782</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55290,7 +55290,7 @@
         <v>45188</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>45188</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55436,7 +55436,7 @@
         <v>44928</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55509,7 +55509,7 @@
         <v>45252</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>46267</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55655,7 +55655,7 @@
         <v>45321</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55733,7 +55733,7 @@
         <v>45670</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55806,7 +55806,7 @@
         <v>45267</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55879,7 +55879,7 @@
         <v>45574</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55957,7 +55957,7 @@
         <v>46226</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56030,7 +56030,7 @@
         <v>45621</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56103,7 +56103,7 @@
         <v>45642</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>46272</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56254,7 +56254,7 @@
         <v>46272</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56332,7 +56332,7 @@
         <v>45226</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56410,7 +56410,7 @@
         <v>46272</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56488,7 +56488,7 @@
         <v>46272</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56566,7 +56566,7 @@
         <v>45483</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56639,7 +56639,7 @@
         <v>45642</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56712,7 +56712,7 @@
         <v>45503</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45072</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56868,7 +56868,7 @@
         <v>45195</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56941,7 +56941,7 @@
         <v>46274</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57014,7 +57014,7 @@
         <v>44523</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57092,7 +57092,7 @@
         <v>45204</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57170,7 +57170,7 @@
         <v>46274</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57243,7 +57243,7 @@
         <v>46275</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57321,7 +57321,7 @@
         <v>46274</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57399,7 +57399,7 @@
         <v>46275</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57477,7 +57477,7 @@
         <v>46231</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57555,7 +57555,7 @@
         <v>45106</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57633,7 +57633,7 @@
         <v>45583</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>46275</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57789,7 +57789,7 @@
         <v>46280</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57867,7 +57867,7 @@
         <v>45244</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57940,7 +57940,7 @@
         <v>45597</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58013,7 +58013,7 @@
         <v>45246</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58086,7 +58086,7 @@
         <v>45645</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45775</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58232,7 +58232,7 @@
         <v>45483</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58305,7 +58305,7 @@
         <v>45756</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58383,7 +58383,7 @@
         <v>46239</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58456,7 +58456,7 @@
         <v>46239</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>46283</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58607,7 +58607,7 @@
         <v>46282</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58685,7 +58685,7 @@
         <v>45665</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58758,7 +58758,7 @@
         <v>45672</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58831,7 +58831,7 @@
         <v>45077</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58904,7 +58904,7 @@
         <v>46287</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58977,7 +58977,7 @@
         <v>45391</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59050,7 +59050,7 @@
         <v>45231</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59123,7 +59123,7 @@
         <v>44837</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59201,7 +59201,7 @@
         <v>46244</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59274,7 +59274,7 @@
         <v>45225</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59352,7 +59352,7 @@
         <v>46287</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59430,7 +59430,7 @@
         <v>44888</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59503,7 +59503,7 @@
         <v>44643</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59581,7 +59581,7 @@
         <v>45531</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59659,7 +59659,7 @@
         <v>46245</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59732,7 +59732,7 @@
         <v>46245</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59805,7 +59805,7 @@
         <v>45769</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59878,7 +59878,7 @@
         <v>45355</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59951,7 +59951,7 @@
         <v>46288</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60029,7 +60029,7 @@
         <v>46246</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60102,7 +60102,7 @@
         <v>45072</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60180,7 +60180,7 @@
         <v>45118</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60253,7 +60253,7 @@
         <v>46289</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60331,7 +60331,7 @@
         <v>44540</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60409,7 +60409,7 @@
         <v>45078</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60487,7 +60487,7 @@
         <v>45720</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60560,7 +60560,7 @@
         <v>45720</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60633,7 +60633,7 @@
         <v>45215</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60706,7 +60706,7 @@
         <v>45034</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60779,7 +60779,7 @@
         <v>46247</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60852,7 +60852,7 @@
         <v>45579</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60930,7 +60930,7 @@
         <v>46287</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61008,7 +61008,7 @@
         <v>44923</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61081,7 +61081,7 @@
         <v>45639</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61154,7 +61154,7 @@
         <v>45456</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61232,7 +61232,7 @@
         <v>44623</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61310,7 +61310,7 @@
         <v>45446</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61388,7 +61388,7 @@
         <v>45272</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61461,7 +61461,7 @@
         <v>44914</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61534,7 +61534,7 @@
         <v>45201</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61607,7 +61607,7 @@
         <v>45430</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61680,7 +61680,7 @@
         <v>46295</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61758,7 +61758,7 @@
         <v>45034</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61831,7 +61831,7 @@
         <v>45257</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61904,7 +61904,7 @@
         <v>44916</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61977,7 +61977,7 @@
         <v>44589</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62055,7 +62055,7 @@
         <v>45646</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62128,7 +62128,7 @@
         <v>46296</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62201,7 +62201,7 @@
         <v>46296</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62274,7 +62274,7 @@
         <v>45128</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62352,7 +62352,7 @@
         <v>45245</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62425,7 +62425,7 @@
         <v>45684</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62498,7 +62498,7 @@
         <v>45072</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62571,7 +62571,7 @@
         <v>45238</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62644,7 +62644,7 @@
         <v>45476</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62717,7 +62717,7 @@
         <v>45187</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62790,7 +62790,7 @@
         <v>45561</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62863,7 +62863,7 @@
         <v>45355</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62936,7 +62936,7 @@
         <v>45355</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63009,7 +63009,7 @@
         <v>45301</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63082,7 +63082,7 @@
         <v>45623</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63155,7 +63155,7 @@
         <v>45636</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63228,7 +63228,7 @@
         <v>45303</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63301,7 +63301,7 @@
         <v>45271</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63374,7 +63374,7 @@
         <v>44623</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63447,7 +63447,7 @@
         <v>45420</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63520,7 +63520,7 @@
         <v>45194</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63593,7 +63593,7 @@
         <v>45204</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63671,7 +63671,7 @@
         <v>45089</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63749,7 +63749,7 @@
         <v>44791</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63827,7 +63827,7 @@
         <v>45027</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63900,7 +63900,7 @@
         <v>45054</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63973,7 +63973,7 @@
         <v>45749</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64046,7 +64046,7 @@
         <v>44950</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64119,7 +64119,7 @@
         <v>44725</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64197,7 +64197,7 @@
         <v>45491</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64275,7 +64275,7 @@
         <v>45293</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64348,7 +64348,7 @@
         <v>45432</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64421,7 +64421,7 @@
         <v>45638</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64494,7 +64494,7 @@
         <v>45175</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64567,7 +64567,7 @@
         <v>44928</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64640,7 +64640,7 @@
         <v>45517</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64713,7 +64713,7 @@
         <v>45226</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64786,7 +64786,7 @@
         <v>45053</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64859,7 +64859,7 @@
         <v>45175</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64932,7 +64932,7 @@
         <v>45726</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65005,7 +65005,7 @@
         <v>45442</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65078,7 +65078,7 @@
         <v>45041</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65151,7 +65151,7 @@
         <v>45547</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65224,7 +65224,7 @@
         <v>45301</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65297,7 +65297,7 @@
         <v>44512</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65375,7 +65375,7 @@
         <v>45119</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65448,7 +65448,7 @@
         <v>44957</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65521,7 +65521,7 @@
         <v>45482</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65599,7 +65599,7 @@
         <v>45525</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65672,7 +65672,7 @@
         <v>45455</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65750,7 +65750,7 @@
         <v>44911</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65823,7 +65823,7 @@
         <v>44641</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65901,7 +65901,7 @@
         <v>45399</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65974,7 +65974,7 @@
         <v>45054</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66052,7 +66052,7 @@
         <v>44722</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66130,7 +66130,7 @@
         <v>45371</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66203,7 +66203,7 @@
         <v>44684</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66281,7 +66281,7 @@
         <v>45699</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66359,7 +66359,7 @@
         <v>45756</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66437,7 +66437,7 @@
         <v>45778</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66510,7 +66510,7 @@
         <v>45342</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66583,7 +66583,7 @@
         <v>46089</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66661,7 +66661,7 @@
         <v>46072</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66739,7 +66739,7 @@
         <v>46171</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>

--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -601,7 +601,7 @@
         <v>46057</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>46070</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44722</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46205</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46033</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>46184</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45092</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>46181</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>46033</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45016</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>44637</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45812</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>46140</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>46178</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>45785</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>46205</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>46157</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45775</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45917</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>46069</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>46191</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45897</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>46055</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45469</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45016</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>46089</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>45533</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>46196</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>46178</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>46178</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>46104</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>46033</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>46196</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>45932</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>45510</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>46055</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45695</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>45016</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>44610</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>45938</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>46055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>44090</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>44722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>45775</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>45099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>46055</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>45839</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45583</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>46178</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>46190</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>46029</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44722</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>45799</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         <v>46055</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>46092</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>45971</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>45754</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>45903</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>45443</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>46093</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45181</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44796</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>46258</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>45713</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45315</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         <v>44589</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45903</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>44704</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>45895</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>45925</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>44741</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>45995</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>45831</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>45831</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>44936</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>44501</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>46164</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>45714</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>44641</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>45233</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>44722</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>44721</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>44867</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>44910</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>46029</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>45705</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>45623</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>45461</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>45957</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>45971</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>45119</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>45824</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>44523</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>45246</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>45188</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>45053</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>45187</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>45631</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>46266</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>46274</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>45538</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>46287</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>46290</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>44944</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>45247</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>45713</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>45461</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>45053</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>45411</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>44637</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>44512</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>44489</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>44508</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>44537</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>44511</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44712</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>44852</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>44733</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>44811</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>44756</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>44887</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44696</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>44616</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>44503</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44588</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>44809</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44602</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>44533</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>44529</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>44501</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         <v>44613</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>44540</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>44701</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44721</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44557</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>44547</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         <v>44802</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>44512</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>44886</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>44721</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>44739</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>44743</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>44743</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>44616</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44811</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>44839</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>44544</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>44749</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>44858</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>44501</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>44600</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44603</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44743</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>44811</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>44811</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45632</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>45645</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>45674</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>44978</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45007</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>45713</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>45244</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>45519</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>44515</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>44900</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>45769</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>44599</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>44894</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45252</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>45191</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>46001</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>45644</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>46003</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>46003</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45093</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>45636</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45162</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>46002</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>45225</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>45789</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>46002</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45237</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>46007</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>46006</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>46006</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>44832</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45245</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>46008</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>45747</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>46009</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>46008</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45195</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45677</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45559</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>46010</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>45453</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>46010</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45629</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>46010</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45089</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45891</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>45891</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>45891</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45890</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>45890</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45891</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>46024</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>45892</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45895</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>45727</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45894</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>45761</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>46029</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>45592</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>46030</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44896</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>45202</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>45898</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
         <v>46031</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>45898</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22249,7 +22249,7 @@
         <v>45659</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>46034</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>46034</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>45775</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>45540</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>44928</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>46035</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>45901</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>45071</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>45712</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>46034</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>46034</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23140,7 +23140,7 @@
         <v>44903</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>44739</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>44741</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>45902</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>45902</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>45902</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>45902</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>46036</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>46036</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>45191</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45152</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>46036</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>46036</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>46036</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>46036</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44946</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>46036</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>46036</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>45982</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24552,7 +24552,7 @@
         <v>45904</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>45904</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>45875</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>45231</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>44903</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>45908</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         <v>45488</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>45481</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>45910</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45036</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45229</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>45020</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>45797</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>45910</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>44923</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>45540</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>45911</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45204</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>45797</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>45797</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>45797</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>45915</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>46034</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>46044</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>46044</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>45912</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26505,7 +26505,7 @@
         <v>45912</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>44931</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>45188</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45916</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>45916</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>45916</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>45799</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>44938</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>45530</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>45919</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>45800</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45800</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>45747</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>45805</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>45804</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>45919</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27698,7 +27698,7 @@
         <v>45713</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
         <v>45919</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45804</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>45805</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>45804</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>45747</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>45807</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>45807</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>44804</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>46055</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>45925</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45461</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>45926</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>45926</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>46059</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>46059</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>46059</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>46059</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>45072</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>45930</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45931</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>45931</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>45931</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>46064</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>45933</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45933</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>45238</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>46064</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>45936</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>45936</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>44897</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>45936</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>46066</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>45810</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>45037</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>45428</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>45937</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30444,7 +30444,7 @@
         <v>45541</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>45937</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>44677</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30678,7 +30678,7 @@
         <v>46070</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30751,7 +30751,7 @@
         <v>45937</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>45939</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>45219</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>45937</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>45477</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45937</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>46073</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>46073</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>45930</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>45940</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>46073</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>45121</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>44886</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>44881</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>45677</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>45947</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>45931</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>45322</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>45672</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>45951</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>45229</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>45036</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>45952</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>45952</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>46073</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>45957</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>45957</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45541</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>45957</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45204</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45204</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45642</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45957</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>45957</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>46085</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>45957</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44860</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>45960</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>45960</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>45960</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33771,7 +33771,7 @@
         <v>45959</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         <v>45965</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33917,7 +33917,7 @@
         <v>45714</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33990,7 +33990,7 @@
         <v>46092</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>45964</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>46092</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>45874</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>45964</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>45964</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>46093</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34511,7 +34511,7 @@
         <v>45964</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>45965</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>45203</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>45692</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>46093</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>45541</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45534</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>45967</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45967</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45965</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>46093</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>45965</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>45971</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>46098</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45763</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>45925</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45198</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>45608</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>46100</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35928,7 +35928,7 @@
         <v>45973</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>45971</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>45972</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>45972</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>45973</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>46104</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45974</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>45974</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>45817</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45525</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>45740</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>45978</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>45978</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36907,7 +36907,7 @@
         <v>45257</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36980,7 +36980,7 @@
         <v>45257</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45575</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>45979</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45818</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>44911</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>45980</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>45981</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>45762</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>45818</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>46107</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>45980</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45622</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>45818</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>45749</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>45007</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>45566</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45820</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>45243</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45821</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38387,7 +38387,7 @@
         <v>45821</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>45821</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>45488</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>45547</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>45987</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>45237</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>45237</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45712</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>45987</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45824</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39132,7 +39132,7 @@
         <v>45989</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45989</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39288,7 +39288,7 @@
         <v>45824</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39361,7 +39361,7 @@
         <v>45993</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>45992</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>45992</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>45728</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>46121</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45993</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>45993</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>46126</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>45714</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45225</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>45827</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>46126</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>45999</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>46128</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>46128</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>46127</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>44637</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>46001</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>46127</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         <v>46133</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>46132</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45831</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>45642</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45831</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45211</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>46132</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41314,7 +41314,7 @@
         <v>45833</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>45832</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>45833</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>46135</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
         <v>44994</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41699,7 +41699,7 @@
         <v>45252</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>45832</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41850,7 +41850,7 @@
         <v>45835</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>46134</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>45838</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>45839</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42147,7 +42147,7 @@
         <v>45491</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>45838</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45839</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>44697</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>45840</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42522,7 +42522,7 @@
         <v>45090</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>45841</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42668,7 +42668,7 @@
         <v>45840</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>45841</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45079</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42892,7 +42892,7 @@
         <v>45597</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>45769</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43038,7 +43038,7 @@
         <v>45841</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43116,7 +43116,7 @@
         <v>45841</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>44881</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>45841</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43345,7 +43345,7 @@
         <v>45842</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>45511</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>45757</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>45883</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43637,7 +43637,7 @@
         <v>44511</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45357</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>45757</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45713</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>45609</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44007,7 +44007,7 @@
         <v>46136</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44080,7 +44080,7 @@
         <v>45846</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44153,7 +44153,7 @@
         <v>45849</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44226,7 +44226,7 @@
         <v>45849</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45849</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>45448</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45875</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45831</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>45853</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>45902</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44747,7 +44747,7 @@
         <v>45855</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>45153</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44898,7 +44898,7 @@
         <v>45636</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>45749</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         <v>45855</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45761</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45195,7 +45195,7 @@
         <v>46133</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>46031</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>45294</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>45624</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>45624</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>44903</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45633,7 +45633,7 @@
         <v>45062</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45706,7 +45706,7 @@
         <v>45162</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45470</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
         <v>45566</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>45236</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         <v>44740</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>45434</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45721</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>45867</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>45322</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46378,7 +46378,7 @@
         <v>45824</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>46140</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>45654</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46602,7 +46602,7 @@
         <v>44501</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46680,7 +46680,7 @@
         <v>44938</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45460</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46831,7 +46831,7 @@
         <v>45841</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>45336</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>45339</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>45541</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47133,7 +47133,7 @@
         <v>45665</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45485</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>45600</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47362,7 +47362,7 @@
         <v>45694</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47435,7 +47435,7 @@
         <v>45643</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47508,7 +47508,7 @@
         <v>45301</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47581,7 +47581,7 @@
         <v>45510</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>45749</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47737,7 +47737,7 @@
         <v>45406</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47810,7 +47810,7 @@
         <v>45041</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47888,7 +47888,7 @@
         <v>46142</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>45792</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48039,7 +48039,7 @@
         <v>45266</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48112,7 +48112,7 @@
         <v>45225</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48185,7 +48185,7 @@
         <v>45817</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45574</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48341,7 +48341,7 @@
         <v>44950</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48414,7 +48414,7 @@
         <v>46146</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48492,7 +48492,7 @@
         <v>45672</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48565,7 +48565,7 @@
         <v>45567</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48638,7 +48638,7 @@
         <v>46149</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48716,7 +48716,7 @@
         <v>46148</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>46149</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48872,7 +48872,7 @@
         <v>46153</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48945,7 +48945,7 @@
         <v>45548</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49018,7 +49018,7 @@
         <v>45673</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49091,7 +49091,7 @@
         <v>45538</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49164,7 +49164,7 @@
         <v>45106</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>44881</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49310,7 +49310,7 @@
         <v>45874</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49383,7 +49383,7 @@
         <v>45580</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49456,7 +49456,7 @@
         <v>46160</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>46160</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45197</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49685,7 +49685,7 @@
         <v>46160</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49763,7 +49763,7 @@
         <v>44897</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49836,7 +49836,7 @@
         <v>45629</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49909,7 +49909,7 @@
         <v>45450</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49982,7 +49982,7 @@
         <v>45560</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50055,7 +50055,7 @@
         <v>45223</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
         <v>45439</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>44979</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50284,7 +50284,7 @@
         <v>45880</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
         <v>45769</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>45439</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>45163</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50591,7 +50591,7 @@
         <v>45727</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50664,7 +50664,7 @@
         <v>45355</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50742,7 +50742,7 @@
         <v>45525</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>45880</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50893,7 +50893,7 @@
         <v>45880</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50966,7 +50966,7 @@
         <v>45646</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45762</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51112,7 +51112,7 @@
         <v>44508</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51185,7 +51185,7 @@
         <v>46174</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51258,7 +51258,7 @@
         <v>45883</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>45539</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51409,7 +51409,7 @@
         <v>45187</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51482,7 +51482,7 @@
         <v>45407</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51555,7 +51555,7 @@
         <v>46177</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45679</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51706,7 +51706,7 @@
         <v>45429</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51784,7 +51784,7 @@
         <v>45709</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51857,7 +51857,7 @@
         <v>46189</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>45449</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52008,7 +52008,7 @@
         <v>46029</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52086,7 +52086,7 @@
         <v>46189</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52164,7 +52164,7 @@
         <v>45483</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52237,7 +52237,7 @@
         <v>45560</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52315,7 +52315,7 @@
         <v>45608</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52388,7 +52388,7 @@
         <v>45177</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>44789</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52534,7 +52534,7 @@
         <v>45294</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45462</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52680,7 +52680,7 @@
         <v>45236</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52758,7 +52758,7 @@
         <v>45271</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52831,7 +52831,7 @@
         <v>46202</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52909,7 +52909,7 @@
         <v>46204</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52982,7 +52982,7 @@
         <v>46205</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53055,7 +53055,7 @@
         <v>44978</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53128,7 +53128,7 @@
         <v>44981</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53206,7 +53206,7 @@
         <v>44495</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53279,7 +53279,7 @@
         <v>45215</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>44725</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53435,7 +53435,7 @@
         <v>44546</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53508,7 +53508,7 @@
         <v>45757</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53581,7 +53581,7 @@
         <v>46211</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53659,7 +53659,7 @@
         <v>44908</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53737,7 +53737,7 @@
         <v>46211</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53815,7 +53815,7 @@
         <v>44907</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53888,7 +53888,7 @@
         <v>44963</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53961,7 +53961,7 @@
         <v>45149</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54039,7 +54039,7 @@
         <v>45168</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54112,7 +54112,7 @@
         <v>45624</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54185,7 +54185,7 @@
         <v>45335</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54258,7 +54258,7 @@
         <v>46259</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54336,7 +54336,7 @@
         <v>45621</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54409,7 +54409,7 @@
         <v>45509</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>44862</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45097</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         <v>45614</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54701,7 +54701,7 @@
         <v>44795</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54774,7 +54774,7 @@
         <v>45491</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54847,7 +54847,7 @@
         <v>44923</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54920,7 +54920,7 @@
         <v>44923</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>44923</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55066,7 +55066,7 @@
         <v>45177</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55139,7 +55139,7 @@
         <v>44938</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55212,7 +55212,7 @@
         <v>44782</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55290,7 +55290,7 @@
         <v>45188</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>45188</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55436,7 +55436,7 @@
         <v>44928</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55509,7 +55509,7 @@
         <v>45252</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>46267</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55655,7 +55655,7 @@
         <v>45321</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55733,7 +55733,7 @@
         <v>45670</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55806,7 +55806,7 @@
         <v>45267</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55879,7 +55879,7 @@
         <v>45574</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55957,7 +55957,7 @@
         <v>46226</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56030,7 +56030,7 @@
         <v>45621</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56103,7 +56103,7 @@
         <v>45642</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>46272</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56254,7 +56254,7 @@
         <v>46272</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56332,7 +56332,7 @@
         <v>45226</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56410,7 +56410,7 @@
         <v>46272</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56488,7 +56488,7 @@
         <v>46272</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56566,7 +56566,7 @@
         <v>45483</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56639,7 +56639,7 @@
         <v>45642</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56712,7 +56712,7 @@
         <v>45503</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45072</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56868,7 +56868,7 @@
         <v>45195</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56941,7 +56941,7 @@
         <v>46274</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57014,7 +57014,7 @@
         <v>44523</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57092,7 +57092,7 @@
         <v>45204</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57170,7 +57170,7 @@
         <v>46274</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57243,7 +57243,7 @@
         <v>46275</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57321,7 +57321,7 @@
         <v>46274</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57399,7 +57399,7 @@
         <v>46275</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57477,7 +57477,7 @@
         <v>46231</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57555,7 +57555,7 @@
         <v>45106</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57633,7 +57633,7 @@
         <v>45583</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>46275</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57789,7 +57789,7 @@
         <v>46280</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57867,7 +57867,7 @@
         <v>45244</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57940,7 +57940,7 @@
         <v>45597</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58013,7 +58013,7 @@
         <v>45246</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58086,7 +58086,7 @@
         <v>45645</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45775</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58232,7 +58232,7 @@
         <v>45483</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58305,7 +58305,7 @@
         <v>45756</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58383,7 +58383,7 @@
         <v>46239</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58456,7 +58456,7 @@
         <v>46239</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>46283</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58607,7 +58607,7 @@
         <v>46282</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58685,7 +58685,7 @@
         <v>45665</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58758,7 +58758,7 @@
         <v>45672</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58831,7 +58831,7 @@
         <v>45077</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58904,7 +58904,7 @@
         <v>46287</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58977,7 +58977,7 @@
         <v>45391</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59050,7 +59050,7 @@
         <v>45231</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59123,7 +59123,7 @@
         <v>44837</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59201,7 +59201,7 @@
         <v>46244</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59274,7 +59274,7 @@
         <v>45225</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59352,7 +59352,7 @@
         <v>46287</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59430,7 +59430,7 @@
         <v>44888</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59503,7 +59503,7 @@
         <v>44643</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59581,7 +59581,7 @@
         <v>45531</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59659,7 +59659,7 @@
         <v>46245</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59732,7 +59732,7 @@
         <v>46245</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59805,7 +59805,7 @@
         <v>45769</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59878,7 +59878,7 @@
         <v>45355</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59951,7 +59951,7 @@
         <v>46288</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60029,7 +60029,7 @@
         <v>46246</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60102,7 +60102,7 @@
         <v>45072</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60180,7 +60180,7 @@
         <v>45118</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60253,7 +60253,7 @@
         <v>46289</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60331,7 +60331,7 @@
         <v>44540</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60409,7 +60409,7 @@
         <v>45078</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60487,7 +60487,7 @@
         <v>45720</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60560,7 +60560,7 @@
         <v>45720</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60633,7 +60633,7 @@
         <v>45215</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60706,7 +60706,7 @@
         <v>45034</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60779,7 +60779,7 @@
         <v>46247</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60852,7 +60852,7 @@
         <v>45579</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60930,7 +60930,7 @@
         <v>46287</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61008,7 +61008,7 @@
         <v>44923</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61081,7 +61081,7 @@
         <v>45639</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61154,7 +61154,7 @@
         <v>45456</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61232,7 +61232,7 @@
         <v>44623</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61310,7 +61310,7 @@
         <v>45446</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61388,7 +61388,7 @@
         <v>45272</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61461,7 +61461,7 @@
         <v>44914</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61534,7 +61534,7 @@
         <v>45201</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61607,7 +61607,7 @@
         <v>45430</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61680,7 +61680,7 @@
         <v>46295</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61758,7 +61758,7 @@
         <v>45034</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61831,7 +61831,7 @@
         <v>45257</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61904,7 +61904,7 @@
         <v>44916</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61977,7 +61977,7 @@
         <v>44589</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62055,7 +62055,7 @@
         <v>45646</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62128,7 +62128,7 @@
         <v>46296</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62201,7 +62201,7 @@
         <v>46296</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62274,7 +62274,7 @@
         <v>45128</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62352,7 +62352,7 @@
         <v>45245</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62425,7 +62425,7 @@
         <v>45684</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62498,7 +62498,7 @@
         <v>45072</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62571,7 +62571,7 @@
         <v>45238</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62644,7 +62644,7 @@
         <v>45476</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62717,7 +62717,7 @@
         <v>45187</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62790,7 +62790,7 @@
         <v>45561</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62863,7 +62863,7 @@
         <v>45355</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62936,7 +62936,7 @@
         <v>45355</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63009,7 +63009,7 @@
         <v>45301</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63082,7 +63082,7 @@
         <v>45623</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63155,7 +63155,7 @@
         <v>45636</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63228,7 +63228,7 @@
         <v>45303</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63301,7 +63301,7 @@
         <v>45271</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63374,7 +63374,7 @@
         <v>44623</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63447,7 +63447,7 @@
         <v>45420</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63520,7 +63520,7 @@
         <v>45194</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63593,7 +63593,7 @@
         <v>45204</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63671,7 +63671,7 @@
         <v>45089</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63749,7 +63749,7 @@
         <v>44791</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63827,7 +63827,7 @@
         <v>45027</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63900,7 +63900,7 @@
         <v>45054</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63973,7 +63973,7 @@
         <v>45749</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64046,7 +64046,7 @@
         <v>44950</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64119,7 +64119,7 @@
         <v>44725</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64197,7 +64197,7 @@
         <v>45491</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64275,7 +64275,7 @@
         <v>45293</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64348,7 +64348,7 @@
         <v>45432</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64421,7 +64421,7 @@
         <v>45638</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64494,7 +64494,7 @@
         <v>45175</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64567,7 +64567,7 @@
         <v>44928</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64640,7 +64640,7 @@
         <v>45517</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64713,7 +64713,7 @@
         <v>45226</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64786,7 +64786,7 @@
         <v>45053</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64859,7 +64859,7 @@
         <v>45175</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64932,7 +64932,7 @@
         <v>45726</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65005,7 +65005,7 @@
         <v>45442</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65078,7 +65078,7 @@
         <v>45041</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65151,7 +65151,7 @@
         <v>45547</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65224,7 +65224,7 @@
         <v>45301</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65297,7 +65297,7 @@
         <v>44512</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65375,7 +65375,7 @@
         <v>45119</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65448,7 +65448,7 @@
         <v>44957</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65521,7 +65521,7 @@
         <v>45482</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65599,7 +65599,7 @@
         <v>45525</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65672,7 +65672,7 @@
         <v>45455</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65750,7 +65750,7 @@
         <v>44911</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65823,7 +65823,7 @@
         <v>44641</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65901,7 +65901,7 @@
         <v>45399</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65974,7 +65974,7 @@
         <v>45054</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66052,7 +66052,7 @@
         <v>44722</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66130,7 +66130,7 @@
         <v>45371</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66203,7 +66203,7 @@
         <v>44684</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66281,7 +66281,7 @@
         <v>45699</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66359,7 +66359,7 @@
         <v>45756</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66437,7 +66437,7 @@
         <v>45778</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66510,7 +66510,7 @@
         <v>45342</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66583,7 +66583,7 @@
         <v>46089</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66661,7 +66661,7 @@
         <v>46072</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66739,7 +66739,7 @@
         <v>46171</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>

--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -601,7 +601,7 @@
         <v>46057</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>46070</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44722</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46205</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46033</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>46184</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45092</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>46181</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>46033</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45016</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>44637</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45812</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>46140</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>46178</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>46205</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>45785</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>46157</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45775</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45917</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>46069</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>46191</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45469</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>45897</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>46055</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45016</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>46089</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>45533</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>46196</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>46178</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>46178</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>45932</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>46104</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>46033</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>46196</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>45510</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>46055</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>45695</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>45016</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>44610</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>45938</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>46055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>44090</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>45583</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>45099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>45839</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>45775</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>46055</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>46178</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>46029</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>46190</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>44722</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>45799</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>45971</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>46055</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>46092</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>45713</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>45903</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>45181</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>44796</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>44725</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>45443</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>45754</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>46093</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>46258</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>44589</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>45315</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>45903</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44704</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>44501</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>45895</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>45233</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>45925</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>45831</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>45831</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>44936</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>45714</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>45995</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>44641</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>44741</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>46164</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>44722</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>44721</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>45713</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>45119</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>45461</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44523</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
         <v>44944</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>44867</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45538</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>44910</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>45053</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>45631</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>45461</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>45957</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>45247</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>45187</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>45971</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>45188</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>45246</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>45705</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>45053</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>45623</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>45824</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>46029</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>46266</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>46274</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>46287</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>46290</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>44637</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>45411</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         <v>44512</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>44489</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>44508</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>44537</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>44511</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>44712</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44852</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44733</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>44811</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>44756</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>44887</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>44696</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>44616</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>44503</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>44588</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44809</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>44602</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44533</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>44529</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>44501</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>44613</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>44512</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>44501</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>44811</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>44886</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>44540</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>44721</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
         <v>44739</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>44701</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16328,7 +16328,7 @@
         <v>44839</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44544</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>44743</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>44743</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44600</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44749</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>44721</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>44603</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>44743</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>44858</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>44616</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>44557</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>44547</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>44802</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>44862</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>45531</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45072</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>44811</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>44811</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>45335</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>45769</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>45293</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>45077</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>45252</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>45037</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44894</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45614</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>45089</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>45187</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>45215</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>45391</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>45761</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>44791</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>45301</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>45202</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45714</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45757</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>44837</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45106</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>45321</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45749</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45128</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>45491</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45301</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45574</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45644</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>44725</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>45670</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>44928</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>45541</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45460</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>44540</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>44903</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45677</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>44903</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>45118</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>44881</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>45267</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>45756</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45541</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>45257</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>45194</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>44795</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45672</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45665</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>45238</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45560</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>45152</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45762</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44914</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>44897</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>44546</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>45446</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21787,7 +21787,7 @@
         <v>45090</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>45072</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>44515</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>45883</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>45062</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45271</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>44931</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45271</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45339</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>45407</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>44888</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>45462</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>45294</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>45530</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>45503</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>45483</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>45163</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>45643</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>45238</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>45430</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>45890</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>45890</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>45177</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45439</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45891</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>45891</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>45892</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>45891</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
         <v>45891</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45894</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45895</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45775</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>45692</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45898</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>45204</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>45898</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>45540</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>45434</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>44928</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>45902</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>45624</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>45624</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>45902</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45294</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>45483</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>45902</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>45902</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45901</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>45672</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>45511</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>45608</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>45539</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>45195</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>44938</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>45583</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25902,7 +25902,7 @@
         <v>45904</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         <v>45432</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>45149</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45904</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>44896</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>45875</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>45908</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45481</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>45215</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>44907</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45488</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>45910</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45910</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>45912</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>45911</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>45236</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>45456</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45491</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>45491</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>45912</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45916</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>45915</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>44523</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>45916</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>45916</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45525</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>45229</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>45482</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>45476</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>45428</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>45079</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>45455</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44641</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28386,7 +28386,7 @@
         <v>44911</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45525</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>45399</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>45713</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>45608</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45525</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28834,7 +28834,7 @@
         <v>45919</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>45054</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>45919</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>45919</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45547</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>44928</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>44599</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>45561</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>45355</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>45355</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45548</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45225</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>45789</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>45621</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>45517</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>45560</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>45636</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>45925</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45926</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>45041</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>45204</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>45483</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>45926</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>45195</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>45534</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30684,7 +30684,7 @@
         <v>45036</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>45930</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30835,7 +30835,7 @@
         <v>45712</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>45188</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>45229</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>45020</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>45541</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31210,7 +31210,7 @@
         <v>45540</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>45488</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>45054</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>45036</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31507,7 +31507,7 @@
         <v>45632</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>45931</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>45449</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44923</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>45442</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31872,7 +31872,7 @@
         <v>45575</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>45797</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32023,7 +32023,7 @@
         <v>44916</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32096,7 +32096,7 @@
         <v>45797</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32169,7 +32169,7 @@
         <v>45931</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32242,7 +32242,7 @@
         <v>45797</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>45797</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32398,7 +32398,7 @@
         <v>45931</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         <v>45429</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32554,7 +32554,7 @@
         <v>45799</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>45713</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>45933</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>45800</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>45645</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>44512</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33007,7 +33007,7 @@
         <v>45679</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>45244</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>45097</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>45642</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>44923</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>44923</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>45757</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>45933</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33591,7 +33591,7 @@
         <v>45936</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>45597</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>45800</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>45072</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>45203</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>45804</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>45121</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>45747</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>45936</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>45936</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>45804</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>45677</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>45937</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>45937</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>45646</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>45646</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>45804</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>45937</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>45747</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45805</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>45805</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>44903</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>45007</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>45072</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>45197</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>45201</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>45937</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>45624</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45714</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>45807</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>45322</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>45937</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>45807</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>45236</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>45191</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45810</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36284,7 +36284,7 @@
         <v>45226</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>45093</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>45187</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36508,7 +36508,7 @@
         <v>45940</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>44994</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>45939</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36732,7 +36732,7 @@
         <v>45930</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>44804</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>45204</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36956,7 +36956,7 @@
         <v>45231</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>45931</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37107,7 +37107,7 @@
         <v>45559</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>45629</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37253,7 +37253,7 @@
         <v>45817</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
         <v>45818</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37404,7 +37404,7 @@
         <v>45762</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>45740</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37550,7 +37550,7 @@
         <v>45775</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>45818</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37696,7 +37696,7 @@
         <v>45198</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>44923</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>45818</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45820</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>45211</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>45579</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38144,7 +38144,7 @@
         <v>45749</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>44677</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38295,7 +38295,7 @@
         <v>45621</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         <v>45824</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>45821</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>45947</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>45580</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38665,7 +38665,7 @@
         <v>45821</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>45821</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>45824</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38894,7 +38894,7 @@
         <v>45636</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38967,7 +38967,7 @@
         <v>45574</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39045,7 +39045,7 @@
         <v>45622</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39123,7 +39123,7 @@
         <v>45642</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>45642</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39269,7 +39269,7 @@
         <v>45952</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>45827</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39415,7 +39415,7 @@
         <v>45951</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39488,7 +39488,7 @@
         <v>45191</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>45832</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>45832</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>45831</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45177</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>45225</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45831</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40024,7 +40024,7 @@
         <v>45461</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>45952</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>45957</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40248,7 +40248,7 @@
         <v>45957</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>45957</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>45957</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40482,7 +40482,7 @@
         <v>45957</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>45957</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>45960</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>45960</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
         <v>45959</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>45960</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>45833</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41023,7 +41023,7 @@
         <v>45246</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41096,7 +41096,7 @@
         <v>45245</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41169,7 +41169,7 @@
         <v>45833</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45519</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>45964</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41393,7 +41393,7 @@
         <v>45964</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41471,7 +41471,7 @@
         <v>45204</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>45964</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>45835</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>45838</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>44981</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41846,7 +41846,7 @@
         <v>45673</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41919,7 +41919,7 @@
         <v>45838</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41997,7 +41997,7 @@
         <v>45175</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         <v>45245</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42143,7 +42143,7 @@
         <v>45964</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>45188</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>45188</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>45840</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>45840</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>45839</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>45965</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>45839</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45965</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>45728</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>45636</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>45769</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>45175</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>45965</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>45659</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>45965</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45967</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43404,7 +43404,7 @@
         <v>45225</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43477,7 +43477,7 @@
         <v>45712</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>45642</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>45841</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45967</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45841</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>45842</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45841</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45638</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45841</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>45925</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>45841</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>45971</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44373,7 +44373,7 @@
         <v>45357</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44446,7 +44446,7 @@
         <v>45971</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44519,7 +44519,7 @@
         <v>45034</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44592,7 +44592,7 @@
         <v>45034</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>45252</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44738,7 +44738,7 @@
         <v>45629</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44811,7 +44811,7 @@
         <v>44739</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>45846</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>45972</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>45972</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>45645</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45176,7 +45176,7 @@
         <v>45974</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>45973</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45639</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45405,7 +45405,7 @@
         <v>45727</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45478,7 +45478,7 @@
         <v>45257</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45551,7 +45551,7 @@
         <v>44782</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45629,7 +45629,7 @@
         <v>45727</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45702,7 +45702,7 @@
         <v>45849</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45775,7 +45775,7 @@
         <v>45973</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45853,7 +45853,7 @@
         <v>45974</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>45252</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45849</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45713</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46150,7 +46150,7 @@
         <v>45849</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46223,7 +46223,7 @@
         <v>45853</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>45855</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45322</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>44886</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45855</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>44881</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>44508</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45747</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45978</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46890,7 +46890,7 @@
         <v>45237</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>45237</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47036,7 +47036,7 @@
         <v>45243</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47109,7 +47109,7 @@
         <v>45257</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45694</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>45089</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47333,7 +47333,7 @@
         <v>45867</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47406,7 +47406,7 @@
         <v>45978</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>45219</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>44978</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>45980</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47698,7 +47698,7 @@
         <v>45769</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47776,7 +47776,7 @@
         <v>45237</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>44697</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47922,7 +47922,7 @@
         <v>45355</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47995,7 +47995,7 @@
         <v>44908</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>45763</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45980</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>44950</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>44950</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>45168</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>45272</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
         <v>45684</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45979</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45355</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45880</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45880</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48891,7 +48891,7 @@
         <v>45880</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
         <v>45981</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45541</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49115,7 +49115,7 @@
         <v>45672</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>46098</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>45119</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>45509</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>44495</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>45301</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>46100</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49626,7 +49626,7 @@
         <v>45566</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49699,7 +49699,7 @@
         <v>46104</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49772,7 +49772,7 @@
         <v>45223</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>45078</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49928,7 +49928,7 @@
         <v>44789</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50001,7 +50001,7 @@
         <v>45027</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45303</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>45244</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50220,7 +50220,7 @@
         <v>44938</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50293,7 +50293,7 @@
         <v>46107</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>45987</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45071</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50517,7 +50517,7 @@
         <v>45567</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50590,7 +50590,7 @@
         <v>45547</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50663,7 +50663,7 @@
         <v>45053</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45761</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50814,7 +50814,7 @@
         <v>45987</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50887,7 +50887,7 @@
         <v>44860</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50960,7 +50960,7 @@
         <v>45992</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51033,7 +51033,7 @@
         <v>45992</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51106,7 +51106,7 @@
         <v>45989</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51184,7 +51184,7 @@
         <v>45769</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51257,7 +51257,7 @@
         <v>44900</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>45989</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51413,7 +51413,7 @@
         <v>45439</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51491,7 +51491,7 @@
         <v>45623</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51564,7 +51564,7 @@
         <v>45453</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51637,7 +51637,7 @@
         <v>44897</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51710,7 +51710,7 @@
         <v>44881</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51783,7 +51783,7 @@
         <v>45993</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45993</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>46121</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52012,7 +52012,7 @@
         <v>45225</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52085,7 +52085,7 @@
         <v>45993</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52163,7 +52163,7 @@
         <v>44740</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52241,7 +52241,7 @@
         <v>44589</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>46127</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>45999</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>46001</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>46126</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52616,7 +52616,7 @@
         <v>46002</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52689,7 +52689,7 @@
         <v>46127</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52762,7 +52762,7 @@
         <v>46001</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52840,7 +52840,7 @@
         <v>46128</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52913,7 +52913,7 @@
         <v>46132</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>44957</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53064,7 +53064,7 @@
         <v>44832</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>46132</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53215,7 +53215,7 @@
         <v>46002</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53288,7 +53288,7 @@
         <v>46128</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53361,7 +53361,7 @@
         <v>46133</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53439,7 +53439,7 @@
         <v>44741</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53517,7 +53517,7 @@
         <v>46134</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53595,7 +53595,7 @@
         <v>45420</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53668,7 +53668,7 @@
         <v>44979</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53741,7 +53741,7 @@
         <v>46006</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53814,7 +53814,7 @@
         <v>46006</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53887,7 +53887,7 @@
         <v>46003</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53965,7 +53965,7 @@
         <v>46003</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54038,7 +54038,7 @@
         <v>46008</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>44637</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54194,7 +54194,7 @@
         <v>46007</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54267,7 +54267,7 @@
         <v>46008</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54345,7 +54345,7 @@
         <v>44623</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54423,7 +54423,7 @@
         <v>46135</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54501,7 +54501,7 @@
         <v>45162</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54579,7 +54579,7 @@
         <v>44946</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54652,7 +54652,7 @@
         <v>46136</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54725,7 +54725,7 @@
         <v>46010</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54803,7 +54803,7 @@
         <v>45674</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54876,7 +54876,7 @@
         <v>46010</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>46009</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55022,7 +55022,7 @@
         <v>45450</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55095,7 +55095,7 @@
         <v>46010</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45883</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55241,7 +55241,7 @@
         <v>45721</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55314,7 +55314,7 @@
         <v>45204</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55392,7 +55392,7 @@
         <v>44623</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55465,7 +55465,7 @@
         <v>45875</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55538,7 +55538,7 @@
         <v>45831</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55611,7 +55611,7 @@
         <v>46024</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55684,7 +55684,7 @@
         <v>45226</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55757,7 +55757,7 @@
         <v>45749</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55830,7 +55830,7 @@
         <v>45041</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55908,7 +55908,7 @@
         <v>45477</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55981,7 +55981,7 @@
         <v>45106</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56054,7 +56054,7 @@
         <v>46030</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56127,7 +56127,7 @@
         <v>45665</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56200,7 +56200,7 @@
         <v>44511</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56273,7 +56273,7 @@
         <v>45153</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56346,7 +56346,7 @@
         <v>46029</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56424,7 +56424,7 @@
         <v>46140</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56497,7 +56497,7 @@
         <v>45448</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>46031</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56643,7 +56643,7 @@
         <v>46034</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56716,7 +56716,7 @@
         <v>46034</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56789,7 +56789,7 @@
         <v>46034</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56862,7 +56862,7 @@
         <v>46034</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56935,7 +56935,7 @@
         <v>45162</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45600</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57086,7 +57086,7 @@
         <v>45824</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57164,7 +57164,7 @@
         <v>46035</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57242,7 +57242,7 @@
         <v>46036</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57315,7 +57315,7 @@
         <v>44923</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57388,7 +57388,7 @@
         <v>46036</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57461,7 +57461,7 @@
         <v>46036</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57534,7 +57534,7 @@
         <v>46036</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57607,7 +57607,7 @@
         <v>46036</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>46036</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57753,7 +57753,7 @@
         <v>44963</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57826,7 +57826,7 @@
         <v>46031</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57899,7 +57899,7 @@
         <v>46036</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57972,7 +57972,7 @@
         <v>45566</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>46036</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58118,7 +58118,7 @@
         <v>45982</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58196,7 +58196,7 @@
         <v>45007</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58269,7 +58269,7 @@
         <v>46044</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58342,7 +58342,7 @@
         <v>45592</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>45336</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58488,7 +58488,7 @@
         <v>46133</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58561,7 +58561,7 @@
         <v>44643</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58639,7 +58639,7 @@
         <v>45406</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45902</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58790,7 +58790,7 @@
         <v>46044</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58863,7 +58863,7 @@
         <v>44978</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58936,7 +58936,7 @@
         <v>45757</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59009,7 +59009,7 @@
         <v>44911</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59082,7 +59082,7 @@
         <v>46034</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59155,7 +59155,7 @@
         <v>45231</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59228,7 +59228,7 @@
         <v>45538</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59301,7 +59301,7 @@
         <v>45597</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45609</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59452,7 +59452,7 @@
         <v>44938</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>44501</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59603,7 +59603,7 @@
         <v>45792</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59676,7 +59676,7 @@
         <v>45749</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59754,7 +59754,7 @@
         <v>45654</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59827,7 +59827,7 @@
         <v>46142</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59905,7 +59905,7 @@
         <v>45485</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59983,7 +59983,7 @@
         <v>45470</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60061,7 +60061,7 @@
         <v>45510</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>45266</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60212,7 +60212,7 @@
         <v>46055</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60290,7 +60290,7 @@
         <v>46059</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60363,7 +60363,7 @@
         <v>46059</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60436,7 +60436,7 @@
         <v>46059</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         <v>46059</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60582,7 +60582,7 @@
         <v>45841</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60660,7 +60660,7 @@
         <v>46146</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60738,7 +60738,7 @@
         <v>46064</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60811,7 +60811,7 @@
         <v>46064</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60884,7 +60884,7 @@
         <v>46148</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60962,7 +60962,7 @@
         <v>46066</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61035,7 +61035,7 @@
         <v>45817</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61113,7 +61113,7 @@
         <v>46149</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61191,7 +61191,7 @@
         <v>46070</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61264,7 +61264,7 @@
         <v>46149</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         <v>46153</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61415,7 +61415,7 @@
         <v>46073</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61488,7 +61488,7 @@
         <v>46073</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61566,7 +61566,7 @@
         <v>46073</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61639,7 +61639,7 @@
         <v>45874</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61712,7 +61712,7 @@
         <v>46085</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61785,7 +61785,7 @@
         <v>46073</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61863,7 +61863,7 @@
         <v>46160</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61941,7 +61941,7 @@
         <v>46160</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62019,7 +62019,7 @@
         <v>46160</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62097,7 +62097,7 @@
         <v>46093</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62170,7 +62170,7 @@
         <v>46092</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62243,7 +62243,7 @@
         <v>46093</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62316,7 +62316,7 @@
         <v>46093</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62389,7 +62389,7 @@
         <v>45874</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62462,7 +62462,7 @@
         <v>46092</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62535,7 +62535,7 @@
         <v>46174</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62608,7 +62608,7 @@
         <v>46177</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62686,7 +62686,7 @@
         <v>46189</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62764,7 +62764,7 @@
         <v>46189</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62842,7 +62842,7 @@
         <v>46029</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62920,7 +62920,7 @@
         <v>46202</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62998,7 +62998,7 @@
         <v>46205</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63071,7 +63071,7 @@
         <v>46204</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63144,7 +63144,7 @@
         <v>46211</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63222,7 +63222,7 @@
         <v>46211</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63300,7 +63300,7 @@
         <v>46267</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63373,7 +63373,7 @@
         <v>46272</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63451,7 +63451,7 @@
         <v>46272</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63529,7 +63529,7 @@
         <v>46272</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63607,7 +63607,7 @@
         <v>46226</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63680,7 +63680,7 @@
         <v>46272</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63758,7 +63758,7 @@
         <v>46231</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63836,7 +63836,7 @@
         <v>46274</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63914,7 +63914,7 @@
         <v>46274</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63987,7 +63987,7 @@
         <v>46274</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64060,7 +64060,7 @@
         <v>46275</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64138,7 +64138,7 @@
         <v>46275</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64216,7 +64216,7 @@
         <v>46280</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64294,7 +64294,7 @@
         <v>46275</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64372,7 +64372,7 @@
         <v>46239</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64445,7 +64445,7 @@
         <v>46282</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64523,7 +64523,7 @@
         <v>46239</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64596,7 +64596,7 @@
         <v>46283</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64674,7 +64674,7 @@
         <v>46287</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64747,7 +64747,7 @@
         <v>46287</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64825,7 +64825,7 @@
         <v>46245</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64898,7 +64898,7 @@
         <v>46288</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64976,7 +64976,7 @@
         <v>46244</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65049,7 +65049,7 @@
         <v>46245</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65122,7 +65122,7 @@
         <v>46247</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65195,7 +65195,7 @@
         <v>45720</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65268,7 +65268,7 @@
         <v>46246</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65341,7 +65341,7 @@
         <v>46289</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65419,7 +65419,7 @@
         <v>46287</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65497,7 +65497,7 @@
         <v>45720</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65570,7 +65570,7 @@
         <v>46296</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65643,7 +65643,7 @@
         <v>46296</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65716,7 +65716,7 @@
         <v>46295</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65794,7 +65794,7 @@
         <v>45709</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65867,7 +65867,7 @@
         <v>46126</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65940,7 +65940,7 @@
         <v>45726</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -66013,7 +66013,7 @@
         <v>46259</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66091,7 +66091,7 @@
         <v>46301</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66169,7 +66169,7 @@
         <v>46302</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66247,7 +66247,7 @@
         <v>46297</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66320,7 +66320,7 @@
         <v>46297</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66393,7 +66393,7 @@
         <v>46303</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66466,7 +66466,7 @@
         <v>44722</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66544,7 +66544,7 @@
         <v>44684</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66622,7 +66622,7 @@
         <v>45371</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66695,7 +66695,7 @@
         <v>45699</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66773,7 +66773,7 @@
         <v>45756</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66851,7 +66851,7 @@
         <v>45778</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66924,7 +66924,7 @@
         <v>45342</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66997,7 +66997,7 @@
         <v>46089</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67075,7 +67075,7 @@
         <v>46072</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67153,7 +67153,7 @@
         <v>46171</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>

--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -601,7 +601,7 @@
         <v>46057</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>46070</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44722</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46205</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46033</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>46184</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45092</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>46181</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>46033</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45016</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>44637</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45812</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>46140</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>46178</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>46205</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>45785</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>46157</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45775</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45917</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>46069</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>46191</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45897</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>46055</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45469</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45016</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>46089</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>45533</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>46196</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>46178</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>46178</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45932</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>46033</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>46196</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>46104</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>45510</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>45695</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>46055</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>45016</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>44610</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>45938</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>46055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>44090</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>45099</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>45583</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>45775</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>46178</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>46055</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>46190</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>46029</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>45839</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>44722</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>45971</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>46055</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>46092</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>45799</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>45754</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>45903</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>45181</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>46093</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>44796</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>45713</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>44725</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>46258</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>45443</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>45315</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44589</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>45903</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44704</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>44741</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>45895</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>45925</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>44936</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>45995</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>44501</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>46164</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>45714</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44641</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>45233</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>45831</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>45831</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>44722</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>44721</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>44867</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>44910</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>45705</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>45623</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>45461</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>45119</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>45824</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>44523</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>45246</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>45957</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>45971</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45188</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>46029</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45053</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>45187</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>45631</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>45538</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>46274</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>44944</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>45247</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>45713</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>46287</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>45461</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>46290</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>45053</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>46266</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>45411</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>44637</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         <v>44512</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>44489</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>44508</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>44537</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>44511</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>44712</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44852</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44733</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>44811</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>44756</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>44887</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>44696</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>44616</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>44503</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>44588</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44809</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>44602</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44533</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>44529</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>44501</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>44613</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>44540</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44701</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>44721</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>44557</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>44547</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>44802</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>44512</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44886</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>44739</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>44721</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>44743</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>44743</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>44616</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>44811</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>44839</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>44544</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>44749</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>44858</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>44501</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>44600</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44603</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>44743</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>44811</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>44811</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>45632</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>45645</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>44978</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>45674</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>45007</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45244</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45519</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>44900</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44515</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>45713</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>45252</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>45191</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>45769</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>44599</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>44894</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45093</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>45636</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45162</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18860,7 +18860,7 @@
         <v>45644</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>44832</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45237</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>45245</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>45225</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>45747</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>45677</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>45559</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>45453</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>45089</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>45629</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>45592</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>45727</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>45761</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>44896</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>45202</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>45659</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         <v>45191</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20179,7 +20179,7 @@
         <v>45152</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44928</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44903</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>44946</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20476,7 +20476,7 @@
         <v>44739</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>44741</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>45071</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>45231</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>44903</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>44931</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>45204</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>44938</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>45530</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>44804</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45461</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>45072</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>44677</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>45238</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45037</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>45428</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>45541</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>45219</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         <v>44897</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>45477</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>45121</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>44886</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>44881</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>45677</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
         <v>45229</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45672</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45036</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>44860</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>45541</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>45204</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45204</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45642</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45714</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>45692</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>45541</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45203</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45534</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45763</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>45198</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>45608</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45525</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>45257</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45257</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>45575</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>44911</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>45622</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>45243</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>45007</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>45883</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>45757</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>45488</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>45547</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         <v>45609</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>46136</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>45237</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>45237</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>45712</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>45448</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>45875</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
         <v>45831</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24951,7 +24951,7 @@
         <v>45902</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>45728</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45153</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>45714</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>45749</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45891</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>45891</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>44637</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>45891</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25633,7 +25633,7 @@
         <v>45890</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>45890</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>45891</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>45892</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>45895</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>45894</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>45642</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26164,7 +26164,7 @@
         <v>45211</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>45898</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>46133</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>46031</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>45898</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>44994</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>45252</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26680,7 +26680,7 @@
         <v>45162</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45470</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>45566</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>45775</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>45721</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>45824</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>46140</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>45540</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>45654</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>45901</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>45841</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
         <v>45336</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27576,7 +27576,7 @@
         <v>45665</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>45485</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45600</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>45902</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45902</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>45902</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>45902</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>45904</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>45904</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>45875</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45510</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>45749</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45908</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>45491</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45481</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>45910</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45406</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>45910</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>44697</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>45911</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>46142</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>45090</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>45915</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29315,7 +29315,7 @@
         <v>45079</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>45912</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>45792</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>45266</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>45912</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>45597</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>45769</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>45916</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         <v>45916</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>44881</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>45916</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30123,7 +30123,7 @@
         <v>45511</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>45757</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>45817</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30347,7 +30347,7 @@
         <v>45919</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>44511</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>45919</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30566,7 +30566,7 @@
         <v>45713</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>45713</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>45919</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>46146</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>45925</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>45926</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31009,7 +31009,7 @@
         <v>45926</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>46149</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>46148</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>46149</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>45930</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>45931</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>45931</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>46153</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31623,7 +31623,7 @@
         <v>45931</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>45933</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45933</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>45936</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>45936</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>45936</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32071,7 +32071,7 @@
         <v>45937</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45636</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45937</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>45937</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32373,7 +32373,7 @@
         <v>45939</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45937</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>45937</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>45761</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45930</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>45940</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>45294</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32904,7 +32904,7 @@
         <v>45624</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>45624</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
         <v>45947</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>44903</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33196,7 +33196,7 @@
         <v>45062</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>45931</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>45951</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>45236</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>44740</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>45952</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>45434</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>45952</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>45322</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45874</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>45957</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>45957</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34097,7 +34097,7 @@
         <v>45957</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>45957</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>45957</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>44501</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34409,7 +34409,7 @@
         <v>45957</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34487,7 +34487,7 @@
         <v>44938</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>45460</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>46160</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>45960</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>45960</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>45960</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>45959</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45339</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>45541</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>45965</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45964</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>46160</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>45964</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>45964</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>45964</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>45965</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>45643</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>45301</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>45967</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>45967</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>45965</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36070,7 +36070,7 @@
         <v>45965</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>45971</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>45041</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>46160</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36382,7 +36382,7 @@
         <v>45225</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>45925</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36528,7 +36528,7 @@
         <v>45973</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>45971</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36679,7 +36679,7 @@
         <v>45972</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>45972</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36825,7 +36825,7 @@
         <v>45973</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>45574</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>45974</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37059,7 +37059,7 @@
         <v>44950</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37132,7 +37132,7 @@
         <v>45974</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>45978</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37283,7 +37283,7 @@
         <v>45978</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>45672</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>45567</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37502,7 +37502,7 @@
         <v>45979</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37580,7 +37580,7 @@
         <v>45548</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>45673</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37726,7 +37726,7 @@
         <v>45980</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>45981</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37872,7 +37872,7 @@
         <v>45538</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37945,7 +37945,7 @@
         <v>45980</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38018,7 +38018,7 @@
         <v>45566</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>45106</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38164,7 +38164,7 @@
         <v>44881</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>45580</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45987</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>45987</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>45989</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38534,7 +38534,7 @@
         <v>45989</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>45993</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>45197</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>45992</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45992</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>45993</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45993</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>44897</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39133,7 +39133,7 @@
         <v>45629</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>45450</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>45560</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>45999</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39425,7 +39425,7 @@
         <v>46001</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>45223</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>45439</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>46001</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>44979</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>46003</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>46003</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>45769</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>46002</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40107,7 +40107,7 @@
         <v>45439</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>45163</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>46002</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40336,7 +40336,7 @@
         <v>45727</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40409,7 +40409,7 @@
         <v>45355</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>45525</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>46007</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>46006</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40711,7 +40711,7 @@
         <v>46006</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40784,7 +40784,7 @@
         <v>46008</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>46009</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>46008</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>45646</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41086,7 +41086,7 @@
         <v>46010</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>44508</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>46010</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>46010</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         <v>46174</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45539</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>45187</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>45407</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45679</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41753,7 +41753,7 @@
         <v>46024</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>46029</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>45429</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>46030</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>46031</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>46034</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>46034</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>46035</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>46034</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42425,7 +42425,7 @@
         <v>46034</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>46036</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>46036</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>46036</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>46036</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>46036</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>46036</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>46036</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>46036</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43082,7 +43082,7 @@
         <v>45982</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>46177</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>45449</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>46034</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>46044</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>46044</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45483</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>45560</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>45608</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>45177</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>46055</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43905,7 +43905,7 @@
         <v>46059</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>46059</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>46059</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>46059</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44197,7 +44197,7 @@
         <v>44789</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45294</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45462</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>46064</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45236</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44567,7 +44567,7 @@
         <v>46064</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>45271</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>46066</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44786,7 +44786,7 @@
         <v>46070</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44859,7 +44859,7 @@
         <v>46073</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>46073</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>46073</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>46073</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>44978</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>44981</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45312,7 +45312,7 @@
         <v>46189</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>44495</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>45215</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>46085</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>46029</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>46189</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>44725</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45848,7 +45848,7 @@
         <v>44546</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45921,7 +45921,7 @@
         <v>45757</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45994,7 +45994,7 @@
         <v>44908</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46072,7 +46072,7 @@
         <v>46092</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>46092</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45874</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46291,7 +46291,7 @@
         <v>46093</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>44907</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>46093</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>44963</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>45149</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>46093</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45168</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45624</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45335</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>45621</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47026,7 +47026,7 @@
         <v>46098</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>46100</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>45509</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>46104</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47318,7 +47318,7 @@
         <v>44862</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47391,7 +47391,7 @@
         <v>45097</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>45614</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>44795</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47610,7 +47610,7 @@
         <v>45491</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47683,7 +47683,7 @@
         <v>44923</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>44923</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47829,7 +47829,7 @@
         <v>44923</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>45177</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>46107</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>44938</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48121,7 +48121,7 @@
         <v>44782</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45188</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48272,7 +48272,7 @@
         <v>45188</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48345,7 +48345,7 @@
         <v>44928</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>45252</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>46121</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>46126</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>45321</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
         <v>45670</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48798,7 +48798,7 @@
         <v>45225</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>45267</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48944,7 +48944,7 @@
         <v>45574</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49022,7 +49022,7 @@
         <v>45621</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49095,7 +49095,7 @@
         <v>46128</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>46128</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>45642</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49314,7 +49314,7 @@
         <v>46127</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>46127</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>46202</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>46133</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49616,7 +49616,7 @@
         <v>46132</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>46132</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49772,7 +49772,7 @@
         <v>45226</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>45483</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>46135</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50001,7 +50001,7 @@
         <v>45642</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45503</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50152,7 +50152,7 @@
         <v>45072</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>45195</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>44523</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50381,7 +50381,7 @@
         <v>45204</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
         <v>46204</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50532,7 +50532,7 @@
         <v>46134</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45106</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>45583</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50766,7 +50766,7 @@
         <v>46205</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50839,7 +50839,7 @@
         <v>45244</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50912,7 +50912,7 @@
         <v>45597</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50985,7 +50985,7 @@
         <v>45246</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>45645</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51131,7 +51131,7 @@
         <v>45775</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51204,7 +51204,7 @@
         <v>45483</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51277,7 +51277,7 @@
         <v>45756</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51355,7 +51355,7 @@
         <v>46211</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>46211</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>45665</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51584,7 +51584,7 @@
         <v>45672</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51657,7 +51657,7 @@
         <v>45077</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51730,7 +51730,7 @@
         <v>45391</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51803,7 +51803,7 @@
         <v>45231</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>44837</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>45225</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>44888</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52105,7 +52105,7 @@
         <v>44643</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52183,7 +52183,7 @@
         <v>45531</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52261,7 +52261,7 @@
         <v>45769</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52334,7 +52334,7 @@
         <v>45355</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52407,7 +52407,7 @@
         <v>45072</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52485,7 +52485,7 @@
         <v>46226</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52558,7 +52558,7 @@
         <v>45118</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52631,7 +52631,7 @@
         <v>44540</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52709,7 +52709,7 @@
         <v>46272</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52787,7 +52787,7 @@
         <v>45078</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52865,7 +52865,7 @@
         <v>46272</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52943,7 +52943,7 @@
         <v>46272</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>46272</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53099,7 +53099,7 @@
         <v>45215</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53172,7 +53172,7 @@
         <v>45034</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53245,7 +53245,7 @@
         <v>46274</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53318,7 +53318,7 @@
         <v>45579</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>46274</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53469,7 +53469,7 @@
         <v>46275</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>46274</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53625,7 +53625,7 @@
         <v>46275</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53703,7 +53703,7 @@
         <v>44923</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53776,7 +53776,7 @@
         <v>46231</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53854,7 +53854,7 @@
         <v>45639</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53927,7 +53927,7 @@
         <v>45456</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54005,7 +54005,7 @@
         <v>44623</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54083,7 +54083,7 @@
         <v>45446</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54161,7 +54161,7 @@
         <v>45272</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54234,7 +54234,7 @@
         <v>44914</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54307,7 +54307,7 @@
         <v>45201</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54380,7 +54380,7 @@
         <v>45430</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54453,7 +54453,7 @@
         <v>46275</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45034</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54604,7 +54604,7 @@
         <v>46280</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54682,7 +54682,7 @@
         <v>45257</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54755,7 +54755,7 @@
         <v>44916</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54828,7 +54828,7 @@
         <v>44589</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54906,7 +54906,7 @@
         <v>45646</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54979,7 +54979,7 @@
         <v>46239</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55052,7 +55052,7 @@
         <v>46239</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55125,7 +55125,7 @@
         <v>46283</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55203,7 +55203,7 @@
         <v>45128</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55281,7 +55281,7 @@
         <v>46282</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>45245</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55432,7 +55432,7 @@
         <v>45684</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55505,7 +55505,7 @@
         <v>45072</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55578,7 +55578,7 @@
         <v>45238</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55651,7 +55651,7 @@
         <v>46287</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>45476</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55797,7 +55797,7 @@
         <v>46244</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55870,7 +55870,7 @@
         <v>45187</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45561</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56016,7 +56016,7 @@
         <v>46287</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56094,7 +56094,7 @@
         <v>45355</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56167,7 +56167,7 @@
         <v>45355</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>45301</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56313,7 +56313,7 @@
         <v>45623</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56386,7 +56386,7 @@
         <v>45636</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         <v>46245</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56532,7 +56532,7 @@
         <v>46245</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56605,7 +56605,7 @@
         <v>45303</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56678,7 +56678,7 @@
         <v>45271</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56751,7 +56751,7 @@
         <v>44623</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56824,7 +56824,7 @@
         <v>45420</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56897,7 +56897,7 @@
         <v>46288</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56975,7 +56975,7 @@
         <v>46246</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57048,7 +57048,7 @@
         <v>45194</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57121,7 +57121,7 @@
         <v>45204</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57199,7 +57199,7 @@
         <v>45089</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>46289</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57355,7 +57355,7 @@
         <v>44791</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57433,7 +57433,7 @@
         <v>45027</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57506,7 +57506,7 @@
         <v>45720</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57579,7 +57579,7 @@
         <v>45720</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57652,7 +57652,7 @@
         <v>45054</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57725,7 +57725,7 @@
         <v>45749</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57798,7 +57798,7 @@
         <v>46247</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57871,7 +57871,7 @@
         <v>44950</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>46287</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58022,7 +58022,7 @@
         <v>45491</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58100,7 +58100,7 @@
         <v>45293</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58173,7 +58173,7 @@
         <v>45432</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58246,7 +58246,7 @@
         <v>45638</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58319,7 +58319,7 @@
         <v>45175</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58392,7 +58392,7 @@
         <v>44928</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58465,7 +58465,7 @@
         <v>45517</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58538,7 +58538,7 @@
         <v>45226</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58611,7 +58611,7 @@
         <v>45053</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58684,7 +58684,7 @@
         <v>46295</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58762,7 +58762,7 @@
         <v>45175</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58835,7 +58835,7 @@
         <v>45442</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58908,7 +58908,7 @@
         <v>46296</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58981,7 +58981,7 @@
         <v>46296</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>45041</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59127,7 +59127,7 @@
         <v>45547</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59200,7 +59200,7 @@
         <v>45301</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59273,7 +59273,7 @@
         <v>44512</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59351,7 +59351,7 @@
         <v>45726</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59424,7 +59424,7 @@
         <v>45709</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59497,7 +59497,7 @@
         <v>45119</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59570,7 +59570,7 @@
         <v>44957</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59643,7 +59643,7 @@
         <v>46301</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59721,7 +59721,7 @@
         <v>46126</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59794,7 +59794,7 @@
         <v>45482</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59872,7 +59872,7 @@
         <v>45525</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59945,7 +59945,7 @@
         <v>45455</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60023,7 +60023,7 @@
         <v>44911</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60096,7 +60096,7 @@
         <v>44641</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60174,7 +60174,7 @@
         <v>45399</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60247,7 +60247,7 @@
         <v>45054</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60325,7 +60325,7 @@
         <v>46297</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60398,7 +60398,7 @@
         <v>46297</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60471,7 +60471,7 @@
         <v>46303</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60544,7 +60544,7 @@
         <v>46259</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60622,7 +60622,7 @@
         <v>46302</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60700,7 +60700,7 @@
         <v>45789</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60778,7 +60778,7 @@
         <v>45195</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60851,7 +60851,7 @@
         <v>45712</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60924,7 +60924,7 @@
         <v>45488</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61002,7 +61002,7 @@
         <v>45036</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61075,7 +61075,7 @@
         <v>45229</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61153,7 +61153,7 @@
         <v>45020</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61226,7 +61226,7 @@
         <v>45797</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61304,7 +61304,7 @@
         <v>44923</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61377,7 +61377,7 @@
         <v>45540</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61450,7 +61450,7 @@
         <v>45797</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61528,7 +61528,7 @@
         <v>45797</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61601,7 +61601,7 @@
         <v>45797</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61679,7 +61679,7 @@
         <v>45188</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61752,7 +61752,7 @@
         <v>45799</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61825,7 +61825,7 @@
         <v>45800</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61903,7 +61903,7 @@
         <v>45800</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61981,7 +61981,7 @@
         <v>45747</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62059,7 +62059,7 @@
         <v>45805</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62137,7 +62137,7 @@
         <v>45804</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62215,7 +62215,7 @@
         <v>45804</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62288,7 +62288,7 @@
         <v>45805</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62366,7 +62366,7 @@
         <v>45804</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62439,7 +62439,7 @@
         <v>45747</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62512,7 +62512,7 @@
         <v>46307</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62585,7 +62585,7 @@
         <v>45807</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62658,7 +62658,7 @@
         <v>45807</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62731,7 +62731,7 @@
         <v>46308</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62804,7 +62804,7 @@
         <v>45810</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62877,7 +62877,7 @@
         <v>46267</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62950,7 +62950,7 @@
         <v>45322</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63023,7 +63023,7 @@
         <v>45817</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63101,7 +63101,7 @@
         <v>45740</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63174,7 +63174,7 @@
         <v>45818</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63247,7 +63247,7 @@
         <v>45762</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63320,7 +63320,7 @@
         <v>45818</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63393,7 +63393,7 @@
         <v>45818</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63466,7 +63466,7 @@
         <v>45749</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63539,7 +63539,7 @@
         <v>45820</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63612,7 +63612,7 @@
         <v>45821</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63690,7 +63690,7 @@
         <v>45821</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63768,7 +63768,7 @@
         <v>45821</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63846,7 +63846,7 @@
         <v>45824</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63919,7 +63919,7 @@
         <v>45824</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63992,7 +63992,7 @@
         <v>45827</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64065,7 +64065,7 @@
         <v>45831</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64143,7 +64143,7 @@
         <v>45831</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64221,7 +64221,7 @@
         <v>45833</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64299,7 +64299,7 @@
         <v>45832</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64377,7 +64377,7 @@
         <v>45833</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64455,7 +64455,7 @@
         <v>45832</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64533,7 +64533,7 @@
         <v>45835</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64606,7 +64606,7 @@
         <v>45838</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64679,7 +64679,7 @@
         <v>45839</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64752,7 +64752,7 @@
         <v>45838</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64830,7 +64830,7 @@
         <v>45839</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64903,7 +64903,7 @@
         <v>45840</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64976,7 +64976,7 @@
         <v>45841</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65049,7 +65049,7 @@
         <v>45840</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65127,7 +65127,7 @@
         <v>45841</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65200,7 +65200,7 @@
         <v>45841</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65278,7 +65278,7 @@
         <v>45841</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65356,7 +65356,7 @@
         <v>45841</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65434,7 +65434,7 @@
         <v>45842</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65507,7 +65507,7 @@
         <v>45357</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65580,7 +65580,7 @@
         <v>45846</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65653,7 +65653,7 @@
         <v>45849</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65726,7 +65726,7 @@
         <v>45849</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65799,7 +65799,7 @@
         <v>45849</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65872,7 +65872,7 @@
         <v>45853</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65950,7 +65950,7 @@
         <v>45855</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -66028,7 +66028,7 @@
         <v>45855</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66101,7 +66101,7 @@
         <v>45867</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66174,7 +66174,7 @@
         <v>45694</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66247,7 +66247,7 @@
         <v>45880</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66320,7 +66320,7 @@
         <v>45880</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66393,7 +66393,7 @@
         <v>45880</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66466,7 +66466,7 @@
         <v>45762</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66539,7 +66539,7 @@
         <v>45883</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66612,7 +66612,7 @@
         <v>44722</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66690,7 +66690,7 @@
         <v>45371</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66763,7 +66763,7 @@
         <v>44684</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66841,7 +66841,7 @@
         <v>45699</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66919,7 +66919,7 @@
         <v>45756</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66997,7 +66997,7 @@
         <v>45778</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67070,7 +67070,7 @@
         <v>45342</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67143,7 +67143,7 @@
         <v>46089</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67221,7 +67221,7 @@
         <v>46072</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67299,7 +67299,7 @@
         <v>46171</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>

--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -601,7 +601,7 @@
         <v>46057</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>46070</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44722</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46205</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46033</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>46184</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45092</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>46181</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>46033</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45016</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>44637</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45812</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>46140</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>46178</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>46205</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>45785</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>46157</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45775</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45917</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>46069</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>46191</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45897</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>46055</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45469</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45016</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>46089</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>45533</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>46196</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>46178</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>46178</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45932</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>46033</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>46196</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>46104</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>45510</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>45695</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>46055</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>45016</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>44610</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>45938</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>46055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>44090</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>45099</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>45583</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>45775</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>46178</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>46055</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>46190</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>46029</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>45839</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>44722</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>45971</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>46055</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>46092</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>45799</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>45754</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>45903</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>45181</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>46093</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>44796</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>45713</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>44725</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>46258</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>45443</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>45315</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44589</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>45903</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>44704</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>44741</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>45895</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>45925</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>44936</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>45995</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>44501</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>46164</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>45714</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44641</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>45233</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>45831</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>45831</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>44722</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>44721</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>44867</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>44910</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>45705</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>45623</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>45461</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>45119</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>45824</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>44523</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>45246</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>45957</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>45971</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45188</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>46029</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45053</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>45187</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>45631</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>45538</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>46274</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>44944</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>45247</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>45713</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>46287</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>45461</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>46290</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>45053</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>46266</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>45411</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>44637</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         <v>44512</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>44489</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>44508</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>44537</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>44511</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>44712</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44852</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44733</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>44811</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>44756</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>44887</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>44696</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>44616</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>44503</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>44588</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44809</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>44602</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44533</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>44529</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>44501</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>44613</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>44540</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44701</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>44721</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>44557</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>44547</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>44802</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>44512</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44886</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>44739</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>44721</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>44743</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>44743</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>44616</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>44811</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>44839</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>44544</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>44749</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>44858</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>44501</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>44600</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44603</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>44743</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>44811</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>44811</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>45632</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>45645</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>44978</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>45674</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>45007</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45244</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45519</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>44900</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44515</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>45713</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>45252</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>45191</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>45769</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>44599</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>44894</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45093</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>45636</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45162</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18860,7 +18860,7 @@
         <v>45644</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>44832</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45237</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>45245</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>45225</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>45747</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>45677</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>45559</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>45453</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>45089</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>45629</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>45592</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>45727</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>45761</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>44896</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>45202</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>45659</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         <v>45191</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20179,7 +20179,7 @@
         <v>45152</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44928</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44903</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>44946</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20476,7 +20476,7 @@
         <v>44739</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>44741</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>45071</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>45231</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>44903</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>44931</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>45204</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>44938</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>45530</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>44804</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45461</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>45072</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>44677</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>45238</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45037</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>45428</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>45541</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>45219</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         <v>44897</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>45477</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>45121</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>44886</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>44881</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>45677</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
         <v>45229</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45672</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45036</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>44860</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>45541</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>45204</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45204</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45642</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45714</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>45692</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>45541</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45203</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45534</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45763</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>45198</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>45608</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45525</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>45257</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45257</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>45575</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>44911</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>45622</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>45243</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>45007</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>45883</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>45757</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>45488</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>45547</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         <v>45609</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>46136</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>45237</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>45237</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>45712</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>45448</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>45875</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
         <v>45831</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24951,7 +24951,7 @@
         <v>45902</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>45728</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45153</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>45714</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>45749</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45891</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>45891</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>44637</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>45891</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25633,7 +25633,7 @@
         <v>45890</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>45890</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>45891</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>45892</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>45895</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>45894</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>45642</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26164,7 +26164,7 @@
         <v>45211</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>45898</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>46133</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>46031</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>45898</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>44994</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>45252</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26680,7 +26680,7 @@
         <v>45162</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45470</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>45566</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>45775</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>45721</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>45824</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>46140</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>45540</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>45654</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>45901</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>45841</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
         <v>45336</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27576,7 +27576,7 @@
         <v>45665</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>45485</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45600</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>45902</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45902</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>45902</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>45902</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>45904</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>45904</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>45875</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45510</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>45749</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45908</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>45491</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45481</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>45910</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45406</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>45910</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>44697</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>45911</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>46142</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>45090</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>45915</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29315,7 +29315,7 @@
         <v>45079</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>45912</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>45792</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>45266</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>45912</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>45597</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>45769</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>45916</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         <v>45916</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>44881</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>45916</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30123,7 +30123,7 @@
         <v>45511</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>45757</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>45817</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30347,7 +30347,7 @@
         <v>45919</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>44511</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>45919</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30566,7 +30566,7 @@
         <v>45713</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>45713</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>45919</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>46146</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>45925</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>45926</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31009,7 +31009,7 @@
         <v>45926</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>46149</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>46148</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>46149</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>45930</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>45931</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>45931</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>46153</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31623,7 +31623,7 @@
         <v>45931</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>45933</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45933</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>45936</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>45936</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>45936</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32071,7 +32071,7 @@
         <v>45937</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45636</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45937</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>45937</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32373,7 +32373,7 @@
         <v>45939</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45937</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>45937</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>45761</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45930</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>45940</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>45294</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32904,7 +32904,7 @@
         <v>45624</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>45624</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
         <v>45947</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>44903</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33196,7 +33196,7 @@
         <v>45062</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>45931</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>45951</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>45236</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>44740</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>45952</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>45434</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>45952</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>45322</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45874</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>45957</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>45957</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34097,7 +34097,7 @@
         <v>45957</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>45957</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>45957</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>44501</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34409,7 +34409,7 @@
         <v>45957</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34487,7 +34487,7 @@
         <v>44938</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>45460</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>46160</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>45960</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>45960</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>45960</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>45959</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45339</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>45541</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>45965</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45964</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>46160</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>45964</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>45964</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>45964</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>45965</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>45643</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>45301</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>45967</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>45967</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>45965</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36070,7 +36070,7 @@
         <v>45965</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>45971</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>45041</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>46160</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36382,7 +36382,7 @@
         <v>45225</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>45925</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36528,7 +36528,7 @@
         <v>45973</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>45971</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36679,7 +36679,7 @@
         <v>45972</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>45972</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36825,7 +36825,7 @@
         <v>45973</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>45574</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>45974</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37059,7 +37059,7 @@
         <v>44950</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37132,7 +37132,7 @@
         <v>45974</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>45978</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37283,7 +37283,7 @@
         <v>45978</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>45672</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>45567</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37502,7 +37502,7 @@
         <v>45979</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37580,7 +37580,7 @@
         <v>45548</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>45673</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37726,7 +37726,7 @@
         <v>45980</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>45981</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37872,7 +37872,7 @@
         <v>45538</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37945,7 +37945,7 @@
         <v>45980</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38018,7 +38018,7 @@
         <v>45566</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>45106</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38164,7 +38164,7 @@
         <v>44881</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>45580</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45987</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>45987</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>45989</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38534,7 +38534,7 @@
         <v>45989</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>45993</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>45197</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>45992</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45992</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>45993</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45993</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>44897</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39133,7 +39133,7 @@
         <v>45629</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>45450</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>45560</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>45999</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39425,7 +39425,7 @@
         <v>46001</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>45223</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>45439</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>46001</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>44979</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>46003</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>46003</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>45769</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>46002</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40107,7 +40107,7 @@
         <v>45439</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>45163</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>46002</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40336,7 +40336,7 @@
         <v>45727</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40409,7 +40409,7 @@
         <v>45355</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>45525</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>46007</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>46006</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40711,7 +40711,7 @@
         <v>46006</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40784,7 +40784,7 @@
         <v>46008</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>46009</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>46008</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>45646</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41086,7 +41086,7 @@
         <v>46010</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>44508</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>46010</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>46010</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         <v>46174</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45539</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>45187</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>45407</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45679</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41753,7 +41753,7 @@
         <v>46024</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>46029</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>45429</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>46030</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>46031</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>46034</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>46034</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>46035</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>46034</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42425,7 +42425,7 @@
         <v>46034</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>46036</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>46036</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>46036</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>46036</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>46036</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>46036</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>46036</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>46036</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43082,7 +43082,7 @@
         <v>45982</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>46177</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>45449</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>46034</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>46044</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>46044</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45483</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>45560</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>45608</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>45177</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>46055</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43905,7 +43905,7 @@
         <v>46059</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>46059</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>46059</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>46059</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44197,7 +44197,7 @@
         <v>44789</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45294</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45462</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>46064</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45236</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44567,7 +44567,7 @@
         <v>46064</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>45271</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>46066</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44786,7 +44786,7 @@
         <v>46070</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44859,7 +44859,7 @@
         <v>46073</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>46073</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>46073</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>46073</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>44978</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>44981</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45312,7 +45312,7 @@
         <v>46189</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>44495</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>45215</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>46085</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>46029</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>46189</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>44725</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45848,7 +45848,7 @@
         <v>44546</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45921,7 +45921,7 @@
         <v>45757</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45994,7 +45994,7 @@
         <v>44908</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46072,7 +46072,7 @@
         <v>46092</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>46092</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45874</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46291,7 +46291,7 @@
         <v>46093</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>44907</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>46093</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>44963</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>45149</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>46093</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45168</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45624</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45335</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>45621</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47026,7 +47026,7 @@
         <v>46098</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>46100</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>45509</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>46104</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47318,7 +47318,7 @@
         <v>44862</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47391,7 +47391,7 @@
         <v>45097</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>45614</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>44795</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47610,7 +47610,7 @@
         <v>45491</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47683,7 +47683,7 @@
         <v>44923</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>44923</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47829,7 +47829,7 @@
         <v>44923</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>45177</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>46107</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>44938</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48121,7 +48121,7 @@
         <v>44782</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45188</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48272,7 +48272,7 @@
         <v>45188</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48345,7 +48345,7 @@
         <v>44928</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>45252</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>46121</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>46126</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>45321</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
         <v>45670</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48798,7 +48798,7 @@
         <v>45225</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>45267</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48944,7 +48944,7 @@
         <v>45574</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49022,7 +49022,7 @@
         <v>45621</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49095,7 +49095,7 @@
         <v>46128</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>46128</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>45642</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49314,7 +49314,7 @@
         <v>46127</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>46127</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>46202</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>46133</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49616,7 +49616,7 @@
         <v>46132</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>46132</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49772,7 +49772,7 @@
         <v>45226</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>45483</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>46135</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50001,7 +50001,7 @@
         <v>45642</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45503</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50152,7 +50152,7 @@
         <v>45072</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>45195</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>44523</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50381,7 +50381,7 @@
         <v>45204</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
         <v>46204</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50532,7 +50532,7 @@
         <v>46134</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45106</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>45583</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50766,7 +50766,7 @@
         <v>46205</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50839,7 +50839,7 @@
         <v>45244</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50912,7 +50912,7 @@
         <v>45597</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50985,7 +50985,7 @@
         <v>45246</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>45645</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51131,7 +51131,7 @@
         <v>45775</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51204,7 +51204,7 @@
         <v>45483</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51277,7 +51277,7 @@
         <v>45756</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51355,7 +51355,7 @@
         <v>46211</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>46211</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>45665</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51584,7 +51584,7 @@
         <v>45672</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51657,7 +51657,7 @@
         <v>45077</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51730,7 +51730,7 @@
         <v>45391</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51803,7 +51803,7 @@
         <v>45231</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>44837</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>45225</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>44888</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52105,7 +52105,7 @@
         <v>44643</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52183,7 +52183,7 @@
         <v>45531</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52261,7 +52261,7 @@
         <v>45769</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52334,7 +52334,7 @@
         <v>45355</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52407,7 +52407,7 @@
         <v>45072</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52485,7 +52485,7 @@
         <v>46226</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52558,7 +52558,7 @@
         <v>45118</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52631,7 +52631,7 @@
         <v>44540</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52709,7 +52709,7 @@
         <v>46272</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52787,7 +52787,7 @@
         <v>45078</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52865,7 +52865,7 @@
         <v>46272</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52943,7 +52943,7 @@
         <v>46272</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>46272</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53099,7 +53099,7 @@
         <v>45215</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53172,7 +53172,7 @@
         <v>45034</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53245,7 +53245,7 @@
         <v>46274</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53318,7 +53318,7 @@
         <v>45579</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>46274</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53469,7 +53469,7 @@
         <v>46275</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>46274</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53625,7 +53625,7 @@
         <v>46275</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53703,7 +53703,7 @@
         <v>44923</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53776,7 +53776,7 @@
         <v>46231</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53854,7 +53854,7 @@
         <v>45639</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53927,7 +53927,7 @@
         <v>45456</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54005,7 +54005,7 @@
         <v>44623</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54083,7 +54083,7 @@
         <v>45446</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54161,7 +54161,7 @@
         <v>45272</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54234,7 +54234,7 @@
         <v>44914</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54307,7 +54307,7 @@
         <v>45201</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54380,7 +54380,7 @@
         <v>45430</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54453,7 +54453,7 @@
         <v>46275</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45034</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54604,7 +54604,7 @@
         <v>46280</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54682,7 +54682,7 @@
         <v>45257</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54755,7 +54755,7 @@
         <v>44916</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54828,7 +54828,7 @@
         <v>44589</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54906,7 +54906,7 @@
         <v>45646</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54979,7 +54979,7 @@
         <v>46239</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55052,7 +55052,7 @@
         <v>46239</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55125,7 +55125,7 @@
         <v>46283</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55203,7 +55203,7 @@
         <v>45128</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55281,7 +55281,7 @@
         <v>46282</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>45245</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55432,7 +55432,7 @@
         <v>45684</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55505,7 +55505,7 @@
         <v>45072</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55578,7 +55578,7 @@
         <v>45238</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55651,7 +55651,7 @@
         <v>46287</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>45476</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55797,7 +55797,7 @@
         <v>46244</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55870,7 +55870,7 @@
         <v>45187</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45561</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56016,7 +56016,7 @@
         <v>46287</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56094,7 +56094,7 @@
         <v>45355</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56167,7 +56167,7 @@
         <v>45355</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>45301</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56313,7 +56313,7 @@
         <v>45623</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56386,7 +56386,7 @@
         <v>45636</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         <v>46245</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56532,7 +56532,7 @@
         <v>46245</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56605,7 +56605,7 @@
         <v>45303</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56678,7 +56678,7 @@
         <v>45271</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56751,7 +56751,7 @@
         <v>44623</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56824,7 +56824,7 @@
         <v>45420</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56897,7 +56897,7 @@
         <v>46288</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56975,7 +56975,7 @@
         <v>46246</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57048,7 +57048,7 @@
         <v>45194</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57121,7 +57121,7 @@
         <v>45204</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57199,7 +57199,7 @@
         <v>45089</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>46289</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57355,7 +57355,7 @@
         <v>44791</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57433,7 +57433,7 @@
         <v>45027</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57506,7 +57506,7 @@
         <v>45720</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57579,7 +57579,7 @@
         <v>45720</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57652,7 +57652,7 @@
         <v>45054</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57725,7 +57725,7 @@
         <v>45749</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57798,7 +57798,7 @@
         <v>46247</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57871,7 +57871,7 @@
         <v>44950</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>46287</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58022,7 +58022,7 @@
         <v>45491</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58100,7 +58100,7 @@
         <v>45293</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58173,7 +58173,7 @@
         <v>45432</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58246,7 +58246,7 @@
         <v>45638</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58319,7 +58319,7 @@
         <v>45175</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58392,7 +58392,7 @@
         <v>44928</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58465,7 +58465,7 @@
         <v>45517</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58538,7 +58538,7 @@
         <v>45226</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58611,7 +58611,7 @@
         <v>45053</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58684,7 +58684,7 @@
         <v>46295</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58762,7 +58762,7 @@
         <v>45175</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58835,7 +58835,7 @@
         <v>45442</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58908,7 +58908,7 @@
         <v>46296</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58981,7 +58981,7 @@
         <v>46296</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>45041</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59127,7 +59127,7 @@
         <v>45547</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59200,7 +59200,7 @@
         <v>45301</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59273,7 +59273,7 @@
         <v>44512</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59351,7 +59351,7 @@
         <v>45726</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59424,7 +59424,7 @@
         <v>45709</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59497,7 +59497,7 @@
         <v>45119</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59570,7 +59570,7 @@
         <v>44957</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59643,7 +59643,7 @@
         <v>46301</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59721,7 +59721,7 @@
         <v>46126</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59794,7 +59794,7 @@
         <v>45482</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59872,7 +59872,7 @@
         <v>45525</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59945,7 +59945,7 @@
         <v>45455</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60023,7 +60023,7 @@
         <v>44911</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60096,7 +60096,7 @@
         <v>44641</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60174,7 +60174,7 @@
         <v>45399</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60247,7 +60247,7 @@
         <v>45054</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60325,7 +60325,7 @@
         <v>46297</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60398,7 +60398,7 @@
         <v>46297</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60471,7 +60471,7 @@
         <v>46303</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60544,7 +60544,7 @@
         <v>46259</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60622,7 +60622,7 @@
         <v>46302</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60700,7 +60700,7 @@
         <v>45789</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60778,7 +60778,7 @@
         <v>45195</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60851,7 +60851,7 @@
         <v>45712</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60924,7 +60924,7 @@
         <v>45488</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61002,7 +61002,7 @@
         <v>45036</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61075,7 +61075,7 @@
         <v>45229</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61153,7 +61153,7 @@
         <v>45020</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61226,7 +61226,7 @@
         <v>45797</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61304,7 +61304,7 @@
         <v>44923</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61377,7 +61377,7 @@
         <v>45540</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61450,7 +61450,7 @@
         <v>45797</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61528,7 +61528,7 @@
         <v>45797</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61601,7 +61601,7 @@
         <v>45797</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61679,7 +61679,7 @@
         <v>45188</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61752,7 +61752,7 @@
         <v>45799</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61825,7 +61825,7 @@
         <v>45800</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61903,7 +61903,7 @@
         <v>45800</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61981,7 +61981,7 @@
         <v>45747</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62059,7 +62059,7 @@
         <v>45805</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62137,7 +62137,7 @@
         <v>45804</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62215,7 +62215,7 @@
         <v>45804</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62288,7 +62288,7 @@
         <v>45805</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62366,7 +62366,7 @@
         <v>45804</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62439,7 +62439,7 @@
         <v>45747</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62512,7 +62512,7 @@
         <v>46307</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62585,7 +62585,7 @@
         <v>45807</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62658,7 +62658,7 @@
         <v>45807</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62731,7 +62731,7 @@
         <v>46308</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62804,7 +62804,7 @@
         <v>45810</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62877,7 +62877,7 @@
         <v>46267</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62950,7 +62950,7 @@
         <v>45322</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63023,7 +63023,7 @@
         <v>45817</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63101,7 +63101,7 @@
         <v>45740</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63174,7 +63174,7 @@
         <v>45818</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63247,7 +63247,7 @@
         <v>45762</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63320,7 +63320,7 @@
         <v>45818</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63393,7 +63393,7 @@
         <v>45818</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63466,7 +63466,7 @@
         <v>45749</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63539,7 +63539,7 @@
         <v>45820</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63612,7 +63612,7 @@
         <v>45821</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63690,7 +63690,7 @@
         <v>45821</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63768,7 +63768,7 @@
         <v>45821</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63846,7 +63846,7 @@
         <v>45824</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63919,7 +63919,7 @@
         <v>45824</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63992,7 +63992,7 @@
         <v>45827</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64065,7 +64065,7 @@
         <v>45831</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64143,7 +64143,7 @@
         <v>45831</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64221,7 +64221,7 @@
         <v>45833</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64299,7 +64299,7 @@
         <v>45832</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64377,7 +64377,7 @@
         <v>45833</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64455,7 +64455,7 @@
         <v>45832</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64533,7 +64533,7 @@
         <v>45835</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64606,7 +64606,7 @@
         <v>45838</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64679,7 +64679,7 @@
         <v>45839</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64752,7 +64752,7 @@
         <v>45838</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64830,7 +64830,7 @@
         <v>45839</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64903,7 +64903,7 @@
         <v>45840</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64976,7 +64976,7 @@
         <v>45841</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65049,7 +65049,7 @@
         <v>45840</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65127,7 +65127,7 @@
         <v>45841</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65200,7 +65200,7 @@
         <v>45841</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65278,7 +65278,7 @@
         <v>45841</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65356,7 +65356,7 @@
         <v>45841</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65434,7 +65434,7 @@
         <v>45842</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65507,7 +65507,7 @@
         <v>45357</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65580,7 +65580,7 @@
         <v>45846</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65653,7 +65653,7 @@
         <v>45849</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65726,7 +65726,7 @@
         <v>45849</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65799,7 +65799,7 @@
         <v>45849</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65872,7 +65872,7 @@
         <v>45853</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65950,7 +65950,7 @@
         <v>45855</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -66028,7 +66028,7 @@
         <v>45855</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66101,7 +66101,7 @@
         <v>45867</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66174,7 +66174,7 @@
         <v>45694</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66247,7 +66247,7 @@
         <v>45880</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66320,7 +66320,7 @@
         <v>45880</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66393,7 +66393,7 @@
         <v>45880</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66466,7 +66466,7 @@
         <v>45762</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66539,7 +66539,7 @@
         <v>45883</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66612,7 +66612,7 @@
         <v>44722</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66690,7 +66690,7 @@
         <v>45371</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66763,7 +66763,7 @@
         <v>44684</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66841,7 +66841,7 @@
         <v>45699</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66919,7 +66919,7 @@
         <v>45756</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66997,7 +66997,7 @@
         <v>45778</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67070,7 +67070,7 @@
         <v>45342</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67143,7 +67143,7 @@
         <v>46089</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67221,7 +67221,7 @@
         <v>46072</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67299,7 +67299,7 @@
         <v>46171</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>

--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -601,7 +601,7 @@
         <v>46057</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>46070</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44722</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46205</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46184</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>46033</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45092</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>46316</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>46181</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>46033</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45016</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>44637</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45812</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>46140</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>46178</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>45785</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>46205</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>44796</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>46157</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45775</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>45917</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>46069</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>46191</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>45897</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>45469</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>46055</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>45016</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>46089</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45533</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>46196</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>46295</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>46316</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45932</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>46178</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>46178</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>46196</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>46104</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>46033</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>46055</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>45510</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>45016</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44610</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45938</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>46055</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>44090</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>44722</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>46178</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>46190</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>45583</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>45099</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45775</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>46055</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>45839</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>46029</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44722</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44810</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>45971</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>45799</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>46055</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>46092</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>45903</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>45713</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>45443</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>46258</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>46093</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>44796</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>44725</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>45181</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>45754</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>44589</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>45315</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>45903</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>44704</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>45895</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>45925</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>45995</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>46164</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>45233</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>45831</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>45831</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>44936</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>44501</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>45714</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>44641</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>44741</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>44722</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>44721</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>45623</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>45957</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>45713</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>45971</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>45461</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>45119</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>44867</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>45053</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>46029</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>46287</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>46290</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>44523</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>45538</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>44910</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>46266</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>45824</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>46274</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>45461</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45705</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>44944</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45631</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>45247</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>45187</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>45188</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>45246</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>45053</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>44637</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>45411</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44512</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>44508</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44537</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>44511</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>44712</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>44852</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>44733</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>44811</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>44756</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>44887</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>44696</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>44616</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>44503</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44588</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>44809</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>44602</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>44533</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>44529</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>44501</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>44613</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>44540</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>44701</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>44721</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>44557</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>44547</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>44802</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44512</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>44886</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>44721</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44739</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44743</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>44743</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>44616</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>44811</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>44839</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44749</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>44544</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>44858</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44501</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>44600</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>44603</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>44743</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>45762</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>44811</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>44811</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45089</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>45187</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         <v>45215</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>44637</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>45890</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>45890</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>45891</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>45891</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45892</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45891</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>45891</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44623</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>45894</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>45162</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>44946</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>45895</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>44725</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45775</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45674</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45883</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>45898</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>45450</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45898</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>45541</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45540</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45902</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>44795</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45902</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45204</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>45902</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45902</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45901</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>44862</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45531</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>44623</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45904</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45904</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45875</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>45908</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45481</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45226</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>46160</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>45910</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>45910</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>45041</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>45477</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>45106</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>45912</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>44511</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>45911</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>45912</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45916</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45915</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>45916</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21962,7 +21962,7 @@
         <v>45916</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>45713</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>44923</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>44963</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
         <v>45919</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22327,7 +22327,7 @@
         <v>45919</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>45919</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>45007</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>45925</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>45926</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>45592</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>45926</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44643</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>45335</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>45930</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>44978</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>45931</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23218,7 +23218,7 @@
         <v>44911</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>45931</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>45231</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>45931</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>45538</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>45933</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>45933</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>45936</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>45252</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>45597</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>45936</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>45936</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>45937</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>44938</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>44501</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24338,7 +24338,7 @@
         <v>45937</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>45937</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>45937</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>45937</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>46174</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>45939</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>45930</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45391</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45072</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>46177</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45321</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>45293</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>44894</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>44928</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>45931</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>44903</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>45267</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>45947</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>45952</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45761</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45951</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>45952</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>45202</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45957</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>45957</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>45957</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>45957</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>45957</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26457,7 +26457,7 @@
         <v>45957</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>45960</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>45301</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>45574</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>45960</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>45959</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>45960</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>45644</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>45670</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>45964</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>45541</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27290,7 +27290,7 @@
         <v>45460</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>45964</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>45964</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>46189</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>45964</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>46189</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>45677</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>44881</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>45965</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>45965</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45965</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>45965</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>45967</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>45257</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>45967</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>45925</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45971</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45665</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45238</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>45971</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45972</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>45972</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>45560</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>45152</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>45974</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>45973</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>45090</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>45072</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>45973</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>45974</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>44515</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45062</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45978</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>45978</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>44931</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29925,7 +29925,7 @@
         <v>45980</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>45339</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45980</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>46202</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>45407</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>44888</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>45979</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>45163</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30524,7 +30524,7 @@
         <v>45981</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>45643</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>45238</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>45430</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>45177</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30889,7 +30889,7 @@
         <v>46205</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>44914</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>46204</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31108,7 +31108,7 @@
         <v>45439</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>45566</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>45692</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>45987</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>45204</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>45987</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>45624</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45624</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45294</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>44897</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>44546</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>45992</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>46211</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>45992</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>46211</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>45989</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>45672</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>45989</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45446</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>45993</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>45993</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>45993</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45432</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45999</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45215</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>46001</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>46002</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33124,7 +33124,7 @@
         <v>46001</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33202,7 +33202,7 @@
         <v>46002</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>46006</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>46006</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>46226</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>46003</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>46231</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>46003</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33723,7 +33723,7 @@
         <v>45525</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>46008</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>45482</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33952,7 +33952,7 @@
         <v>46007</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>46008</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>46010</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45455</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>44641</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34337,7 +34337,7 @@
         <v>46010</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>44911</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>46009</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>45399</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>46280</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>46010</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>45054</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>45271</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>46239</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>46024</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>45789</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>46282</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>46239</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>46030</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>46283</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>46029</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>46031</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>46034</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>46034</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>46034</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>46034</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>45195</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>46035</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>46036</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>46036</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>46036</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>46036</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36343,7 +36343,7 @@
         <v>46036</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>46036</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36489,7 +36489,7 @@
         <v>46036</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>46036</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>45712</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>45188</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>46287</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>45229</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>45020</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>45540</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>45982</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37156,7 +37156,7 @@
         <v>45488</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>45036</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>44923</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>46044</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>46287</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>45797</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>46245</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45797</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>45797</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>46044</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>45797</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>46288</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>46034</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>46244</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>45799</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>46245</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38354,7 +38354,7 @@
         <v>45800</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38432,7 +38432,7 @@
         <v>46247</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>45800</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45804</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45747</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>45804</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>45804</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>45294</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38958,7 +38958,7 @@
         <v>45747</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45805</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>45805</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39187,7 +39187,7 @@
         <v>46055</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>45720</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39338,7 +39338,7 @@
         <v>46246</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>45807</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>45322</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>45807</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>46289</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45810</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>46059</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>46059</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>46059</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>46059</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40073,7 +40073,7 @@
         <v>46064</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40146,7 +40146,7 @@
         <v>46287</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>46064</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45503</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45720</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40448,7 +40448,7 @@
         <v>45817</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40526,7 +40526,7 @@
         <v>45818</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>45762</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40672,7 +40672,7 @@
         <v>45740</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40745,7 +40745,7 @@
         <v>46066</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>45818</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>45483</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>46070</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>45818</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41110,7 +41110,7 @@
         <v>45820</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>45749</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>46296</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>45824</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>45821</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>46073</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41553,7 +41553,7 @@
         <v>45821</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
         <v>46073</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>45821</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>46073</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>45824</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>46296</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>45827</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45832</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45832</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45831</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42313,7 +42313,7 @@
         <v>46085</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42386,7 +42386,7 @@
         <v>45709</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45831</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>46073</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>45833</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>46126</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>45833</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>45726</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>45835</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45838</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>45838</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>46093</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>45840</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
         <v>46092</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>46093</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>45840</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>45839</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>46093</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45874</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>46092</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45839</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43876,7 +43876,7 @@
         <v>45841</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43954,7 +43954,7 @@
         <v>45841</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44027,7 +44027,7 @@
         <v>45842</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>45841</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44178,7 +44178,7 @@
         <v>45841</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44251,7 +44251,7 @@
         <v>45841</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44329,7 +44329,7 @@
         <v>46098</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44402,7 +44402,7 @@
         <v>45357</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45846</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>46100</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>46104</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>46259</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>45434</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>46301</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>44928</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>45849</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45074,7 +45074,7 @@
         <v>46302</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>46107</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45225,7 +45225,7 @@
         <v>45849</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45298,7 +45298,7 @@
         <v>45849</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>45853</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>45855</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>45855</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>45483</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>46297</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>46297</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45694</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45892,7 +45892,7 @@
         <v>46303</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45511</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46038,7 +46038,7 @@
         <v>45867</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46111,7 +46111,7 @@
         <v>46121</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46189,7 +46189,7 @@
         <v>45225</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>46127</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>45195</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>46126</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45583</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46564,7 +46564,7 @@
         <v>46127</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>46128</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46710,7 +46710,7 @@
         <v>46132</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45880</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46861,7 +46861,7 @@
         <v>45880</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>46132</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47012,7 +47012,7 @@
         <v>45880</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>46128</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>44896</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>46133</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47309,7 +47309,7 @@
         <v>46134</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>44907</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47460,7 +47460,7 @@
         <v>45488</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47538,7 +47538,7 @@
         <v>46308</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>45456</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47689,7 +47689,7 @@
         <v>45491</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47767,7 +47767,7 @@
         <v>45491</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>45476</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>46135</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>46136</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48069,7 +48069,7 @@
         <v>46307</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>45525</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45883</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48293,7 +48293,7 @@
         <v>46267</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48366,7 +48366,7 @@
         <v>45721</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>45608</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48512,7 +48512,7 @@
         <v>45525</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48590,7 +48590,7 @@
         <v>45875</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48663,7 +48663,7 @@
         <v>45831</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48736,7 +48736,7 @@
         <v>45749</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48809,7 +48809,7 @@
         <v>45547</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>44928</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48955,7 +48955,7 @@
         <v>45665</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49028,7 +49028,7 @@
         <v>45153</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>46140</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45561</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>45448</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45225</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49393,7 +49393,7 @@
         <v>45162</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49466,7 +49466,7 @@
         <v>45636</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49539,7 +49539,7 @@
         <v>45600</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49617,7 +49617,7 @@
         <v>45824</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>45041</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49768,7 +49768,7 @@
         <v>46031</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49841,7 +49841,7 @@
         <v>46272</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>45566</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>46272</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>45336</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>46133</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50216,7 +50216,7 @@
         <v>46272</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50294,7 +50294,7 @@
         <v>45406</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50367,7 +50367,7 @@
         <v>46272</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50445,7 +50445,7 @@
         <v>45902</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45534</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50596,7 +50596,7 @@
         <v>45757</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50669,7 +50669,7 @@
         <v>45632</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50742,7 +50742,7 @@
         <v>45609</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>45449</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50893,7 +50893,7 @@
         <v>46315</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50971,7 +50971,7 @@
         <v>45792</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>45442</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51117,7 +51117,7 @@
         <v>46275</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51195,7 +51195,7 @@
         <v>45575</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>44916</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>45749</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51419,7 +51419,7 @@
         <v>46275</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51497,7 +51497,7 @@
         <v>46274</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51570,7 +51570,7 @@
         <v>46274</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45654</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>46142</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         <v>45485</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>45470</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         <v>45510</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52028,7 +52028,7 @@
         <v>45266</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52101,7 +52101,7 @@
         <v>45429</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52179,7 +52179,7 @@
         <v>46317</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52252,7 +52252,7 @@
         <v>45841</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52330,7 +52330,7 @@
         <v>44512</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>45679</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45244</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52554,7 +52554,7 @@
         <v>46274</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52632,7 +52632,7 @@
         <v>44923</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52705,7 +52705,7 @@
         <v>44923</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>45757</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>46275</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52929,7 +52929,7 @@
         <v>46146</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53007,7 +53007,7 @@
         <v>46029</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53085,7 +53085,7 @@
         <v>46148</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53163,7 +53163,7 @@
         <v>45646</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53236,7 +53236,7 @@
         <v>45646</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53309,7 +53309,7 @@
         <v>45817</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>46149</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>44903</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>45007</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53611,7 +53611,7 @@
         <v>46149</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53689,7 +53689,7 @@
         <v>46153</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45191</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53835,7 +53835,7 @@
         <v>45226</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53913,7 +53913,7 @@
         <v>45187</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53986,7 +53986,7 @@
         <v>44994</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54059,7 +54059,7 @@
         <v>45874</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54132,7 +54132,7 @@
         <v>45559</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54205,7 +54205,7 @@
         <v>44923</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54278,7 +54278,7 @@
         <v>46160</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>45579</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54434,7 +54434,7 @@
         <v>46160</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54512,7 +54512,7 @@
         <v>45580</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54585,7 +54585,7 @@
         <v>45636</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54658,7 +54658,7 @@
         <v>45574</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>45225</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54814,7 +54814,7 @@
         <v>45461</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45519</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54960,7 +54960,7 @@
         <v>45204</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>44981</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55116,7 +55116,7 @@
         <v>45673</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55189,7 +55189,7 @@
         <v>45728</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55262,7 +55262,7 @@
         <v>45636</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>45769</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55408,7 +55408,7 @@
         <v>45659</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55481,7 +55481,7 @@
         <v>45712</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55554,7 +55554,7 @@
         <v>45642</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55627,7 +55627,7 @@
         <v>45638</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55700,7 +55700,7 @@
         <v>45034</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55773,7 +55773,7 @@
         <v>45034</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55846,7 +55846,7 @@
         <v>45629</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>45639</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55992,7 +55992,7 @@
         <v>45727</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56065,7 +56065,7 @@
         <v>44508</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56138,7 +56138,7 @@
         <v>45747</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56211,7 +56211,7 @@
         <v>45243</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56284,7 +56284,7 @@
         <v>45089</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56362,7 +56362,7 @@
         <v>45219</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56435,7 +56435,7 @@
         <v>44978</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56508,7 +56508,7 @@
         <v>45237</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56581,7 +56581,7 @@
         <v>44697</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56654,7 +56654,7 @@
         <v>45763</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         <v>45168</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56805,7 +56805,7 @@
         <v>45684</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56878,7 +56878,7 @@
         <v>45672</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45119</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57024,7 +57024,7 @@
         <v>45509</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57097,7 +57097,7 @@
         <v>45223</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57175,7 +57175,7 @@
         <v>45078</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57253,7 +57253,7 @@
         <v>44789</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57326,7 +57326,7 @@
         <v>45027</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57399,7 +57399,7 @@
         <v>45244</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57472,7 +57472,7 @@
         <v>45071</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57550,7 +57550,7 @@
         <v>45761</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57628,7 +57628,7 @@
         <v>45769</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57701,7 +57701,7 @@
         <v>45439</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57779,7 +57779,7 @@
         <v>44881</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57852,7 +57852,7 @@
         <v>45769</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57925,7 +57925,7 @@
         <v>45077</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57998,7 +57998,7 @@
         <v>45037</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58071,7 +58071,7 @@
         <v>45614</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58144,7 +58144,7 @@
         <v>44791</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58222,7 +58222,7 @@
         <v>45301</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
         <v>45714</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58368,7 +58368,7 @@
         <v>45757</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58441,7 +58441,7 @@
         <v>44837</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         <v>45106</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58597,7 +58597,7 @@
         <v>45749</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58670,7 +58670,7 @@
         <v>45128</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58748,7 +58748,7 @@
         <v>45491</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58821,7 +58821,7 @@
         <v>44540</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58899,7 +58899,7 @@
         <v>44903</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58972,7 +58972,7 @@
         <v>45118</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59045,7 +59045,7 @@
         <v>45756</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59123,7 +59123,7 @@
         <v>45194</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59196,7 +59196,7 @@
         <v>45672</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59269,7 +59269,7 @@
         <v>45271</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59342,7 +59342,7 @@
         <v>45462</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59415,7 +59415,7 @@
         <v>45530</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59488,7 +59488,7 @@
         <v>45608</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59561,7 +59561,7 @@
         <v>45539</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59639,7 +59639,7 @@
         <v>44938</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59712,7 +59712,7 @@
         <v>45149</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59790,7 +59790,7 @@
         <v>45236</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59863,7 +59863,7 @@
         <v>44523</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59941,7 +59941,7 @@
         <v>45229</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60019,7 +60019,7 @@
         <v>45428</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60092,7 +60092,7 @@
         <v>45079</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>44599</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60238,7 +60238,7 @@
         <v>45355</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60311,7 +60311,7 @@
         <v>45355</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60384,7 +60384,7 @@
         <v>45548</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60457,7 +60457,7 @@
         <v>45621</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60530,7 +60530,7 @@
         <v>45517</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60603,7 +60603,7 @@
         <v>45560</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60681,7 +60681,7 @@
         <v>45204</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60759,7 +60759,7 @@
         <v>45483</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60832,7 +60832,7 @@
         <v>45036</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60905,7 +60905,7 @@
         <v>45541</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60983,7 +60983,7 @@
         <v>45054</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61056,7 +61056,7 @@
         <v>45713</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61129,7 +61129,7 @@
         <v>45645</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61202,7 +61202,7 @@
         <v>45097</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61275,7 +61275,7 @@
         <v>45642</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61348,7 +61348,7 @@
         <v>45597</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61421,7 +61421,7 @@
         <v>45072</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>45203</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61572,7 +61572,7 @@
         <v>45121</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61650,7 +61650,7 @@
         <v>45677</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61723,7 +61723,7 @@
         <v>45072</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61796,7 +61796,7 @@
         <v>45197</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61869,7 +61869,7 @@
         <v>45201</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61942,7 +61942,7 @@
         <v>45624</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62015,7 +62015,7 @@
         <v>45714</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62088,7 +62088,7 @@
         <v>45236</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -62166,7 +62166,7 @@
         <v>45093</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62239,7 +62239,7 @@
         <v>44804</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62312,7 +62312,7 @@
         <v>45204</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62390,7 +62390,7 @@
         <v>45231</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62463,7 +62463,7 @@
         <v>45629</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62536,7 +62536,7 @@
         <v>45775</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62609,7 +62609,7 @@
         <v>45198</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62687,7 +62687,7 @@
         <v>45211</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62760,7 +62760,7 @@
         <v>44677</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62838,7 +62838,7 @@
         <v>45621</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62911,7 +62911,7 @@
         <v>45622</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62989,7 +62989,7 @@
         <v>45642</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63062,7 +63062,7 @@
         <v>45642</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -63135,7 +63135,7 @@
         <v>45191</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63208,7 +63208,7 @@
         <v>45177</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63281,7 +63281,7 @@
         <v>45246</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63354,7 +63354,7 @@
         <v>45245</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63427,7 +63427,7 @@
         <v>45175</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63500,7 +63500,7 @@
         <v>45245</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63573,7 +63573,7 @@
         <v>45188</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63646,7 +63646,7 @@
         <v>45188</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63719,7 +63719,7 @@
         <v>45175</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63792,7 +63792,7 @@
         <v>45225</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63865,7 +63865,7 @@
         <v>45252</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63938,7 +63938,7 @@
         <v>44739</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64011,7 +64011,7 @@
         <v>45645</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -64084,7 +64084,7 @@
         <v>45257</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -64157,7 +64157,7 @@
         <v>44782</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64235,7 +64235,7 @@
         <v>45727</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64308,7 +64308,7 @@
         <v>45252</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64381,7 +64381,7 @@
         <v>45713</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64454,7 +64454,7 @@
         <v>45322</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64527,7 +64527,7 @@
         <v>44886</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64600,7 +64600,7 @@
         <v>44881</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64673,7 +64673,7 @@
         <v>45237</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64746,7 +64746,7 @@
         <v>45237</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64819,7 +64819,7 @@
         <v>45257</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64892,7 +64892,7 @@
         <v>45769</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64970,7 +64970,7 @@
         <v>45355</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -65043,7 +65043,7 @@
         <v>44908</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -65121,7 +65121,7 @@
         <v>44950</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65194,7 +65194,7 @@
         <v>44950</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65267,7 +65267,7 @@
         <v>45272</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65340,7 +65340,7 @@
         <v>45355</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65418,7 +65418,7 @@
         <v>45541</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65496,7 +65496,7 @@
         <v>44495</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65569,7 +65569,7 @@
         <v>45301</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65642,7 +65642,7 @@
         <v>45303</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65715,7 +65715,7 @@
         <v>44938</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65788,7 +65788,7 @@
         <v>45567</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65861,7 +65861,7 @@
         <v>45547</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65934,7 +65934,7 @@
         <v>45053</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -66007,7 +66007,7 @@
         <v>44860</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -66080,7 +66080,7 @@
         <v>44900</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -66158,7 +66158,7 @@
         <v>45623</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66231,7 +66231,7 @@
         <v>45453</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66304,7 +66304,7 @@
         <v>44897</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66377,7 +66377,7 @@
         <v>44740</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66455,7 +66455,7 @@
         <v>44589</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66533,7 +66533,7 @@
         <v>44957</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66606,7 +66606,7 @@
         <v>44832</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66679,7 +66679,7 @@
         <v>44741</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66757,7 +66757,7 @@
         <v>45420</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66830,7 +66830,7 @@
         <v>44979</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66903,7 +66903,7 @@
         <v>44722</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66981,7 +66981,7 @@
         <v>44684</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -67059,7 +67059,7 @@
         <v>45371</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -67132,7 +67132,7 @@
         <v>45699</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67210,7 +67210,7 @@
         <v>45756</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67288,7 +67288,7 @@
         <v>45778</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67361,7 +67361,7 @@
         <v>45342</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67434,7 +67434,7 @@
         <v>46089</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67512,7 +67512,7 @@
         <v>46072</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67590,7 +67590,7 @@
         <v>46171</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>

--- a/Översikt MALUNG-SÄLEN.xlsx
+++ b/Översikt MALUNG-SÄLEN.xlsx
@@ -601,7 +601,7 @@
         <v>46057</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>46070</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44722</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>46205</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>46149</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>46174</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46184</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>46033</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45092</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>46316</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>46181</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>46033</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45016</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>44637</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45812</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>46140</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>46178</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>45785</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>46205</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>44796</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>46157</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45775</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>45917</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>46069</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>46191</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>45897</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>45469</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>46055</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>45016</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>46089</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45533</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>46196</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>46295</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>46316</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45932</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>46178</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>46178</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>46196</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>46104</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>46033</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>46055</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>45510</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>45016</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44610</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45938</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>46055</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>44090</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>44722</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>46178</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>46190</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>45583</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>45099</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45775</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>46055</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>45839</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>46029</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44722</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44810</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>45971</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>45799</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>46055</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>46092</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>45903</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>45713</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>45443</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>46258</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>46093</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>44796</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>44725</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>45181</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>45754</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>44589</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>45315</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>45903</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>44704</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>45895</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>45925</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>45995</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>46164</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>45233</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>45831</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>45831</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>44936</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>44501</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>45714</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>44641</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>44741</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>44722</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>44721</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>45623</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>45957</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>45713</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>45971</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>45461</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>45119</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>44867</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>45053</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>46029</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>46287</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>46290</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>44523</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>45538</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>44910</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>46266</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>45824</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>46274</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>45461</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45705</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>44944</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45631</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>45247</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>45187</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>45188</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>45246</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>45053</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>44637</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>45411</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44512</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>44508</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44537</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>44511</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>44712</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>44852</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>44733</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>44811</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>44756</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>44887</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>44696</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>44616</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>44503</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44588</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>44809</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>44602</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>44533</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>44529</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>44501</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>44613</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>44540</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>44701</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>44721</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>44557</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>44547</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>44802</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44512</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>44886</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>44721</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44739</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44743</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>44743</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>44616</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>44811</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>44839</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44749</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>44544</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>44858</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44501</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>44600</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>44603</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>44743</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>45762</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>44811</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>44811</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45089</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>45187</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         <v>45215</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>44637</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>45890</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>45890</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>45891</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>45891</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45892</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45891</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>45891</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44623</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>45894</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>45162</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>44946</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>45895</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>44725</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45775</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45674</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45883</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>45898</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>45450</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45898</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>45541</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45540</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45902</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>44795</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45902</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45204</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>45902</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45902</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45901</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>44862</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45531</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>44623</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45904</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45904</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45875</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>45908</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45481</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45226</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>46160</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>45910</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>45910</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>45041</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>45477</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>45106</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>45912</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>44511</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>45911</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>45912</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45916</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45915</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>45916</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21962,7 +21962,7 @@
         <v>45916</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>45713</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>44923</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>44963</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
         <v>45919</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22327,7 +22327,7 @@
         <v>45919</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>45919</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>45007</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>45925</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>45926</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>45592</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>45926</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44643</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>45335</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>45930</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>44978</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>45931</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23218,7 +23218,7 @@
         <v>44911</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>45931</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>45231</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>45931</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>45538</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>45933</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>45933</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>45936</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>45252</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>45597</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>45936</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>45936</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>45937</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>44938</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>44501</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24338,7 +24338,7 @@
         <v>45937</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>45937</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>45937</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>45937</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>46174</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>45939</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>45930</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45391</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45072</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>46177</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45321</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>45293</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>44894</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>44928</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>45931</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>44903</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>45267</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>45947</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>45952</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45761</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45951</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>45952</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>45202</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45957</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>45957</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>45957</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>45957</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>45957</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26457,7 +26457,7 @@
         <v>45957</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>45960</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>45301</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>45574</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>45960</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>45959</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>45960</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>45644</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>45670</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>45964</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>45541</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27290,7 +27290,7 @@
         <v>45460</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>45964</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>45964</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>46189</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>45964</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>46189</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>45677</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>44881</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>45965</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>45965</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45965</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>45965</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>45967</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>45257</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>45967</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>45925</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45971</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45665</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45238</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>45971</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45972</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>45972</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>45560</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>45152</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>45974</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>45973</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>45090</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>45072</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>45973</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>45974</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>44515</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45062</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45978</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>45978</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>44931</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29925,7 +29925,7 @@
         <v>45980</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>45339</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45980</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>46202</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>45407</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>44888</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>45979</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>45163</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30524,7 +30524,7 @@
         <v>45981</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>45643</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>45238</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>45430</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>45177</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30889,7 +30889,7 @@
         <v>46205</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>44914</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>46204</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31108,7 +31108,7 @@
         <v>45439</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>45566</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>45692</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>45987</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>45204</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>45987</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>45624</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45624</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45294</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>44897</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>44546</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>45992</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>46211</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>45992</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>46211</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>45989</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>45672</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>45989</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45446</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>45993</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>45993</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>45993</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45432</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45999</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45215</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>46001</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>46002</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33124,7 +33124,7 @@
         <v>46001</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33202,7 +33202,7 @@
         <v>46002</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>46006</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>46006</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>46226</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>46003</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>46231</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>46003</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33723,7 +33723,7 @@
         <v>45525</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>46008</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>45482</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33952,7 +33952,7 @@
         <v>46007</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>46008</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>46010</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45455</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>44641</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34337,7 +34337,7 @@
         <v>46010</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>44911</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>46009</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>45399</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>46280</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>46010</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>45054</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>45271</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>46239</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>46024</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>45789</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>46282</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>46239</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>46030</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>46283</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>46029</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>46031</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>46034</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>46034</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>46034</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>46034</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>45195</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>46035</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>46036</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>46036</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>46036</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>46036</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36343,7 +36343,7 @@
         <v>46036</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>46036</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36489,7 +36489,7 @@
         <v>46036</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>46036</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>45712</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>45188</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>46287</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>45229</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>45020</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>45540</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>45982</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37156,7 +37156,7 @@
         <v>45488</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>45036</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>44923</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>46044</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>46287</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>45797</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>46245</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45797</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>45797</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>46044</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>45797</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>46288</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>46034</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>46244</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>45799</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>46245</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38354,7 +38354,7 @@
         <v>45800</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38432,7 +38432,7 @@
         <v>46247</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>45800</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45804</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45747</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>45804</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>45804</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>45294</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38958,7 +38958,7 @@
         <v>45747</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>45805</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>45805</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39187,7 +39187,7 @@
         <v>46055</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>45720</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39338,7 +39338,7 @@
         <v>46246</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>45807</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>45322</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>45807</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>46289</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45810</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>46059</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>46059</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>46059</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>46059</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40073,7 +40073,7 @@
         <v>46064</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40146,7 +40146,7 @@
         <v>46287</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>46064</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45503</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45720</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40448,7 +40448,7 @@
         <v>45817</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40526,7 +40526,7 @@
         <v>45818</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>45762</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40672,7 +40672,7 @@
         <v>45740</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40745,7 +40745,7 @@
         <v>46066</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>45818</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>45483</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>46070</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>45818</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41110,7 +41110,7 @@
         <v>45820</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>45749</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>46296</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>45824</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>45821</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>46073</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41553,7 +41553,7 @@
         <v>45821</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
         <v>46073</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>45821</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>46073</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>45824</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>46296</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>45827</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45832</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45832</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45831</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42313,7 +42313,7 @@
         <v>46085</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42386,7 +42386,7 @@
         <v>45709</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45831</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>46073</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>45833</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>46126</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>45833</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>45726</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>45835</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45838</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>45838</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>46093</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>45840</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
         <v>46092</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>46093</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>45840</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>45839</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>46093</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45874</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>46092</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45839</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43876,7 +43876,7 @@
         <v>45841</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43954,7 +43954,7 @@
         <v>45841</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44027,7 +44027,7 @@
         <v>45842</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>45841</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44178,7 +44178,7 @@
         <v>45841</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44251,7 +44251,7 @@
         <v>45841</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44329,7 +44329,7 @@
         <v>46098</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44402,7 +44402,7 @@
         <v>45357</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45846</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>46100</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>46104</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>46259</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>45434</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>46301</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>44928</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>45849</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45074,7 +45074,7 @@
         <v>46302</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>46107</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45225,7 +45225,7 @@
         <v>45849</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45298,7 +45298,7 @@
         <v>45849</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>45853</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>45855</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>45855</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>45483</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>46297</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>46297</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45694</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45892,7 +45892,7 @@
         <v>46303</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45511</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46038,7 +46038,7 @@
         <v>45867</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46111,7 +46111,7 @@
         <v>46121</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46189,7 +46189,7 @@
         <v>45225</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>46127</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>45195</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>46126</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45583</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46564,7 +46564,7 @@
         <v>46127</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>46128</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46710,7 +46710,7 @@
         <v>46132</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45880</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46861,7 +46861,7 @@
         <v>45880</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>46132</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47012,7 +47012,7 @@
         <v>45880</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>46128</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>44896</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>46133</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47309,7 +47309,7 @@
         <v>46134</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>44907</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47460,7 +47460,7 @@
         <v>45488</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47538,7 +47538,7 @@
         <v>46308</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>45456</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47689,7 +47689,7 @@
         <v>45491</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47767,7 +47767,7 @@
         <v>45491</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>45476</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>46135</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>46136</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48069,7 +48069,7 @@
         <v>46307</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>45525</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45883</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48293,7 +48293,7 @@
         <v>46267</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48366,7 +48366,7 @@
         <v>45721</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>45608</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48512,7 +48512,7 @@
         <v>45525</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48590,7 +48590,7 @@
         <v>45875</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48663,7 +48663,7 @@
         <v>45831</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48736,7 +48736,7 @@
         <v>45749</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48809,7 +48809,7 @@
         <v>45547</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>44928</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48955,7 +48955,7 @@
         <v>45665</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49028,7 +49028,7 @@
         <v>45153</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>46140</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45561</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>45448</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45225</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49393,7 +49393,7 @@
         <v>45162</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49466,7 +49466,7 @@
         <v>45636</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49539,7 +49539,7 @@
         <v>45600</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49617,7 +49617,7 @@
         <v>45824</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>45041</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49768,7 +49768,7 @@
         <v>46031</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49841,7 +49841,7 @@
         <v>46272</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>45566</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>46272</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>45336</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>46133</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50216,7 +50216,7 @@
         <v>46272</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50294,7 +50294,7 @@
         <v>45406</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50367,7 +50367,7 @@
         <v>46272</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50445,7 +50445,7 @@
         <v>45902</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45534</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50596,7 +50596,7 @@
         <v>45757</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50669,7 +50669,7 @@
         <v>45632</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50742,7 +50742,7 @@
         <v>45609</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>45449</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50893,7 +50893,7 @@
         <v>46315</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50971,7 +50971,7 @@
         <v>45792</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>45442</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51117,7 +51117,7 @@
         <v>46275</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51195,7 +51195,7 @@
         <v>45575</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>44916</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>45749</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51419,7 +51419,7 @@
         <v>46275</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51497,7 +51497,7 @@
         <v>46274</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51570,7 +51570,7 @@
         <v>46274</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45654</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>46142</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         <v>45485</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>45470</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         <v>45510</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52028,7 +52028,7 @@
         <v>45266</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52101,7 +52101,7 @@
         <v>45429</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52179,7 +52179,7 @@
         <v>46317</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52252,7 +52252,7 @@
         <v>45841</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52330,7 +52330,7 @@
         <v>44512</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>45679</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45244</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52554,7 +52554,7 @@
         <v>46274</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52632,7 +52632,7 @@
         <v>44923</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52705,7 +52705,7 @@
         <v>44923</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>45757</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>46275</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52929,7 +52929,7 @@
         <v>46146</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53007,7 +53007,7 @@
         <v>46029</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53085,7 +53085,7 @@
         <v>46148</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53163,7 +53163,7 @@
         <v>45646</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53236,7 +53236,7 @@
         <v>45646</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53309,7 +53309,7 @@
         <v>45817</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>46149</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>44903</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>45007</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53611,7 +53611,7 @@
         <v>46149</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53689,7 +53689,7 @@
         <v>46153</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45191</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53835,7 +53835,7 @@
         <v>45226</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53913,7 +53913,7 @@
         <v>45187</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53986,7 +53986,7 @@
         <v>44994</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54059,7 +54059,7 @@
         <v>45874</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54132,7 +54132,7 @@
         <v>45559</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54205,7 +54205,7 @@
         <v>44923</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54278,7 +54278,7 @@
         <v>46160</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>45579</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54434,7 +54434,7 @@
         <v>46160</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54512,7 +54512,7 @@
         <v>45580</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54585,7 +54585,7 @@
         <v>45636</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54658,7 +54658,7 @@
         <v>45574</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>45225</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54814,7 +54814,7 @@
         <v>45461</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45519</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54960,7 +54960,7 @@
         <v>45204</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>44981</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55116,7 +55116,7 @@
         <v>45673</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55189,7 +55189,7 @@
         <v>45728</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55262,7 +55262,7 @@
         <v>45636</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>45769</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55408,7 +55408,7 @@
         <v>45659</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55481,7 +55481,7 @@
         <v>45712</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55554,7 +55554,7 @@
         <v>45642</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55627,7 +55627,7 @@
         <v>45638</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55700,7 +55700,7 @@
         <v>45034</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55773,7 +55773,7 @@
         <v>45034</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55846,7 +55846,7 @@
         <v>45629</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>45639</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55992,7 +55992,7 @@
         <v>45727</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56065,7 +56065,7 @@
         <v>44508</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56138,7 +56138,7 @@
         <v>45747</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56211,7 +56211,7 @@
         <v>45243</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56284,7 +56284,7 @@
         <v>45089</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56362,7 +56362,7 @@
         <v>45219</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56435,7 +56435,7 @@
         <v>44978</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56508,7 +56508,7 @@
         <v>45237</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56581,7 +56581,7 @@
         <v>44697</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56654,7 +56654,7 @@
         <v>45763</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56732,7 +56732,7 @@
         <v>45168</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56805,7 +56805,7 @@
         <v>45684</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56878,7 +56878,7 @@
         <v>45672</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45119</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57024,7 +57024,7 @@
         <v>45509</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57097,7 +57097,7 @@
         <v>45223</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57175,7 +57175,7 @@
         <v>45078</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57253,7 +57253,7 @@
         <v>44789</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57326,7 +57326,7 @@
         <v>45027</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57399,7 +57399,7 @@
         <v>45244</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57472,7 +57472,7 @@
         <v>45071</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57550,7 +57550,7 @@
         <v>45761</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57628,7 +57628,7 @@
         <v>45769</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57701,7 +57701,7 @@
         <v>45439</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57779,7 +57779,7 @@
         <v>44881</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57852,7 +57852,7 @@
         <v>45769</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57925,7 +57925,7 @@
         <v>45077</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57998,7 +57998,7 @@
         <v>45037</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58071,7 +58071,7 @@
         <v>45614</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58144,7 +58144,7 @@
         <v>44791</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58222,7 +58222,7 @@
         <v>45301</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
         <v>45714</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58368,7 +58368,7 @@
         <v>45757</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58441,7 +58441,7 @@
         <v>44837</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         <v>45106</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58597,7 +58597,7 @@
         <v>45749</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58670,7 +58670,7 @@
         <v>45128</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58748,7 +58748,7 @@
         <v>45491</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58821,7 +58821,7 @@
         <v>44540</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58899,7 +58899,7 @@
         <v>44903</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58972,7 +58972,7 @@
         <v>45118</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59045,7 +59045,7 @@
         <v>45756</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59123,7 +59123,7 @@
         <v>45194</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59196,7 +59196,7 @@
         <v>45672</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59269,7 +59269,7 @@
         <v>45271</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59342,7 +59342,7 @@
         <v>45462</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59415,7 +59415,7 @@
         <v>45530</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59488,7 +59488,7 @@
         <v>45608</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59561,7 +59561,7 @@
         <v>45539</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59639,7 +59639,7 @@
         <v>44938</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59712,7 +59712,7 @@
         <v>45149</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59790,7 +59790,7 @@
         <v>45236</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59863,7 +59863,7 @@
         <v>44523</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59941,7 +59941,7 @@
         <v>45229</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60019,7 +60019,7 @@
         <v>45428</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60092,7 +60092,7 @@
         <v>45079</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         <v>44599</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60238,7 +60238,7 @@
         <v>45355</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60311,7 +60311,7 @@
         <v>45355</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60384,7 +60384,7 @@
         <v>45548</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60457,7 +60457,7 @@
         <v>45621</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60530,7 +60530,7 @@
         <v>45517</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60603,7 +60603,7 @@
         <v>45560</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60681,7 +60681,7 @@
         <v>45204</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60759,7 +60759,7 @@
         <v>45483</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60832,7 +60832,7 @@
         <v>45036</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60905,7 +60905,7 @@
         <v>45541</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60983,7 +60983,7 @@
         <v>45054</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61056,7 +61056,7 @@
         <v>45713</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61129,7 +61129,7 @@
         <v>45645</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61202,7 +61202,7 @@
         <v>45097</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61275,7 +61275,7 @@
         <v>45642</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61348,7 +61348,7 @@
         <v>45597</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61421,7 +61421,7 @@
         <v>45072</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>45203</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61572,7 +61572,7 @@
         <v>45121</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61650,7 +61650,7 @@
         <v>45677</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61723,7 +61723,7 @@
         <v>45072</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61796,7 +61796,7 @@
         <v>45197</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61869,7 +61869,7 @@
         <v>45201</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61942,7 +61942,7 @@
         <v>45624</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62015,7 +62015,7 @@
         <v>45714</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62088,7 +62088,7 @@
         <v>45236</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -62166,7 +62166,7 @@
         <v>45093</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62239,7 +62239,7 @@
         <v>44804</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62312,7 +62312,7 @@
         <v>45204</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62390,7 +62390,7 @@
         <v>45231</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62463,7 +62463,7 @@
         <v>45629</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62536,7 +62536,7 @@
         <v>45775</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62609,7 +62609,7 @@
         <v>45198</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62687,7 +62687,7 @@
         <v>45211</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62760,7 +62760,7 @@
         <v>44677</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62838,7 +62838,7 @@
         <v>45621</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62911,7 +62911,7 @@
         <v>45622</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62989,7 +62989,7 @@
         <v>45642</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63062,7 +63062,7 @@
         <v>45642</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -63135,7 +63135,7 @@
         <v>45191</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63208,7 +63208,7 @@
         <v>45177</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63281,7 +63281,7 @@
         <v>45246</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63354,7 +63354,7 @@
         <v>45245</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63427,7 +63427,7 @@
         <v>45175</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63500,7 +63500,7 @@
         <v>45245</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63573,7 +63573,7 @@
         <v>45188</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63646,7 +63646,7 @@
         <v>45188</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63719,7 +63719,7 @@
         <v>45175</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63792,7 +63792,7 @@
         <v>45225</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63865,7 +63865,7 @@
         <v>45252</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63938,7 +63938,7 @@
         <v>44739</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64011,7 +64011,7 @@
         <v>45645</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -64084,7 +64084,7 @@
         <v>45257</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -64157,7 +64157,7 @@
         <v>44782</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64235,7 +64235,7 @@
         <v>45727</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64308,7 +64308,7 @@
         <v>45252</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64381,7 +64381,7 @@
         <v>45713</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -64454,7 +64454,7 @@
         <v>45322</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -64527,7 +64527,7 @@
         <v>44886</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -64600,7 +64600,7 @@
         <v>44881</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -64673,7 +64673,7 @@
         <v>45237</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -64746,7 +64746,7 @@
         <v>45237</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -64819,7 +64819,7 @@
         <v>45257</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64892,7 +64892,7 @@
         <v>45769</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64970,7 +64970,7 @@
         <v>45355</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -65043,7 +65043,7 @@
         <v>44908</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -65121,7 +65121,7 @@
         <v>44950</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65194,7 +65194,7 @@
         <v>44950</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65267,7 +65267,7 @@
         <v>45272</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -65340,7 +65340,7 @@
         <v>45355</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -65418,7 +65418,7 @@
         <v>45541</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65496,7 +65496,7 @@
         <v>44495</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -65569,7 +65569,7 @@
         <v>45301</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -65642,7 +65642,7 @@
         <v>45303</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -65715,7 +65715,7 @@
         <v>44938</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -65788,7 +65788,7 @@
         <v>45567</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65861,7 +65861,7 @@
         <v>45547</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65934,7 +65934,7 @@
         <v>45053</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -66007,7 +66007,7 @@
         <v>44860</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -66080,7 +66080,7 @@
         <v>44900</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -66158,7 +66158,7 @@
         <v>45623</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -66231,7 +66231,7 @@
         <v>45453</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -66304,7 +66304,7 @@
         <v>44897</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -66377,7 +66377,7 @@
         <v>44740</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -66455,7 +66455,7 @@
         <v>44589</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -66533,7 +66533,7 @@
         <v>44957</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -66606,7 +66606,7 @@
         <v>44832</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -66679,7 +66679,7 @@
         <v>44741</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -66757,7 +66757,7 @@
         <v>45420</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -66830,7 +66830,7 @@
         <v>44979</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66903,7 +66903,7 @@
         <v>44722</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66981,7 +66981,7 @@
         <v>44684</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -67059,7 +67059,7 @@
         <v>45371</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -67132,7 +67132,7 @@
         <v>45699</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -67210,7 +67210,7 @@
         <v>45756</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -67288,7 +67288,7 @@
         <v>45778</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -67361,7 +67361,7 @@
         <v>45342</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -67434,7 +67434,7 @@
         <v>46089</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -67512,7 +67512,7 @@
         <v>46072</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -67590,7 +67590,7 @@
         <v>46171</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
